--- a/MDT_Model.xlsx
+++ b/MDT_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Health Care\MedTech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C299E12D-1D64-4529-A1C5-C16A53DA18F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE657204-D818-43CE-989B-5BE997F636CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -6976,9 +6976,6 @@
   </si>
   <si>
     <t>Taxes</t>
-  </si>
-  <si>
-    <t>Q2'25</t>
   </si>
   <si>
     <t>Q3 2020</t>
@@ -7736,10 +7733,13 @@
     <t>This initiative was to work through structural challenges the business was facing including … Subpar growth and market share erosion; supply chain and operational inefficiencies due to unalligned global footprint; product innovation cycle and regulatory hurdles; and a perceived "bureaucratic" structure ... Business culture is difficult to reorient once set in ... its been almost six years</t>
   </si>
   <si>
-    <t>10/31/25</t>
-  </si>
-  <si>
     <t xml:space="preserve">Revenue Breakdown by Segment </t>
+  </si>
+  <si>
+    <t>Q2'26</t>
+  </si>
+  <si>
+    <t>1/10/2026</t>
   </si>
 </sst>
 </file>
@@ -17344,10 +17344,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="78">
-        <v>91.17</v>
+        <v>97.89</v>
       </c>
       <c r="D3" s="55" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="4" spans="1:47">
@@ -17355,10 +17355,10 @@
         <v>113</v>
       </c>
       <c r="C4" s="70">
-        <v>1282.68</v>
+        <v>1282.01</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>2284</v>
+        <v>2315</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>139</v>
@@ -17370,7 +17370,7 @@
       </c>
       <c r="C5" s="70">
         <f>C3*C4</f>
-        <v>116941.93560000001</v>
+        <v>125495.9589</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>7</v>
@@ -17384,11 +17384,11 @@
         <v>3</v>
       </c>
       <c r="C6" s="70">
-        <f>1273+6848</f>
-        <v>8121</v>
+        <f>1282+7045</f>
+        <v>8327</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2284</v>
+        <v>2315</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>168</v>
@@ -17402,11 +17402,11 @@
         <v>4</v>
       </c>
       <c r="C7" s="70">
-        <f>2430+26179</f>
-        <v>28609</v>
+        <f>1420+27680</f>
+        <v>29100</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>2284</v>
+        <v>2315</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>2228</v>
@@ -17421,7 +17421,7 @@
       </c>
       <c r="C8" s="70">
         <f>C5-C6+C7</f>
-        <v>137429.93560000003</v>
+        <v>146268.9589</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>8</v>
@@ -17594,27 +17594,27 @@
     </row>
     <row r="22" spans="1:18">
       <c r="B22" s="1" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="C23" s="1" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="C24" s="1" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="D25" s="1" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="B26" s="1" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -17624,32 +17624,32 @@
     </row>
     <row r="28" spans="1:18">
       <c r="B28" s="1" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="C29" s="1" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="15">
       <c r="D30" s="1" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="15">
       <c r="E31" s="1" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="D32" s="1" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15">
       <c r="C33" s="1" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -17659,52 +17659,52 @@
     </row>
     <row r="35" spans="1:5" ht="15">
       <c r="C35" s="1" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15">
       <c r="D36" s="1" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="E37" s="1" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="D38" s="1" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15">
       <c r="C39" s="1" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="D40" s="1" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="D41" s="1" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="B42" s="1" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="B43" s="1" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="C44" s="1" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -17742,9 +17742,6 @@
     <hyperlink ref="R18" r:id="rId16" xr:uid="{91F2DA07-B0F2-477B-AE34-A8449AD4A1B5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="D3" twoDigitTextYear="1"/>
-  </ignoredErrors>
   <drawing r:id="rId17"/>
 </worksheet>
 </file>
@@ -18020,10 +18017,10 @@
         <v>59</v>
       </c>
       <c r="Y3" s="33" t="s">
+        <v>2284</v>
+      </c>
+      <c r="Z3" s="33" t="s">
         <v>2285</v>
-      </c>
-      <c r="Z3" s="33" t="s">
-        <v>2286</v>
       </c>
       <c r="AA3" s="33" t="s">
         <v>62</v>
@@ -18823,23 +18820,23 @@
       </c>
       <c r="BR7" s="61">
         <f t="shared" ref="BR7:BV7" si="7">BQ7*(1+BR21)</f>
-        <v>13448.277499999998</v>
+        <v>13529.404</v>
       </c>
       <c r="BS7" s="61">
         <f t="shared" si="7"/>
-        <v>14154.312068749998</v>
+        <v>14408.815259999999</v>
       </c>
       <c r="BT7" s="61">
         <f t="shared" si="7"/>
-        <v>14791.256111843746</v>
+        <v>15186.891284040001</v>
       </c>
       <c r="BU7" s="61">
         <f t="shared" si="7"/>
-        <v>15382.906356317497</v>
+        <v>15870.3013918218</v>
       </c>
       <c r="BV7" s="61">
         <f t="shared" si="7"/>
-        <v>15921.308078788608</v>
+        <v>16457.502543319206</v>
       </c>
       <c r="BW7" s="60"/>
       <c r="BX7" s="60"/>
@@ -19309,23 +19306,23 @@
       </c>
       <c r="BR11" s="61">
         <f t="shared" ref="BR11:BV11" si="11">BQ11*(1+BR22)</f>
-        <v>10091.125</v>
+        <v>10189.574999999999</v>
       </c>
       <c r="BS11" s="61">
         <f t="shared" si="11"/>
-        <v>10368.6309375</v>
+        <v>10505.451824999998</v>
       </c>
       <c r="BT11" s="61">
         <f t="shared" si="11"/>
-        <v>10679.689865625</v>
+        <v>10820.615379749999</v>
       </c>
       <c r="BU11" s="61">
         <f t="shared" si="11"/>
-        <v>11026.779786257812</v>
+        <v>11172.285379591875</v>
       </c>
       <c r="BV11" s="61">
         <f t="shared" si="11"/>
-        <v>11357.583179845546</v>
+        <v>11563.315367877589</v>
       </c>
       <c r="BW11" s="61"/>
       <c r="BX11" s="61"/>
@@ -19699,23 +19696,23 @@
       </c>
       <c r="BR14" s="61">
         <f>BQ14*(1+BR24)</f>
-        <v>8743.2800000000007</v>
+        <v>9331.77</v>
       </c>
       <c r="BS14" s="61">
         <f t="shared" ref="BS14:BV14" si="15">BR14*(1+BS24)</f>
-        <v>9180.4440000000013</v>
+        <v>10124.970450000001</v>
       </c>
       <c r="BT14" s="61">
         <f t="shared" si="15"/>
-        <v>9685.3684200000007</v>
+        <v>10681.84382475</v>
       </c>
       <c r="BU14" s="61">
         <f t="shared" si="15"/>
-        <v>10169.636841000001</v>
+        <v>11215.9360159875</v>
       </c>
       <c r="BV14" s="61">
         <f t="shared" si="15"/>
-        <v>10627.270498845</v>
+        <v>11720.653136706936</v>
       </c>
       <c r="BW14" s="61"/>
       <c r="BX14" s="61"/>
@@ -20184,23 +20181,23 @@
       </c>
       <c r="BR18" s="61">
         <f t="shared" ref="BR18:BV18" si="21">BQ18*(1+BR24)</f>
-        <v>2914.08</v>
+        <v>3110.2200000000003</v>
       </c>
       <c r="BS18" s="61">
         <f t="shared" si="21"/>
-        <v>3059.7840000000001</v>
+        <v>3374.5887000000002</v>
       </c>
       <c r="BT18" s="61">
         <f t="shared" si="21"/>
-        <v>3228.0721199999998</v>
+        <v>3560.1910785</v>
       </c>
       <c r="BU18" s="61">
         <f t="shared" si="21"/>
-        <v>3389.4757260000001</v>
+        <v>3738.2006324250001</v>
       </c>
       <c r="BV18" s="61">
         <f t="shared" si="21"/>
-        <v>3542.0021336699997</v>
+        <v>3906.4196608841248</v>
       </c>
       <c r="BW18" s="60"/>
       <c r="BX18" s="60"/>
@@ -20382,23 +20379,23 @@
       </c>
       <c r="BR19" s="61">
         <f t="shared" ref="BR19:BU19" si="27">BR7+BR11+BR14+BR18</f>
-        <v>35196.762499999997</v>
+        <v>36160.968999999997</v>
       </c>
       <c r="BS19" s="61">
         <f t="shared" si="27"/>
-        <v>36763.171006249999</v>
+        <v>38413.826235</v>
       </c>
       <c r="BT19" s="61">
         <f t="shared" si="27"/>
-        <v>38384.386517468745</v>
+        <v>40249.541567040003</v>
       </c>
       <c r="BU19" s="61">
         <f t="shared" si="27"/>
-        <v>39968.798709575305</v>
+        <v>41996.723419826179</v>
       </c>
       <c r="BV19" s="61">
         <f t="shared" ref="BV19" si="28">BV7+BV11+BV14+BV18</f>
-        <v>41448.163891149154</v>
+        <v>43647.890708787854</v>
       </c>
       <c r="BW19" s="60"/>
       <c r="BX19" s="60"/>
@@ -20558,19 +20555,19 @@
         <v>5.7500000000000002E-2</v>
       </c>
       <c r="BR21" s="62">
-        <v>7.7499999999999999E-2</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="BS21" s="62">
-        <v>5.2499999999999998E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="BT21" s="62">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="BU21" s="62">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="BU21" s="62">
-        <v>0.04</v>
-      </c>
       <c r="BV21" s="62">
-        <v>3.5000000000000003E-2</v>
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="BW21" s="62"/>
     </row>
@@ -20671,10 +20668,10 @@
         <v>0.03</v>
       </c>
       <c r="BR22" s="62">
-        <v>2.5000000000000001E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="BS22" s="62">
-        <v>2.75E-2</v>
+        <v>3.1E-2</v>
       </c>
       <c r="BT22" s="62">
         <v>0.03</v>
@@ -20683,7 +20680,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
       <c r="BV22" s="62">
-        <v>0.03</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="BW22" s="62"/>
     </row>
@@ -20784,7 +20781,7 @@
         <v>0.05</v>
       </c>
       <c r="BR23" s="62">
-        <v>0.01</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="BS23" s="62">
         <v>0.03</v>
@@ -20897,10 +20894,10 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="BR24" s="62">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="BS24" s="62">
-        <v>0.05</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="BT24" s="62">
         <v>5.5E-2</v>
@@ -21152,23 +21149,23 @@
       </c>
       <c r="BR25" s="69">
         <f t="shared" ref="BR25:BV25" si="41">BR19/BQ19-1</f>
-        <v>4.9553078872819345E-2</v>
+        <v>7.8305322797077581E-2</v>
       </c>
       <c r="BS25" s="69">
         <f t="shared" si="41"/>
-        <v>4.4504334915747013E-2</v>
+        <v>6.2300798272302949E-2</v>
       </c>
       <c r="BT25" s="69">
         <f t="shared" si="41"/>
-        <v>4.4098902973933596E-2</v>
+        <v>4.7787880353543866E-2</v>
       </c>
       <c r="BU25" s="69">
         <f t="shared" si="41"/>
-        <v>4.1277517653838025E-2</v>
+        <v>4.3408739199576996E-2</v>
       </c>
       <c r="BV25" s="69">
         <f t="shared" si="41"/>
-        <v>3.7013000874090318E-2</v>
+        <v>3.9316574115926706E-2</v>
       </c>
       <c r="BW25" s="69"/>
       <c r="BX25" s="60"/>
@@ -22064,28 +22061,28 @@
         <v>4.7454503570605766E-2</v>
       </c>
       <c r="AU36" s="44">
-        <f>AU32/AQ32-1</f>
+        <f t="shared" ref="AU36:AV38" si="57">AU32/AQ32-1</f>
         <v>3.478686918177365E-2</v>
       </c>
       <c r="AV36" s="44">
-        <f>AV32/AR32-1</f>
+        <f t="shared" si="57"/>
         <v>4.9256505576208198E-2</v>
       </c>
       <c r="BM36" s="44"/>
       <c r="BN36" s="44">
-        <f t="shared" ref="BN36:BO36" si="57">BN32/BM32-1</f>
+        <f t="shared" ref="BN36:BO36" si="58">BN32/BM32-1</f>
         <v>3.9227053140096668E-2</v>
       </c>
       <c r="BO36" s="44">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>1.4813437461261847E-2</v>
       </c>
       <c r="BP36" s="44">
-        <f t="shared" ref="BP36:BQ38" si="58">BP32/BO32-1</f>
+        <f t="shared" ref="BP36:BQ38" si="59">BP32/BO32-1</f>
         <v>1.1543394613082514E-2</v>
       </c>
       <c r="BQ36" s="44">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>3.6710542205047769E-2</v>
       </c>
     </row>
@@ -22094,59 +22091,59 @@
         <v>2203</v>
       </c>
       <c r="AE37" s="44">
-        <f t="shared" ref="AE37:AT37" si="59">AE33/AA33-1</f>
+        <f t="shared" ref="AE37:AT37" si="60">AE33/AA33-1</f>
         <v>0.23162230671736372</v>
       </c>
       <c r="AF37" s="44">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>7.1527971054828887E-2</v>
       </c>
       <c r="AG37" s="44">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-3.1282586027111536E-3</v>
       </c>
       <c r="AH37" s="44">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-3.9930122285999348E-3</v>
       </c>
       <c r="AI37" s="44">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-7.2806791870337007E-2</v>
       </c>
       <c r="AJ37" s="44">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-8.6753246753246804E-2</v>
       </c>
       <c r="AK37" s="44">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-4.1579497907949792E-2</v>
       </c>
       <c r="AL37" s="44">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.9543973941368087E-2</v>
       </c>
       <c r="AM37" s="44">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>4.8002219755826969E-2</v>
       </c>
       <c r="AN37" s="44">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>8.3333333333333259E-2</v>
       </c>
       <c r="AO37" s="44">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>8.2673942701227743E-2</v>
       </c>
       <c r="AP37" s="44">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>4.3991152617350648E-2</v>
       </c>
       <c r="AQ37" s="44">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.4826581943341299E-2</v>
       </c>
       <c r="AR37" s="44">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>7.6135468626936209E-2</v>
       </c>
       <c r="AS37" s="44">
@@ -22154,32 +22151,32 @@
         <v>2.1925403225806495E-2</v>
       </c>
       <c r="AT37" s="44">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>3.0602636534839966E-2</v>
       </c>
       <c r="AU37" s="44">
-        <f>AU33/AQ33-1</f>
+        <f t="shared" si="57"/>
         <v>0.13592486303156792</v>
       </c>
       <c r="AV37" s="44">
-        <f>AV33/AR33-1</f>
+        <f t="shared" si="57"/>
         <v>8.4410831910221917E-2</v>
       </c>
       <c r="BM37" s="44"/>
       <c r="BN37" s="44">
-        <f t="shared" ref="BN37:BO37" si="60">BN33/BM33-1</f>
+        <f t="shared" ref="BN37:BO37" si="61">BN33/BM33-1</f>
         <v>6.578947368421062E-2</v>
       </c>
       <c r="BO37" s="44">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>-4.4881687242798396E-2</v>
       </c>
       <c r="BP37" s="44">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>6.3821192944661265E-2</v>
       </c>
       <c r="BQ37" s="44">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>3.562840146816848E-2</v>
       </c>
     </row>
@@ -22188,59 +22185,59 @@
         <v>2204</v>
       </c>
       <c r="AE38" s="44">
-        <f t="shared" ref="AE38:AT38" si="61">AE34/AA34-1</f>
+        <f t="shared" ref="AE38:AT38" si="62">AE34/AA34-1</f>
         <v>0.22744736437682489</v>
       </c>
       <c r="AF38" s="44">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>2.6154047338825759E-2</v>
       </c>
       <c r="AG38" s="44">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-1.543408360128562E-3</v>
       </c>
       <c r="AH38" s="44">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-1.209086468001952E-2</v>
       </c>
       <c r="AI38" s="44">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-7.7125328659070957E-2</v>
       </c>
       <c r="AJ38" s="44">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-3.338855613610292E-2</v>
       </c>
       <c r="AK38" s="44">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>-4.6373824552363718E-3</v>
       </c>
       <c r="AL38" s="44">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>5.6249227345778197E-2</v>
       </c>
       <c r="AM38" s="44">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>4.4905711572378326E-2</v>
       </c>
       <c r="AN38" s="44">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>5.2603823335530597E-2</v>
       </c>
       <c r="AO38" s="44">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>4.6848712307493212E-2</v>
       </c>
       <c r="AP38" s="44">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>5.2668539325841923E-3</v>
       </c>
       <c r="AQ38" s="44">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>2.7655154505323187E-2</v>
       </c>
       <c r="AR38" s="44">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>5.247995991983978E-2</v>
       </c>
       <c r="AS38" s="44">
@@ -22248,32 +22245,32 @@
         <v>2.5095809123500956E-2</v>
       </c>
       <c r="AT38" s="44">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>3.9119804400977953E-2</v>
       </c>
       <c r="AU38" s="44">
-        <f>AU34/AQ34-1</f>
+        <f t="shared" si="57"/>
         <v>8.3765003158559725E-2</v>
       </c>
       <c r="AV38" s="44">
-        <f>AV34/AR34-1</f>
+        <f t="shared" si="57"/>
         <v>6.6404855408782604E-2</v>
       </c>
       <c r="BM38" s="44"/>
       <c r="BN38" s="44">
-        <f t="shared" ref="BN38:BO38" si="62">BN34/BM34-1</f>
+        <f t="shared" ref="BN38:BO38" si="63">BN34/BM34-1</f>
         <v>5.2096822392668551E-2</v>
       </c>
       <c r="BO38" s="44">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>-1.4485892823328905E-2</v>
       </c>
       <c r="BP38" s="44">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>3.6410798347583873E-2</v>
       </c>
       <c r="BQ38" s="44">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>3.6182177728340204E-2</v>
       </c>
     </row>
@@ -22289,75 +22286,75 @@
         <v>90</v>
       </c>
       <c r="AA40" s="44">
-        <f t="shared" ref="AA40:AR40" si="63">AA32/AA34</f>
+        <f t="shared" ref="AA40:AR40" si="64">AA32/AA34</f>
         <v>0.51498386353158132</v>
       </c>
       <c r="AB40" s="44">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.53014253955799662</v>
       </c>
       <c r="AC40" s="44">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.5066237942122187</v>
       </c>
       <c r="AD40" s="44">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.51062530532486561</v>
       </c>
       <c r="AE40" s="44">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.51333416802303744</v>
       </c>
       <c r="AF40" s="44">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.50936663693131135</v>
       </c>
       <c r="AG40" s="44">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.50740693031044704</v>
       </c>
       <c r="AH40" s="44">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.50661392013845963</v>
       </c>
       <c r="AI40" s="44">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.51105684439017773</v>
       </c>
       <c r="AJ40" s="44">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.53645352669742918</v>
       </c>
       <c r="AK40" s="44">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.52568914196971661</v>
       </c>
       <c r="AL40" s="44">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.52375936329588013</v>
       </c>
       <c r="AM40" s="44">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.5096078940534926</v>
       </c>
       <c r="AN40" s="44">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.52292084168336672</v>
       </c>
       <c r="AO40" s="44">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.50945728767461984</v>
       </c>
       <c r="AP40" s="44">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.50541390150192111</v>
       </c>
       <c r="AQ40" s="44">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.51572962728995575</v>
       </c>
       <c r="AR40" s="44">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.51219802451505414</v>
       </c>
       <c r="AS40" s="44">
@@ -22365,7 +22362,7 @@
         <v>0.51097443318861557</v>
       </c>
       <c r="AT40" s="44">
-        <f t="shared" ref="AT40" si="64">AT32/AT34</f>
+        <f t="shared" ref="AT40" si="65">AT32/AT34</f>
         <v>0.50946778711484597</v>
       </c>
       <c r="AU40" s="44">
@@ -22377,15 +22374,15 @@
         <v>0.50396161142729601</v>
       </c>
       <c r="BM40" s="44">
-        <f t="shared" ref="BM40:BO40" si="65">BM32/BM34</f>
+        <f t="shared" ref="BM40:BO40" si="66">BM32/BM34</f>
         <v>0.51548959059667299</v>
       </c>
       <c r="BN40" s="44">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.5091838666919144</v>
       </c>
       <c r="BO40" s="44">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.52432190091907649</v>
       </c>
       <c r="BP40" s="44">
@@ -22402,75 +22399,75 @@
         <v>2202</v>
       </c>
       <c r="AA41" s="44">
-        <f t="shared" ref="AA41:AR41" si="66">AA33/AA34</f>
+        <f t="shared" ref="AA41:AR41" si="67">AA33/AA34</f>
         <v>0.48501613646841862</v>
       </c>
       <c r="AB41" s="44">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.46985746044200338</v>
       </c>
       <c r="AC41" s="44">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.49337620578778135</v>
       </c>
       <c r="AD41" s="44">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.48937469467513434</v>
       </c>
       <c r="AE41" s="44">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.48666583197696256</v>
       </c>
       <c r="AF41" s="44">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.49063336306868865</v>
       </c>
       <c r="AG41" s="44">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.49259306968955302</v>
       </c>
       <c r="AH41" s="44">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.49338607986154037</v>
       </c>
       <c r="AI41" s="44">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.48894315560982227</v>
       </c>
       <c r="AJ41" s="44">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.46354647330257087</v>
       </c>
       <c r="AK41" s="44">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.47431085803028344</v>
       </c>
       <c r="AL41" s="44">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.47624063670411987</v>
       </c>
       <c r="AM41" s="44">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.4903921059465074</v>
       </c>
       <c r="AN41" s="44">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.47707915831663328</v>
       </c>
       <c r="AO41" s="44">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.49054271232538016</v>
       </c>
       <c r="AP41" s="44">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.49458609849807894</v>
       </c>
       <c r="AQ41" s="44">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.48427037271004419</v>
       </c>
       <c r="AR41" s="44">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0.48780197548494586</v>
       </c>
       <c r="AS41" s="44">
@@ -22478,7 +22475,7 @@
         <v>0.48902556681138448</v>
       </c>
       <c r="AT41" s="44">
-        <f t="shared" ref="AT41" si="67">AT33/AT34</f>
+        <f t="shared" ref="AT41" si="68">AT33/AT34</f>
         <v>0.49053221288515408</v>
       </c>
       <c r="AU41" s="44">
@@ -22490,15 +22487,15 @@
         <v>0.49603838857270394</v>
       </c>
       <c r="BM41" s="44">
-        <f t="shared" ref="BM41:BO41" si="68">BM33/BM34</f>
+        <f t="shared" ref="BM41:BO41" si="69">BM33/BM34</f>
         <v>0.48451040940332701</v>
       </c>
       <c r="BN41" s="44">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.4908161333080856</v>
       </c>
       <c r="BO41" s="44">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0.47567809908092357</v>
       </c>
       <c r="BP41" s="44">
@@ -22587,75 +22584,75 @@
         <v>5997</v>
       </c>
       <c r="AA43" s="2">
-        <f t="shared" ref="AA43:AR43" si="69">AA19</f>
+        <f t="shared" ref="AA43:AR43" si="70">AA19</f>
         <v>6507</v>
       </c>
       <c r="AB43" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>7647</v>
       </c>
       <c r="AC43" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>7775</v>
       </c>
       <c r="AD43" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>8188</v>
       </c>
       <c r="AE43" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>7987</v>
       </c>
       <c r="AF43" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>7847</v>
       </c>
       <c r="AG43" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>7763</v>
       </c>
       <c r="AH43" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>8089</v>
       </c>
       <c r="AI43" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>7371</v>
       </c>
       <c r="AJ43" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>7585</v>
       </c>
       <c r="AK43" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>7727</v>
       </c>
       <c r="AL43" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>8544</v>
       </c>
       <c r="AM43" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>7702</v>
       </c>
       <c r="AN43" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>7984</v>
       </c>
       <c r="AO43" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>8089</v>
       </c>
       <c r="AP43" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>8589</v>
       </c>
       <c r="AQ43" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>7915</v>
       </c>
       <c r="AR43" s="2">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>8403</v>
       </c>
       <c r="AS43" s="2">
@@ -22663,7 +22660,7 @@
         <v>8292</v>
       </c>
       <c r="AT43" s="2">
-        <f t="shared" ref="AT43" si="70">AT19</f>
+        <f t="shared" ref="AT43" si="71">AT19</f>
         <v>8925</v>
       </c>
       <c r="AU43" s="2">
@@ -22695,43 +22692,43 @@
       <c r="BC43" s="34"/>
       <c r="BD43" s="34"/>
       <c r="BG43" s="2">
-        <f>SUM(C43:F43)</f>
+        <f t="shared" ref="BG43:BG60" si="72">SUM(C43:F43)</f>
         <v>20261</v>
       </c>
       <c r="BH43" s="2">
-        <f>SUM(G43:J43)</f>
+        <f t="shared" ref="BH43:BH60" si="73">SUM(G43:J43)</f>
         <v>28833</v>
       </c>
       <c r="BI43" s="2">
-        <f>SUM(K43:N43)</f>
+        <f t="shared" ref="BI43:BI60" si="74">SUM(K43:N43)</f>
         <v>29710</v>
       </c>
       <c r="BJ43" s="2">
-        <f>SUM(O43:R43)</f>
+        <f t="shared" ref="BJ43:BJ60" si="75">SUM(O43:R43)</f>
         <v>29953</v>
       </c>
       <c r="BK43" s="2">
-        <f>SUM(S43:V43)</f>
+        <f t="shared" ref="BK43:BK60" si="76">SUM(S43:V43)</f>
         <v>30557</v>
       </c>
       <c r="BL43" s="2">
-        <f>SUM(W43:Z43)</f>
+        <f t="shared" ref="BL43:BL60" si="77">SUM(W43:Z43)</f>
         <v>28913</v>
       </c>
       <c r="BM43" s="2">
-        <f>SUM(AA43:AD43)</f>
+        <f t="shared" ref="BM43:BM58" si="78">SUM(AA43:AD43)</f>
         <v>30117</v>
       </c>
       <c r="BN43" s="2">
-        <f>SUM(AE43:AH43)</f>
+        <f t="shared" ref="BN43:BN58" si="79">SUM(AE43:AH43)</f>
         <v>31686</v>
       </c>
       <c r="BO43" s="2">
-        <f>SUM(AI43:AL43)</f>
+        <f t="shared" ref="BO43:BO58" si="80">SUM(AI43:AL43)</f>
         <v>31227</v>
       </c>
       <c r="BP43" s="2">
-        <f>SUM(AM43:AP43)</f>
+        <f t="shared" ref="BP43:BP58" si="81">SUM(AM43:AP43)</f>
         <v>32364</v>
       </c>
       <c r="BQ43" s="58">
@@ -22739,24 +22736,24 @@
         <v>33535</v>
       </c>
       <c r="BR43" s="61">
-        <f t="shared" ref="BR43:BU43" si="71">BR19</f>
-        <v>35196.762499999997</v>
+        <f t="shared" ref="BR43:BU43" si="82">BR19</f>
+        <v>36160.968999999997</v>
       </c>
       <c r="BS43" s="61">
-        <f t="shared" si="71"/>
-        <v>36763.171006249999</v>
+        <f t="shared" si="82"/>
+        <v>38413.826235</v>
       </c>
       <c r="BT43" s="61">
-        <f t="shared" si="71"/>
-        <v>38384.386517468745</v>
+        <f t="shared" si="82"/>
+        <v>40249.541567040003</v>
       </c>
       <c r="BU43" s="61">
-        <f t="shared" si="71"/>
-        <v>39968.798709575305</v>
+        <f t="shared" si="82"/>
+        <v>41996.723419826179</v>
       </c>
       <c r="BV43" s="61">
-        <f t="shared" ref="BV43" si="72">BV19</f>
-        <v>41448.163891149154</v>
+        <f t="shared" ref="BV43" si="83">BV19</f>
+        <v>43647.890708787854</v>
       </c>
       <c r="BW43" s="60"/>
       <c r="BX43" s="60"/>
@@ -22964,68 +22961,68 @@
         <v>3061</v>
       </c>
       <c r="BG44" s="1">
-        <f>SUM(C44:F44)</f>
+        <f t="shared" si="72"/>
         <v>6309</v>
       </c>
       <c r="BH44" s="1">
-        <f>SUM(G44:J44)</f>
+        <f t="shared" si="73"/>
         <v>9142</v>
       </c>
       <c r="BI44" s="1">
-        <f>SUM(K44:N44)</f>
+        <f t="shared" si="74"/>
         <v>9294</v>
       </c>
       <c r="BJ44" s="1">
-        <f>SUM(O44:R44)</f>
+        <f t="shared" si="75"/>
         <v>9067</v>
       </c>
       <c r="BK44" s="1">
-        <f>SUM(S44:V44)</f>
+        <f t="shared" si="76"/>
         <v>9155</v>
       </c>
       <c r="BL44" s="1">
-        <f>SUM(W44:Z44)</f>
+        <f t="shared" si="77"/>
         <v>9424</v>
       </c>
       <c r="BM44" s="1">
-        <f>SUM(AA44:AD44)</f>
+        <f t="shared" si="78"/>
         <v>10483</v>
       </c>
       <c r="BN44" s="1">
-        <f>SUM(AE44:AH44)</f>
+        <f t="shared" si="79"/>
         <v>10145</v>
       </c>
       <c r="BO44" s="1">
-        <f>SUM(AI44:AL44)</f>
+        <f t="shared" si="80"/>
         <v>10719</v>
       </c>
       <c r="BP44" s="1">
-        <f>SUM(AM44:AP44)</f>
+        <f t="shared" si="81"/>
         <v>11216</v>
       </c>
       <c r="BQ44" s="1">
-        <f>SUM(AQ44:AT44)</f>
+        <f t="shared" ref="BQ44:BQ58" si="84">SUM(AQ44:AT44)</f>
         <v>11632</v>
       </c>
       <c r="BR44" s="63">
-        <f t="shared" ref="BR44:BU44" si="73">BR43*(1-BR62)</f>
-        <v>12318.866874999998</v>
+        <f t="shared" ref="BR44:BU44" si="85">BR43*(1-BR62)</f>
+        <v>12584.017211999999</v>
       </c>
       <c r="BS44" s="63">
-        <f t="shared" si="73"/>
-        <v>12793.583510174998</v>
+        <f t="shared" si="85"/>
+        <v>13291.183877309999</v>
       </c>
       <c r="BT44" s="63">
-        <f t="shared" si="73"/>
-        <v>13319.382121561654</v>
+        <f t="shared" si="85"/>
+        <v>13845.84229906176</v>
       </c>
       <c r="BU44" s="63">
-        <f t="shared" si="73"/>
-        <v>13829.204353513054</v>
+        <f t="shared" si="85"/>
+        <v>14362.879409580552</v>
       </c>
       <c r="BV44" s="63">
-        <f t="shared" ref="BV44" si="74">BV43*(1-BV62)</f>
-        <v>14299.616542446456</v>
+        <f t="shared" ref="BV44" si="86">BV43*(1-BV62)</f>
+        <v>14840.282840987869</v>
       </c>
     </row>
     <row r="45" spans="2:131">
@@ -23105,75 +23102,75 @@
         <v>3733</v>
       </c>
       <c r="AA45" s="1">
-        <f t="shared" ref="AA45:AR45" si="75">AA43-AA44</f>
+        <f t="shared" ref="AA45:AR45" si="87">AA43-AA44</f>
         <v>4002</v>
       </c>
       <c r="AB45" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>4942</v>
       </c>
       <c r="AC45" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>5154</v>
       </c>
       <c r="AD45" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>5536</v>
       </c>
       <c r="AE45" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>5389</v>
       </c>
       <c r="AF45" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>5350</v>
       </c>
       <c r="AG45" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>5304</v>
       </c>
       <c r="AH45" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>5498</v>
       </c>
       <c r="AI45" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>4855</v>
       </c>
       <c r="AJ45" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>5050</v>
       </c>
       <c r="AK45" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>5038</v>
       </c>
       <c r="AL45" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>5565</v>
       </c>
       <c r="AM45" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>5074</v>
       </c>
       <c r="AN45" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>5223</v>
       </c>
       <c r="AO45" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>5307</v>
       </c>
       <c r="AP45" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>5544</v>
       </c>
       <c r="AQ45" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>5154</v>
       </c>
       <c r="AR45" s="1">
-        <f t="shared" si="75"/>
+        <f t="shared" si="87"/>
         <v>5457</v>
       </c>
       <c r="AS45" s="1">
@@ -23181,7 +23178,7 @@
         <v>5513</v>
       </c>
       <c r="AT45" s="1">
-        <f t="shared" ref="AT45" si="76">AT43-AT44</f>
+        <f t="shared" ref="AT45" si="88">AT43-AT44</f>
         <v>5779</v>
       </c>
       <c r="AU45" s="1">
@@ -23193,68 +23190,68 @@
         <v>5900</v>
       </c>
       <c r="BG45" s="1">
-        <f>SUM(C45:F45)</f>
+        <f t="shared" si="72"/>
         <v>13952</v>
       </c>
       <c r="BH45" s="1">
-        <f>SUM(G45:J45)</f>
+        <f t="shared" si="73"/>
         <v>19691</v>
       </c>
       <c r="BI45" s="1">
-        <f>SUM(K45:N45)</f>
+        <f t="shared" si="74"/>
         <v>20416</v>
       </c>
       <c r="BJ45" s="1">
-        <f>SUM(O45:R45)</f>
+        <f t="shared" si="75"/>
         <v>20886</v>
       </c>
       <c r="BK45" s="1">
-        <f>SUM(S45:V45)</f>
+        <f t="shared" si="76"/>
         <v>21402</v>
       </c>
       <c r="BL45" s="1">
-        <f>SUM(W45:Z45)</f>
+        <f t="shared" si="77"/>
         <v>19489</v>
       </c>
       <c r="BM45" s="1">
-        <f>SUM(AA45:AD45)</f>
+        <f t="shared" si="78"/>
         <v>19634</v>
       </c>
       <c r="BN45" s="1">
-        <f>SUM(AE45:AH45)</f>
+        <f t="shared" si="79"/>
         <v>21541</v>
       </c>
       <c r="BO45" s="1">
-        <f>SUM(AI45:AL45)</f>
+        <f t="shared" si="80"/>
         <v>20508</v>
       </c>
       <c r="BP45" s="1">
-        <f>SUM(AM45:AP45)</f>
+        <f t="shared" si="81"/>
         <v>21148</v>
       </c>
       <c r="BQ45" s="1">
-        <f>SUM(AQ45:AT45)</f>
+        <f t="shared" si="84"/>
         <v>21903</v>
       </c>
       <c r="BR45" s="63">
-        <f t="shared" ref="BR45:BU45" si="77">BR43-BR44</f>
-        <v>22877.895624999997</v>
+        <f t="shared" ref="BR45:BU45" si="89">BR43-BR44</f>
+        <v>23576.951787999998</v>
       </c>
       <c r="BS45" s="63">
-        <f t="shared" si="77"/>
-        <v>23969.587496075001</v>
+        <f t="shared" si="89"/>
+        <v>25122.642357690002</v>
       </c>
       <c r="BT45" s="63">
-        <f t="shared" si="77"/>
-        <v>25065.00439590709</v>
+        <f t="shared" si="89"/>
+        <v>26403.699267978242</v>
       </c>
       <c r="BU45" s="63">
-        <f t="shared" si="77"/>
-        <v>26139.594356062251</v>
+        <f t="shared" si="89"/>
+        <v>27633.84401024563</v>
       </c>
       <c r="BV45" s="63">
-        <f t="shared" ref="BV45" si="78">BV43-BV44</f>
-        <v>27148.547348702697</v>
+        <f t="shared" ref="BV45" si="90">BV43-BV44</f>
+        <v>28807.607867799983</v>
       </c>
     </row>
     <row r="46" spans="2:131">
@@ -23405,68 +23402,68 @@
         <v>754</v>
       </c>
       <c r="BG46" s="1">
-        <f>SUM(C46:F46)</f>
+        <f t="shared" si="72"/>
         <v>1640</v>
       </c>
       <c r="BH46" s="1">
-        <f>SUM(G46:J46)</f>
+        <f t="shared" si="73"/>
         <v>2224</v>
       </c>
       <c r="BI46" s="1">
-        <f>SUM(K46:N46)</f>
+        <f t="shared" si="74"/>
         <v>2193</v>
       </c>
       <c r="BJ46" s="1">
-        <f>SUM(O46:R46)</f>
+        <f t="shared" si="75"/>
         <v>2256</v>
       </c>
       <c r="BK46" s="1">
-        <f>SUM(S46:V46)</f>
+        <f t="shared" si="76"/>
         <v>2330</v>
       </c>
       <c r="BL46" s="1">
-        <f>SUM(W46:Z46)</f>
+        <f t="shared" si="77"/>
         <v>2331</v>
       </c>
       <c r="BM46" s="1">
-        <f>SUM(AA46:AD46)</f>
+        <f t="shared" si="78"/>
         <v>2493</v>
       </c>
       <c r="BN46" s="1">
-        <f>SUM(AE46:AH46)</f>
+        <f t="shared" si="79"/>
         <v>2746</v>
       </c>
       <c r="BO46" s="1">
-        <f>SUM(AI46:AL46)</f>
+        <f t="shared" si="80"/>
         <v>2696</v>
       </c>
       <c r="BP46" s="1">
-        <f>SUM(AM46:AP46)</f>
+        <f t="shared" si="81"/>
         <v>2735</v>
       </c>
       <c r="BQ46" s="1">
-        <f>SUM(AQ46:AT46)</f>
+        <f t="shared" si="84"/>
         <v>2732</v>
       </c>
       <c r="BR46" s="63">
-        <f t="shared" ref="BR46:BU46" si="79">BR43*(BR63)</f>
-        <v>2921.3312874999997</v>
+        <f t="shared" ref="BR46:BU46" si="91">BR43*(BR63)</f>
+        <v>3001.3604270000001</v>
       </c>
       <c r="BS46" s="63">
-        <f t="shared" si="79"/>
-        <v>3051.34319351875</v>
+        <f t="shared" si="91"/>
+        <v>3188.3475775050001</v>
       </c>
       <c r="BT46" s="63">
-        <f t="shared" si="79"/>
-        <v>3185.9040809499061</v>
+        <f t="shared" si="91"/>
+        <v>3340.7119500643203</v>
       </c>
       <c r="BU46" s="63">
-        <f t="shared" si="79"/>
-        <v>3317.4102928947505</v>
+        <f t="shared" si="91"/>
+        <v>3485.7280438455732</v>
       </c>
       <c r="BV46" s="63">
-        <f t="shared" ref="BV46" si="80">BV43*(BV63)</f>
-        <v>3440.1976029653802</v>
+        <f t="shared" ref="BV46" si="92">BV43*(BV63)</f>
+        <v>3622.7749288293921</v>
       </c>
     </row>
     <row r="47" spans="2:131">
@@ -23617,68 +23614,68 @@
         <v>2965</v>
       </c>
       <c r="BG47" s="1">
-        <f>SUM(C47:F47)</f>
+        <f t="shared" si="72"/>
         <v>6904</v>
       </c>
       <c r="BH47" s="1">
-        <f>SUM(G47:J47)</f>
+        <f t="shared" si="73"/>
         <v>9469</v>
       </c>
       <c r="BI47" s="1">
-        <f>SUM(K47:N47)</f>
+        <f t="shared" si="74"/>
         <v>10018</v>
       </c>
       <c r="BJ47" s="1">
-        <f>SUM(O47:R47)</f>
+        <f t="shared" si="75"/>
         <v>10238</v>
       </c>
       <c r="BK47" s="1">
-        <f>SUM(S47:V47)</f>
+        <f t="shared" si="76"/>
         <v>10418</v>
       </c>
       <c r="BL47" s="1">
-        <f>SUM(W47:Z47)</f>
+        <f t="shared" si="77"/>
         <v>10109</v>
       </c>
       <c r="BM47" s="1">
-        <f>SUM(AA47:AD47)</f>
+        <f t="shared" si="78"/>
         <v>10143</v>
       </c>
       <c r="BN47" s="1">
-        <f>SUM(AE47:AH47)</f>
+        <f t="shared" si="79"/>
         <v>10292</v>
       </c>
       <c r="BO47" s="1">
-        <f>SUM(AI47:AL47)</f>
+        <f t="shared" si="80"/>
         <v>10415</v>
       </c>
       <c r="BP47" s="1">
-        <f>SUM(AM47:AP47)</f>
+        <f t="shared" si="81"/>
         <v>10736</v>
       </c>
       <c r="BQ47" s="1">
-        <f>SUM(AQ47:AT47)</f>
+        <f t="shared" si="84"/>
         <v>10849</v>
       </c>
       <c r="BR47" s="63">
-        <f t="shared" ref="BR47:BU47" si="81">BR43*(BR64)</f>
-        <v>11614.931624999999</v>
+        <f t="shared" ref="BR47:BU47" si="93">BR43*(BR64)</f>
+        <v>11752.314924999999</v>
       </c>
       <c r="BS47" s="63">
-        <f t="shared" si="81"/>
-        <v>12058.32009005</v>
+        <f t="shared" si="93"/>
+        <v>12407.665873905</v>
       </c>
       <c r="BT47" s="63">
-        <f t="shared" si="81"/>
-        <v>12474.925618177343</v>
+        <f t="shared" si="93"/>
+        <v>12920.102843019842</v>
       </c>
       <c r="BU47" s="63">
-        <f t="shared" si="81"/>
-        <v>12949.890781902399</v>
+        <f t="shared" si="93"/>
+        <v>13396.954770924551</v>
       </c>
       <c r="BV47" s="63">
-        <f t="shared" ref="BV47" si="82">BV43*(BV64)</f>
-        <v>13387.756936841177</v>
+        <f t="shared" ref="BV47" si="94">BV43*(BV64)</f>
+        <v>13836.381354685749</v>
       </c>
     </row>
     <row r="48" spans="2:131">
@@ -23829,67 +23826,67 @@
         <v>463</v>
       </c>
       <c r="BG48" s="1">
-        <f>SUM(C48:F48)</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="BH48" s="1">
-        <f>SUM(G48:J48)</f>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="BI48" s="1">
-        <f>SUM(K48:N48)</f>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="BJ48" s="1">
-        <f>SUM(O48:R48)</f>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="BK48" s="1">
-        <f>SUM(S48:V48)</f>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="BL48" s="1">
-        <f>SUM(W48:Z48)</f>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="BM48" s="1">
-        <f>SUM(AA48:AD48)</f>
+        <f t="shared" si="78"/>
         <v>1783</v>
       </c>
       <c r="BN48" s="1">
-        <f>SUM(AE48:AH48)</f>
+        <f t="shared" si="79"/>
         <v>1733</v>
       </c>
       <c r="BO48" s="1">
-        <f>SUM(AI48:AL48)</f>
+        <f t="shared" si="80"/>
         <v>1698</v>
       </c>
       <c r="BP48" s="1">
-        <f>SUM(AM48:AP48)</f>
+        <f t="shared" si="81"/>
         <v>1693</v>
       </c>
       <c r="BQ48" s="1">
-        <f>SUM(AQ48:AT48)</f>
+        <f t="shared" si="84"/>
         <v>1807</v>
       </c>
       <c r="BR48" s="63">
-        <f t="shared" ref="BR48:BV48" si="83">BQ48*1.02</f>
+        <f t="shared" ref="BR48:BV48" si="95">BQ48*1.02</f>
         <v>1843.14</v>
       </c>
       <c r="BS48" s="63">
-        <f t="shared" si="83"/>
+        <f t="shared" si="95"/>
         <v>1880.0028000000002</v>
       </c>
       <c r="BT48" s="63">
-        <f t="shared" si="83"/>
+        <f t="shared" si="95"/>
         <v>1917.6028560000002</v>
       </c>
       <c r="BU48" s="63">
-        <f t="shared" si="83"/>
+        <f t="shared" si="95"/>
         <v>1955.9549131200001</v>
       </c>
       <c r="BV48" s="63">
-        <f t="shared" si="83"/>
+        <f t="shared" si="95"/>
         <v>1995.0740113824002</v>
       </c>
     </row>
@@ -24041,47 +24038,47 @@
         <v>10</v>
       </c>
       <c r="BG49" s="1">
-        <f>SUM(C49:F49)</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="BH49" s="1">
-        <f>SUM(G49:J49)</f>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="BI49" s="1">
-        <f>SUM(K49:N49)</f>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="BJ49" s="1">
-        <f>SUM(O49:R49)</f>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="BK49" s="1">
-        <f>SUM(S49:V49)</f>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="BL49" s="1">
-        <f>SUM(W49:Z49)</f>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="BM49" s="1">
-        <f>SUM(AA49:AD49)</f>
+        <f t="shared" si="78"/>
         <v>293</v>
       </c>
       <c r="BN49" s="1">
-        <f>SUM(AE49:AH49)</f>
+        <f t="shared" si="79"/>
         <v>60</v>
       </c>
       <c r="BO49" s="1">
-        <f>SUM(AI49:AL49)</f>
+        <f t="shared" si="80"/>
         <v>375</v>
       </c>
       <c r="BP49" s="1">
-        <f>SUM(AM49:AP49)</f>
+        <f t="shared" si="81"/>
         <v>226</v>
       </c>
       <c r="BQ49" s="1">
-        <f>SUM(AQ49:AT49)</f>
+        <f t="shared" si="84"/>
         <v>267</v>
       </c>
       <c r="BR49" s="63">
@@ -24089,19 +24086,19 @@
         <v>272.34000000000003</v>
       </c>
       <c r="BS49" s="63">
-        <f t="shared" ref="BS49:BV49" si="84">BR49*1.02</f>
+        <f t="shared" ref="BS49:BV49" si="96">BR49*1.02</f>
         <v>277.78680000000003</v>
       </c>
       <c r="BT49" s="63">
-        <f t="shared" si="84"/>
+        <f t="shared" si="96"/>
         <v>283.34253600000005</v>
       </c>
       <c r="BU49" s="63">
-        <f t="shared" si="84"/>
+        <f t="shared" si="96"/>
         <v>289.00938672000007</v>
       </c>
       <c r="BV49" s="63">
-        <f t="shared" si="84"/>
+        <f t="shared" si="96"/>
         <v>294.78957445440005</v>
       </c>
     </row>
@@ -24288,47 +24285,47 @@
         <v>22</v>
       </c>
       <c r="BG50" s="1">
-        <f>SUM(C50:F50)</f>
+        <f t="shared" si="72"/>
         <v>1642</v>
       </c>
       <c r="BH50" s="1">
-        <f>SUM(G50:J50)</f>
+        <f t="shared" si="73"/>
         <v>2637</v>
       </c>
       <c r="BI50" s="1">
-        <f>SUM(K50:N50)</f>
+        <f t="shared" si="74"/>
         <v>2822</v>
       </c>
       <c r="BJ50" s="1">
-        <f>SUM(O50:R50)</f>
+        <f t="shared" si="75"/>
         <v>1752</v>
       </c>
       <c r="BK50" s="1">
-        <f>SUM(S50:V50)</f>
+        <f t="shared" si="76"/>
         <v>2386</v>
       </c>
       <c r="BL50" s="1">
-        <f>SUM(W50:Z50)</f>
+        <f t="shared" si="77"/>
         <v>2258</v>
       </c>
       <c r="BM50" s="1">
-        <f>SUM(AA50:AD50)</f>
+        <f t="shared" si="78"/>
         <v>433</v>
       </c>
       <c r="BN50" s="1">
-        <f>SUM(AE50:AH50)</f>
+        <f t="shared" si="79"/>
         <v>957</v>
       </c>
       <c r="BO50" s="1">
-        <f>SUM(AI50:AL50)</f>
+        <f t="shared" si="80"/>
         <v>-161</v>
       </c>
       <c r="BP50" s="1">
-        <f>SUM(AM50:AP50)</f>
+        <f t="shared" si="81"/>
         <v>614</v>
       </c>
       <c r="BQ50" s="1">
-        <f>SUM(AQ50:AT50)</f>
+        <f t="shared" si="84"/>
         <v>293</v>
       </c>
       <c r="BR50" s="63">
@@ -24336,19 +24333,19 @@
         <v>342.81</v>
       </c>
       <c r="BS50" s="63">
-        <f t="shared" ref="BS50:BV50" si="85">BR50*1.17</f>
+        <f t="shared" ref="BS50:BV50" si="97">BR50*1.17</f>
         <v>401.08769999999998</v>
       </c>
       <c r="BT50" s="63">
-        <f t="shared" si="85"/>
+        <f t="shared" si="97"/>
         <v>469.27260899999993</v>
       </c>
       <c r="BU50" s="63">
-        <f t="shared" si="85"/>
+        <f t="shared" si="97"/>
         <v>549.04895252999984</v>
       </c>
       <c r="BV50" s="63">
-        <f t="shared" si="85"/>
+        <f t="shared" si="97"/>
         <v>642.38727446009977</v>
       </c>
     </row>
@@ -24361,167 +24358,167 @@
         <v>1088</v>
       </c>
       <c r="D51" s="1">
-        <f t="shared" ref="D51:Z51" si="86">D45-SUM(D46:D50)</f>
+        <f t="shared" ref="D51:Z51" si="98">D45-SUM(D46:D50)</f>
         <v>1030</v>
       </c>
       <c r="E51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1275</v>
       </c>
       <c r="F51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>373</v>
       </c>
       <c r="G51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1131</v>
       </c>
       <c r="H51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1300</v>
       </c>
       <c r="I51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1355</v>
       </c>
       <c r="J51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1575</v>
       </c>
       <c r="K51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1167</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1385</v>
       </c>
       <c r="M51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1147</v>
       </c>
       <c r="N51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1684</v>
       </c>
       <c r="O51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1382</v>
       </c>
       <c r="P51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1197</v>
       </c>
       <c r="Q51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1436</v>
       </c>
       <c r="R51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>2625</v>
       </c>
       <c r="S51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1236</v>
       </c>
       <c r="T51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1544</v>
       </c>
       <c r="U51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1542</v>
       </c>
       <c r="V51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1946</v>
       </c>
       <c r="W51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1485</v>
       </c>
       <c r="X51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1351</v>
       </c>
       <c r="Y51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>1639</v>
       </c>
       <c r="Z51" s="1">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>316</v>
       </c>
       <c r="AA51" s="1">
-        <f t="shared" ref="AA51:AR51" si="87">AA45-SUM(AA46:AA50)</f>
+        <f t="shared" ref="AA51:AR51" si="99">AA45-SUM(AA46:AA50)</f>
         <v>673</v>
       </c>
       <c r="AB51" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="99"/>
         <v>930</v>
       </c>
       <c r="AC51" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="99"/>
         <v>1277</v>
       </c>
       <c r="AD51" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="99"/>
         <v>1609</v>
       </c>
       <c r="AE51" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="99"/>
         <v>859</v>
       </c>
       <c r="AF51" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="99"/>
         <v>1563</v>
       </c>
       <c r="AG51" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="99"/>
         <v>1659</v>
       </c>
       <c r="AH51" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="99"/>
         <v>1672</v>
       </c>
       <c r="AI51" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="99"/>
         <v>1125</v>
       </c>
       <c r="AJ51" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="99"/>
         <v>1404</v>
       </c>
       <c r="AK51" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="99"/>
         <v>1392</v>
       </c>
       <c r="AL51" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="99"/>
         <v>1564</v>
       </c>
       <c r="AM51" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="99"/>
         <v>1268</v>
       </c>
       <c r="AN51" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="99"/>
         <v>1340</v>
       </c>
       <c r="AO51" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="99"/>
         <v>1483</v>
       </c>
       <c r="AP51" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="99"/>
         <v>1053</v>
       </c>
       <c r="AQ51" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="99"/>
         <v>1278</v>
       </c>
       <c r="AR51" s="1">
-        <f t="shared" si="87"/>
+        <f t="shared" si="99"/>
         <v>1595</v>
       </c>
       <c r="AS51" s="1">
@@ -24529,7 +24526,7 @@
         <v>1646</v>
       </c>
       <c r="AT51" s="1">
-        <f t="shared" ref="AT51" si="88">AT45-SUM(AT46:AT50)</f>
+        <f t="shared" ref="AT51" si="100">AT45-SUM(AT46:AT50)</f>
         <v>1436</v>
       </c>
       <c r="AU51" s="1">
@@ -24541,68 +24538,68 @@
         <v>1686</v>
       </c>
       <c r="BG51" s="1">
-        <f>SUM(C51:F51)</f>
+        <f t="shared" si="72"/>
         <v>3766</v>
       </c>
       <c r="BH51" s="1">
-        <f>SUM(G51:J51)</f>
+        <f t="shared" si="73"/>
         <v>5361</v>
       </c>
       <c r="BI51" s="1">
-        <f>SUM(K51:N51)</f>
+        <f t="shared" si="74"/>
         <v>5383</v>
       </c>
       <c r="BJ51" s="1">
-        <f>SUM(O51:R51)</f>
+        <f t="shared" si="75"/>
         <v>6640</v>
       </c>
       <c r="BK51" s="1">
-        <f>SUM(S51:V51)</f>
+        <f t="shared" si="76"/>
         <v>6268</v>
       </c>
       <c r="BL51" s="1">
-        <f>SUM(W51:Z51)</f>
+        <f t="shared" si="77"/>
         <v>4791</v>
       </c>
       <c r="BM51" s="1">
-        <f>SUM(AA51:AD51)</f>
+        <f t="shared" si="78"/>
         <v>4489</v>
       </c>
       <c r="BN51" s="1">
-        <f>SUM(AE51:AH51)</f>
+        <f t="shared" si="79"/>
         <v>5753</v>
       </c>
       <c r="BO51" s="1">
-        <f>SUM(AI51:AL51)</f>
+        <f t="shared" si="80"/>
         <v>5485</v>
       </c>
       <c r="BP51" s="1">
-        <f>SUM(AM51:AP51)</f>
+        <f t="shared" si="81"/>
         <v>5144</v>
       </c>
       <c r="BQ51" s="1">
-        <f>SUM(AQ51:AT51)</f>
+        <f t="shared" si="84"/>
         <v>5955</v>
       </c>
       <c r="BR51" s="63">
-        <f t="shared" ref="BR51:BU51" si="89">BR45-SUM(BR46:BR50)</f>
-        <v>5883.342712499998</v>
+        <f t="shared" ref="BR51:BU51" si="101">BR45-SUM(BR46:BR50)</f>
+        <v>6364.9864359999992</v>
       </c>
       <c r="BS51" s="63">
-        <f t="shared" si="89"/>
-        <v>6301.0469125062482</v>
+        <f t="shared" si="101"/>
+        <v>6967.7516062799987</v>
       </c>
       <c r="BT51" s="63">
-        <f t="shared" si="89"/>
-        <v>6733.9566957798415</v>
+        <f t="shared" si="101"/>
+        <v>7472.6664738940781</v>
       </c>
       <c r="BU51" s="63">
-        <f t="shared" si="89"/>
-        <v>7078.2800288951003</v>
+        <f t="shared" si="101"/>
+        <v>7957.147943105505</v>
       </c>
       <c r="BV51" s="63">
-        <f t="shared" ref="BV51" si="90">BV45-SUM(BV46:BV50)</f>
-        <v>7388.3419485992417</v>
+        <f t="shared" ref="BV51" si="102">BV45-SUM(BV46:BV50)</f>
+        <v>8416.2007239879422</v>
       </c>
     </row>
     <row r="52" spans="2:131">
@@ -24753,68 +24750,68 @@
         <v>-92</v>
       </c>
       <c r="BG52" s="1">
-        <f>SUM(C52:F52)</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="BH52" s="1">
-        <f>SUM(G52:J52)</f>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="BI52" s="1">
-        <f>SUM(K52:N52)</f>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="BJ52" s="1">
-        <f>SUM(O52:R52)</f>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="BK52" s="1">
-        <f>SUM(S52:V52)</f>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="BL52" s="1">
-        <f>SUM(W52:Z52)</f>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="BM52" s="1">
-        <f>SUM(AA52:AD52)</f>
+        <f t="shared" si="78"/>
         <v>-336</v>
       </c>
       <c r="BN52" s="1">
-        <f>SUM(AE52:AH52)</f>
+        <f t="shared" si="79"/>
         <v>-318</v>
       </c>
       <c r="BO52" s="1">
-        <f>SUM(AI52:AL52)</f>
+        <f t="shared" si="80"/>
         <v>-515</v>
       </c>
       <c r="BP52" s="1">
-        <f>SUM(AM52:AP52)</f>
+        <f t="shared" si="81"/>
         <v>-412</v>
       </c>
       <c r="BQ52" s="1">
-        <f>SUM(AQ52:AT52)</f>
+        <f t="shared" si="84"/>
         <v>-402</v>
       </c>
       <c r="BR52" s="63">
         <f>-BQ69*($CA$71)</f>
-        <v>-140.84299999999999</v>
+        <v>-146.38800000000001</v>
       </c>
       <c r="BS52" s="63">
         <f>-BR69*($CA$71)</f>
-        <v>-413.0182828724374</v>
+        <v>-455.32395434855994</v>
       </c>
       <c r="BT52" s="63">
         <f>-BS69*($CA$71)</f>
-        <v>-722.29399040924011</v>
+        <v>-814.67956496976262</v>
       </c>
       <c r="BU52" s="63">
         <f>-BT69*($CA$71)</f>
-        <v>-1071.2582614952505</v>
+        <v>-1221.8129444399235</v>
       </c>
       <c r="BV52" s="63">
         <f>-BU69*($CA$71)</f>
-        <v>-1457.2972119744593</v>
+        <v>-1678.0832108401773</v>
       </c>
     </row>
     <row r="53" spans="2:131">
@@ -24965,67 +24962,67 @@
         <v>181</v>
       </c>
       <c r="BG53" s="1">
-        <f>SUM(C53:F53)</f>
+        <f t="shared" si="72"/>
         <v>-280</v>
       </c>
       <c r="BH53" s="1">
-        <f>SUM(G53:J53)</f>
+        <f t="shared" si="73"/>
         <v>-1025</v>
       </c>
       <c r="BI53" s="1">
-        <f>SUM(K53:N53)</f>
+        <f t="shared" si="74"/>
         <v>-781</v>
       </c>
       <c r="BJ53" s="1">
-        <f>SUM(O53:R53)</f>
+        <f t="shared" si="75"/>
         <v>-965</v>
       </c>
       <c r="BK53" s="1">
-        <f>SUM(S53:V53)</f>
+        <f t="shared" si="76"/>
         <v>-1071</v>
       </c>
       <c r="BL53" s="1">
-        <f>SUM(W53:Z53)</f>
+        <f t="shared" si="77"/>
         <v>-736</v>
       </c>
       <c r="BM53" s="1">
-        <f>SUM(AA53:AD53)</f>
+        <f t="shared" si="78"/>
         <v>925</v>
       </c>
       <c r="BN53" s="1">
-        <f>SUM(AE53:AH53)</f>
+        <f t="shared" si="79"/>
         <v>553</v>
       </c>
       <c r="BO53" s="1">
-        <f>SUM(AI53:AL53)</f>
+        <f t="shared" si="80"/>
         <v>636</v>
       </c>
       <c r="BP53" s="1">
-        <f>SUM(AM53:AP53)</f>
+        <f t="shared" si="81"/>
         <v>719</v>
       </c>
       <c r="BQ53" s="1">
-        <f>SUM(AQ53:AT53)</f>
+        <f t="shared" si="84"/>
         <v>729</v>
       </c>
       <c r="BR53" s="63">
-        <f t="shared" ref="BR53:BV53" si="91">BQ53*0.95</f>
+        <f t="shared" ref="BR53:BV53" si="103">BQ53*0.95</f>
         <v>692.55</v>
       </c>
       <c r="BS53" s="63">
-        <f t="shared" si="91"/>
+        <f t="shared" si="103"/>
         <v>657.9224999999999</v>
       </c>
       <c r="BT53" s="63">
-        <f t="shared" si="91"/>
+        <f t="shared" si="103"/>
         <v>625.02637499999992</v>
       </c>
       <c r="BU53" s="63">
-        <f t="shared" si="91"/>
+        <f t="shared" si="103"/>
         <v>593.77505624999992</v>
       </c>
       <c r="BV53" s="63">
-        <f t="shared" si="91"/>
+        <f t="shared" si="103"/>
         <v>564.08630343749985</v>
       </c>
     </row>
@@ -25050,155 +25047,155 @@
         <v>187</v>
       </c>
       <c r="G54" s="1">
-        <f t="shared" ref="G54:Z54" si="92">G51+G53</f>
+        <f t="shared" ref="G54:Z54" si="104">G51+G53</f>
         <v>940</v>
       </c>
       <c r="H54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>1083</v>
       </c>
       <c r="I54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>1179</v>
       </c>
       <c r="J54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>1134</v>
       </c>
       <c r="K54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>988</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>1212</v>
       </c>
       <c r="M54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>967</v>
       </c>
       <c r="N54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>1435</v>
       </c>
       <c r="O54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>1195</v>
       </c>
       <c r="P54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>1728</v>
       </c>
       <c r="Q54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>1027</v>
       </c>
       <c r="R54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>1725</v>
       </c>
       <c r="S54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>1180</v>
       </c>
       <c r="T54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>1355</v>
       </c>
       <c r="U54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>1370</v>
       </c>
       <c r="V54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>1292</v>
       </c>
       <c r="W54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>977</v>
       </c>
       <c r="X54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>1294</v>
       </c>
       <c r="Y54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>1579</v>
       </c>
       <c r="Z54" s="1">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>205</v>
       </c>
       <c r="AA54" s="1">
-        <f t="shared" ref="AA54:AR54" si="93">AA51-SUM(AA52:AA53)</f>
+        <f t="shared" ref="AA54:AR54" si="105">AA51-SUM(AA52:AA53)</f>
         <v>584</v>
       </c>
       <c r="AB54" s="1">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>525</v>
       </c>
       <c r="AC54" s="1">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>1220</v>
       </c>
       <c r="AD54" s="1">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>1571</v>
       </c>
       <c r="AE54" s="1">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>833</v>
       </c>
       <c r="AF54" s="1">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>1493</v>
       </c>
       <c r="AG54" s="1">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>1589</v>
       </c>
       <c r="AH54" s="1">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>1603</v>
       </c>
       <c r="AI54" s="1">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>1044</v>
       </c>
       <c r="AJ54" s="1">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>1395</v>
       </c>
       <c r="AK54" s="1">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>1375</v>
       </c>
       <c r="AL54" s="1">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>1550</v>
       </c>
       <c r="AM54" s="1">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>1196</v>
       </c>
       <c r="AN54" s="1">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>1313</v>
       </c>
       <c r="AO54" s="1">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>1472</v>
       </c>
       <c r="AP54" s="1">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>856</v>
       </c>
       <c r="AQ54" s="1">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>1268</v>
       </c>
       <c r="AR54" s="1">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>1559</v>
       </c>
       <c r="AS54" s="1">
@@ -25206,7 +25203,7 @@
         <v>1540</v>
       </c>
       <c r="AT54" s="1">
-        <f t="shared" ref="AT54" si="94">AT51-SUM(AT52:AT53)</f>
+        <f t="shared" ref="AT54" si="106">AT51-SUM(AT52:AT53)</f>
         <v>1261</v>
       </c>
       <c r="AU54" s="1">
@@ -25218,68 +25215,68 @@
         <v>1597</v>
       </c>
       <c r="BG54" s="1">
-        <f>SUM(C54:F54)</f>
+        <f t="shared" si="72"/>
         <v>3486</v>
       </c>
       <c r="BH54" s="1">
-        <f>SUM(G54:J54)</f>
+        <f t="shared" si="73"/>
         <v>4336</v>
       </c>
       <c r="BI54" s="1">
-        <f>SUM(K54:N54)</f>
+        <f t="shared" si="74"/>
         <v>4602</v>
       </c>
       <c r="BJ54" s="1">
-        <f>SUM(O54:R54)</f>
+        <f t="shared" si="75"/>
         <v>5675</v>
       </c>
       <c r="BK54" s="1">
-        <f>SUM(S54:V54)</f>
+        <f t="shared" si="76"/>
         <v>5197</v>
       </c>
       <c r="BL54" s="1">
-        <f>SUM(W54:Z54)</f>
+        <f t="shared" si="77"/>
         <v>4055</v>
       </c>
       <c r="BM54" s="1">
-        <f>SUM(AA54:AD54)</f>
+        <f t="shared" si="78"/>
         <v>3900</v>
       </c>
       <c r="BN54" s="1">
-        <f>SUM(AE54:AH54)</f>
+        <f t="shared" si="79"/>
         <v>5518</v>
       </c>
       <c r="BO54" s="1">
-        <f>SUM(AI54:AL54)</f>
+        <f t="shared" si="80"/>
         <v>5364</v>
       </c>
       <c r="BP54" s="1">
-        <f>SUM(AM54:AP54)</f>
+        <f t="shared" si="81"/>
         <v>4837</v>
       </c>
       <c r="BQ54" s="1">
-        <f>SUM(AQ54:AT54)</f>
+        <f t="shared" si="84"/>
         <v>5628</v>
       </c>
       <c r="BR54" s="63">
-        <f t="shared" ref="BR54:BU54" si="95">BR51-SUM(BR52:BR53)</f>
-        <v>5331.6357124999977</v>
+        <f t="shared" ref="BR54:BU54" si="107">BR51-SUM(BR52:BR53)</f>
+        <v>5818.824435999999</v>
       </c>
       <c r="BS54" s="63">
-        <f t="shared" si="95"/>
-        <v>6056.1426953786859</v>
+        <f t="shared" si="107"/>
+        <v>6765.1530606285587</v>
       </c>
       <c r="BT54" s="63">
-        <f t="shared" si="95"/>
-        <v>6831.2243111890821</v>
+        <f t="shared" si="107"/>
+        <v>7662.319663863841</v>
       </c>
       <c r="BU54" s="63">
-        <f t="shared" si="95"/>
-        <v>7555.7632341403505</v>
+        <f t="shared" si="107"/>
+        <v>8585.1858312954282</v>
       </c>
       <c r="BV54" s="63">
-        <f t="shared" ref="BV54" si="96">BV51-SUM(BV52:BV53)</f>
-        <v>8281.5528571362011</v>
+        <f t="shared" ref="BV54" si="108">BV51-SUM(BV52:BV53)</f>
+        <v>9530.1976313906198</v>
       </c>
     </row>
     <row r="55" spans="2:131">
@@ -25430,68 +25427,68 @@
         <v>215</v>
       </c>
       <c r="BG55" s="1">
-        <f>SUM(C55:F55)</f>
+        <f t="shared" si="72"/>
         <v>811</v>
       </c>
       <c r="BH55" s="1">
-        <f>SUM(G55:J55)</f>
+        <f t="shared" si="73"/>
         <v>798</v>
       </c>
       <c r="BI55" s="1">
-        <f>SUM(K55:N55)</f>
+        <f t="shared" si="74"/>
         <v>578</v>
       </c>
       <c r="BJ55" s="1">
-        <f>SUM(O55:R55)</f>
+        <f t="shared" si="75"/>
         <v>2580</v>
       </c>
       <c r="BK55" s="1">
-        <f>SUM(S55:V55)</f>
+        <f t="shared" si="76"/>
         <v>547</v>
       </c>
       <c r="BL55" s="1">
-        <f>SUM(W55:Z55)</f>
+        <f t="shared" si="77"/>
         <v>-751</v>
       </c>
       <c r="BM55" s="1">
-        <f>SUM(AA55:AD55)</f>
+        <f t="shared" si="78"/>
         <v>265</v>
       </c>
       <c r="BN55" s="1">
-        <f>SUM(AE55:AH55)</f>
+        <f t="shared" si="79"/>
         <v>456</v>
       </c>
       <c r="BO55" s="1">
-        <f>SUM(AI55:AL55)</f>
+        <f t="shared" si="80"/>
         <v>1580</v>
       </c>
       <c r="BP55" s="1">
-        <f>SUM(AM55:AP55)</f>
+        <f t="shared" si="81"/>
         <v>1132</v>
       </c>
       <c r="BQ55" s="1">
-        <f>SUM(AQ55:AT55)</f>
+        <f t="shared" si="84"/>
         <v>936</v>
       </c>
       <c r="BR55" s="63">
-        <f t="shared" ref="BR55:BU55" si="97">BR54*(BR66)</f>
-        <v>1013.0107853749996</v>
+        <f t="shared" ref="BR55:BU55" si="109">BR54*(BR66)</f>
+        <v>1105.5766428399997</v>
       </c>
       <c r="BS55" s="63">
-        <f t="shared" si="97"/>
-        <v>1150.6671121219504</v>
+        <f t="shared" si="109"/>
+        <v>1285.3790815194261</v>
       </c>
       <c r="BT55" s="63">
-        <f t="shared" si="97"/>
-        <v>1297.9326191259256</v>
+        <f t="shared" si="109"/>
+        <v>1455.8407361341299</v>
       </c>
       <c r="BU55" s="63">
-        <f t="shared" si="97"/>
-        <v>1435.5950144866665</v>
+        <f t="shared" si="109"/>
+        <v>1631.1853079461314</v>
       </c>
       <c r="BV55" s="63">
-        <f t="shared" ref="BV55" si="98">BV54*(BV66)</f>
-        <v>1573.4950428558782</v>
+        <f t="shared" ref="BV55" si="110">BV54*(BV66)</f>
+        <v>1810.7375499642178</v>
       </c>
     </row>
     <row r="56" spans="2:131">
@@ -25503,167 +25500,167 @@
         <v>871</v>
       </c>
       <c r="D56" s="1">
-        <f t="shared" ref="D56:Z56" si="99">D54-D55</f>
+        <f t="shared" ref="D56:Z56" si="111">D54-D55</f>
         <v>828</v>
       </c>
       <c r="E56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>977</v>
       </c>
       <c r="F56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>-1</v>
       </c>
       <c r="G56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>820</v>
       </c>
       <c r="H56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>520</v>
       </c>
       <c r="I56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>1095</v>
       </c>
       <c r="J56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>1103</v>
       </c>
       <c r="K56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>929</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>1111</v>
       </c>
       <c r="M56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>820</v>
       </c>
       <c r="N56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>1164</v>
       </c>
       <c r="O56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>1009</v>
       </c>
       <c r="P56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>2013</v>
       </c>
       <c r="Q56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>-1392</v>
       </c>
       <c r="R56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>1465</v>
       </c>
       <c r="S56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>1077</v>
       </c>
       <c r="T56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>1120</v>
       </c>
       <c r="U56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>1271</v>
       </c>
       <c r="V56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>1182</v>
       </c>
       <c r="W56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>877</v>
       </c>
       <c r="X56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>1371</v>
       </c>
       <c r="Y56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>1919</v>
       </c>
       <c r="Z56" s="1">
-        <f t="shared" si="99"/>
+        <f t="shared" si="111"/>
         <v>639</v>
       </c>
       <c r="AA56" s="1">
-        <f t="shared" ref="AA56:AR56" si="100">AA54-AA55</f>
+        <f t="shared" ref="AA56:AR56" si="112">AA54-AA55</f>
         <v>491</v>
       </c>
       <c r="AB56" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="112"/>
         <v>494</v>
       </c>
       <c r="AC56" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="112"/>
         <v>1279</v>
       </c>
       <c r="AD56" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="112"/>
         <v>1371</v>
       </c>
       <c r="AE56" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="112"/>
         <v>769</v>
       </c>
       <c r="AF56" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="112"/>
         <v>1317</v>
       </c>
       <c r="AG56" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="112"/>
         <v>1483</v>
       </c>
       <c r="AH56" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="112"/>
         <v>1493</v>
       </c>
       <c r="AI56" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="112"/>
         <v>931</v>
       </c>
       <c r="AJ56" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="112"/>
         <v>435</v>
       </c>
       <c r="AK56" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="112"/>
         <v>1229</v>
       </c>
       <c r="AL56" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="112"/>
         <v>1189</v>
       </c>
       <c r="AM56" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="112"/>
         <v>796</v>
       </c>
       <c r="AN56" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="112"/>
         <v>911</v>
       </c>
       <c r="AO56" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="112"/>
         <v>1337</v>
       </c>
       <c r="AP56" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="112"/>
         <v>661</v>
       </c>
       <c r="AQ56" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="112"/>
         <v>1049</v>
       </c>
       <c r="AR56" s="1">
-        <f t="shared" si="100"/>
+        <f t="shared" si="112"/>
         <v>1279</v>
       </c>
       <c r="AS56" s="1">
@@ -25671,7 +25668,7 @@
         <v>1303</v>
       </c>
       <c r="AT56" s="1">
-        <f t="shared" ref="AT56" si="101">AT54-AT55</f>
+        <f t="shared" ref="AT56" si="113">AT54-AT55</f>
         <v>1061</v>
       </c>
       <c r="AU56" s="1">
@@ -25683,68 +25680,68 @@
         <v>1382</v>
       </c>
       <c r="BG56" s="1">
-        <f>SUM(C56:F56)</f>
+        <f t="shared" si="72"/>
         <v>2675</v>
       </c>
       <c r="BH56" s="1">
-        <f>SUM(G56:J56)</f>
+        <f t="shared" si="73"/>
         <v>3538</v>
       </c>
       <c r="BI56" s="1">
-        <f>SUM(K56:N56)</f>
+        <f t="shared" si="74"/>
         <v>4024</v>
       </c>
       <c r="BJ56" s="1">
-        <f>SUM(O56:R56)</f>
+        <f t="shared" si="75"/>
         <v>3095</v>
       </c>
       <c r="BK56" s="1">
-        <f>SUM(S56:V56)</f>
+        <f t="shared" si="76"/>
         <v>4650</v>
       </c>
       <c r="BL56" s="1">
-        <f>SUM(W56:Z56)</f>
+        <f t="shared" si="77"/>
         <v>4806</v>
       </c>
       <c r="BM56" s="1">
-        <f>SUM(AA56:AD56)</f>
+        <f t="shared" si="78"/>
         <v>3635</v>
       </c>
       <c r="BN56" s="1">
-        <f>SUM(AE56:AH56)</f>
+        <f t="shared" si="79"/>
         <v>5062</v>
       </c>
       <c r="BO56" s="1">
-        <f>SUM(AI56:AL56)</f>
+        <f t="shared" si="80"/>
         <v>3784</v>
       </c>
       <c r="BP56" s="1">
-        <f>SUM(AM56:AP56)</f>
+        <f t="shared" si="81"/>
         <v>3705</v>
       </c>
       <c r="BQ56" s="1">
-        <f>SUM(AQ56:AT56)</f>
+        <f t="shared" si="84"/>
         <v>4692</v>
       </c>
       <c r="BR56" s="63">
-        <f t="shared" ref="BR56:BU56" si="102">BR54-BR55</f>
-        <v>4318.6249271249981</v>
+        <f t="shared" ref="BR56:BU56" si="114">BR54-BR55</f>
+        <v>4713.2477931599988</v>
       </c>
       <c r="BS56" s="63">
-        <f t="shared" si="102"/>
-        <v>4905.4755832567353</v>
+        <f t="shared" si="114"/>
+        <v>5479.7739791091326</v>
       </c>
       <c r="BT56" s="63">
-        <f t="shared" si="102"/>
-        <v>5533.291692063156</v>
+        <f t="shared" si="114"/>
+        <v>6206.4789277297114</v>
       </c>
       <c r="BU56" s="63">
-        <f t="shared" si="102"/>
-        <v>6120.168219653684</v>
+        <f t="shared" si="114"/>
+        <v>6954.0005233492966</v>
       </c>
       <c r="BV56" s="63">
-        <f t="shared" ref="BV56" si="103">BV54-BV55</f>
-        <v>6708.0578142803224</v>
+        <f t="shared" ref="BV56" si="115">BV54-BV55</f>
+        <v>7719.4600814264022</v>
       </c>
     </row>
     <row r="57" spans="2:131">
@@ -25895,67 +25892,67 @@
         <v>-7</v>
       </c>
       <c r="BG57" s="1">
-        <f>SUM(C57:F57)</f>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="BH57" s="1">
-        <f>SUM(G57:J57)</f>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="BI57" s="1">
-        <f>SUM(K57:N57)</f>
+        <f t="shared" si="74"/>
         <v>4</v>
       </c>
       <c r="BJ57" s="1">
-        <f>SUM(O57:R57)</f>
+        <f t="shared" si="75"/>
         <v>9</v>
       </c>
       <c r="BK57" s="1">
-        <f>SUM(S57:V57)</f>
+        <f t="shared" si="76"/>
         <v>-5</v>
       </c>
       <c r="BL57" s="1">
-        <f>SUM(W57:Z57)</f>
+        <f t="shared" si="77"/>
         <v>-17</v>
       </c>
       <c r="BM57" s="1">
-        <f>SUM(AA57:AD57)</f>
+        <f t="shared" si="78"/>
         <v>-29</v>
       </c>
       <c r="BN57" s="1">
-        <f>SUM(AE57:AH57)</f>
+        <f t="shared" si="79"/>
         <v>-23</v>
       </c>
       <c r="BO57" s="1">
-        <f>SUM(AI57:AL57)</f>
+        <f t="shared" si="80"/>
         <v>-26</v>
       </c>
       <c r="BP57" s="1">
-        <f>SUM(AM57:AP57)</f>
+        <f t="shared" si="81"/>
         <v>-29</v>
       </c>
       <c r="BQ57" s="1">
-        <f>SUM(AQ57:AT57)</f>
+        <f t="shared" si="84"/>
         <v>-30</v>
       </c>
       <c r="BR57" s="63">
-        <f t="shared" ref="BR57:BV57" si="104">BQ57*1.08</f>
+        <f t="shared" ref="BR57:BV57" si="116">BQ57*1.08</f>
         <v>-32.400000000000006</v>
       </c>
       <c r="BS57" s="63">
-        <f t="shared" si="104"/>
+        <f t="shared" si="116"/>
         <v>-34.992000000000012</v>
       </c>
       <c r="BT57" s="63">
-        <f t="shared" si="104"/>
+        <f t="shared" si="116"/>
         <v>-37.791360000000012</v>
       </c>
       <c r="BU57" s="63">
-        <f t="shared" si="104"/>
+        <f t="shared" si="116"/>
         <v>-40.814668800000014</v>
       </c>
       <c r="BV57" s="63">
-        <f t="shared" si="104"/>
+        <f t="shared" si="116"/>
         <v>-44.079842304000017</v>
       </c>
     </row>
@@ -25964,171 +25961,171 @@
         <v>2222</v>
       </c>
       <c r="C58" s="2">
-        <f t="shared" ref="C58" si="105">C56+C57</f>
+        <f t="shared" ref="C58" si="117">C56+C57</f>
         <v>871</v>
       </c>
       <c r="D58" s="2">
-        <f t="shared" ref="D58" si="106">D56+D57</f>
+        <f t="shared" ref="D58" si="118">D56+D57</f>
         <v>828</v>
       </c>
       <c r="E58" s="2">
-        <f t="shared" ref="E58" si="107">E56+E57</f>
+        <f t="shared" ref="E58" si="119">E56+E57</f>
         <v>977</v>
       </c>
       <c r="F58" s="2">
-        <f t="shared" ref="F58" si="108">F56+F57</f>
+        <f t="shared" ref="F58" si="120">F56+F57</f>
         <v>-1</v>
       </c>
       <c r="G58" s="2">
-        <f t="shared" ref="G58" si="109">G56+G57</f>
+        <f t="shared" ref="G58" si="121">G56+G57</f>
         <v>820</v>
       </c>
       <c r="H58" s="2">
-        <f t="shared" ref="H58" si="110">H56+H57</f>
+        <f t="shared" ref="H58" si="122">H56+H57</f>
         <v>520</v>
       </c>
       <c r="I58" s="2">
-        <f t="shared" ref="I58" si="111">I56+I57</f>
+        <f t="shared" ref="I58" si="123">I56+I57</f>
         <v>1095</v>
       </c>
       <c r="J58" s="2">
-        <f t="shared" ref="J58" si="112">J56+J57</f>
+        <f t="shared" ref="J58" si="124">J56+J57</f>
         <v>1103</v>
       </c>
       <c r="K58" s="2">
-        <f t="shared" ref="K58" si="113">K56+K57</f>
+        <f t="shared" ref="K58" si="125">K56+K57</f>
         <v>929</v>
       </c>
       <c r="L58" s="2">
-        <f t="shared" ref="L58" si="114">L56+L57</f>
+        <f t="shared" ref="L58" si="126">L56+L57</f>
         <v>1115</v>
       </c>
       <c r="M58" s="2">
-        <f t="shared" ref="M58" si="115">M56+M57</f>
+        <f t="shared" ref="M58" si="127">M56+M57</f>
         <v>821</v>
       </c>
       <c r="N58" s="2">
-        <f t="shared" ref="N58" si="116">N56+N57</f>
+        <f t="shared" ref="N58" si="128">N56+N57</f>
         <v>1163</v>
       </c>
       <c r="O58" s="2">
-        <f t="shared" ref="O58" si="117">O56+O57</f>
+        <f t="shared" ref="O58" si="129">O56+O57</f>
         <v>1016</v>
       </c>
       <c r="P58" s="2">
-        <f t="shared" ref="P58" si="118">P56+P57</f>
+        <f t="shared" ref="P58" si="130">P56+P57</f>
         <v>2017</v>
       </c>
       <c r="Q58" s="2">
-        <f t="shared" ref="Q58" si="119">Q56+Q57</f>
+        <f t="shared" ref="Q58" si="131">Q56+Q57</f>
         <v>-1389</v>
       </c>
       <c r="R58" s="2">
-        <f t="shared" ref="R58" si="120">R56+R57</f>
+        <f t="shared" ref="R58" si="132">R56+R57</f>
         <v>1460</v>
       </c>
       <c r="S58" s="2">
-        <f t="shared" ref="S58" si="121">S56+S57</f>
+        <f t="shared" ref="S58" si="133">S56+S57</f>
         <v>1075</v>
       </c>
       <c r="T58" s="2">
-        <f t="shared" ref="T58" si="122">T56+T57</f>
+        <f t="shared" ref="T58" si="134">T56+T57</f>
         <v>1125</v>
       </c>
       <c r="U58" s="2">
-        <f t="shared" ref="U58" si="123">U56+U57</f>
+        <f t="shared" ref="U58" si="135">U56+U57</f>
         <v>1273</v>
       </c>
       <c r="V58" s="2">
-        <f t="shared" ref="V58" si="124">V56+V57</f>
+        <f t="shared" ref="V58" si="136">V56+V57</f>
         <v>1172</v>
       </c>
       <c r="W58" s="2">
-        <f t="shared" ref="W58" si="125">W56+W57</f>
+        <f t="shared" ref="W58" si="137">W56+W57</f>
         <v>864</v>
       </c>
       <c r="X58" s="2">
-        <f t="shared" ref="X58" si="126">X56+X57</f>
+        <f t="shared" ref="X58" si="138">X56+X57</f>
         <v>1364</v>
       </c>
       <c r="Y58" s="2">
-        <f t="shared" ref="Y58" si="127">Y56+Y57</f>
+        <f t="shared" ref="Y58" si="139">Y56+Y57</f>
         <v>1915</v>
       </c>
       <c r="Z58" s="2">
-        <f t="shared" ref="Z58" si="128">Z56+Z57</f>
+        <f t="shared" ref="Z58" si="140">Z56+Z57</f>
         <v>646</v>
       </c>
       <c r="AA58" s="2">
-        <f t="shared" ref="AA58:AR58" si="129">AA56+AA57</f>
+        <f t="shared" ref="AA58:AR58" si="141">AA56+AA57</f>
         <v>487</v>
       </c>
       <c r="AB58" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>489</v>
       </c>
       <c r="AC58" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>1270</v>
       </c>
       <c r="AD58" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>1360</v>
       </c>
       <c r="AE58" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>763</v>
       </c>
       <c r="AF58" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>1311</v>
       </c>
       <c r="AG58" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>1480</v>
       </c>
       <c r="AH58" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>1485</v>
       </c>
       <c r="AI58" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>929</v>
       </c>
       <c r="AJ58" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>427</v>
       </c>
       <c r="AK58" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>1222</v>
       </c>
       <c r="AL58" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>1180</v>
       </c>
       <c r="AM58" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>791</v>
       </c>
       <c r="AN58" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>909</v>
       </c>
       <c r="AO58" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>1322</v>
       </c>
       <c r="AP58" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>654</v>
       </c>
       <c r="AQ58" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>1043</v>
       </c>
       <c r="AR58" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="141"/>
         <v>1270</v>
       </c>
       <c r="AS58" s="2">
@@ -26136,7 +26133,7 @@
         <v>1294</v>
       </c>
       <c r="AT58" s="2">
-        <f t="shared" ref="AT58" si="130">AT56+AT57</f>
+        <f t="shared" ref="AT58" si="142">AT56+AT57</f>
         <v>1055</v>
       </c>
       <c r="AU58" s="2">
@@ -26168,288 +26165,288 @@
       <c r="BC58" s="34"/>
       <c r="BD58" s="34"/>
       <c r="BG58" s="2">
-        <f>SUM(C58:F58)</f>
+        <f t="shared" si="72"/>
         <v>2675</v>
       </c>
       <c r="BH58" s="2">
-        <f>SUM(G58:J58)</f>
+        <f t="shared" si="73"/>
         <v>3538</v>
       </c>
       <c r="BI58" s="2">
-        <f>SUM(K58:N58)</f>
+        <f t="shared" si="74"/>
         <v>4028</v>
       </c>
       <c r="BJ58" s="2">
-        <f>SUM(O58:R58)</f>
+        <f t="shared" si="75"/>
         <v>3104</v>
       </c>
       <c r="BK58" s="2">
-        <f>SUM(S58:V58)</f>
+        <f t="shared" si="76"/>
         <v>4645</v>
       </c>
       <c r="BL58" s="2">
-        <f>SUM(W58:Z58)</f>
+        <f t="shared" si="77"/>
         <v>4789</v>
       </c>
       <c r="BM58" s="2">
-        <f>SUM(AA58:AD58)</f>
+        <f t="shared" si="78"/>
         <v>3606</v>
       </c>
       <c r="BN58" s="2">
-        <f>SUM(AE58:AH58)</f>
+        <f t="shared" si="79"/>
         <v>5039</v>
       </c>
       <c r="BO58" s="2">
-        <f>SUM(AI58:AL58)</f>
+        <f t="shared" si="80"/>
         <v>3758</v>
       </c>
       <c r="BP58" s="2">
-        <f>SUM(AM58:AP58)</f>
+        <f t="shared" si="81"/>
         <v>3676</v>
       </c>
       <c r="BQ58" s="2">
-        <f>SUM(AQ58:AT58)</f>
+        <f t="shared" si="84"/>
         <v>4662</v>
       </c>
       <c r="BR58" s="61">
-        <f t="shared" ref="BR58:BU58" si="131">BR56+BR57</f>
-        <v>4286.2249271249984</v>
+        <f t="shared" ref="BR58:BU58" si="143">BR56+BR57</f>
+        <v>4680.8477931599991</v>
       </c>
       <c r="BS58" s="61">
-        <f t="shared" si="131"/>
-        <v>4870.4835832567351</v>
+        <f t="shared" si="143"/>
+        <v>5444.7819791091324</v>
       </c>
       <c r="BT58" s="61">
-        <f t="shared" si="131"/>
-        <v>5495.5003320631558</v>
+        <f t="shared" si="143"/>
+        <v>6168.6875677297112</v>
       </c>
       <c r="BU58" s="61">
-        <f t="shared" si="131"/>
-        <v>6079.3535508536843</v>
+        <f t="shared" si="143"/>
+        <v>6913.1858545492969</v>
       </c>
       <c r="BV58" s="61">
-        <f t="shared" ref="BV58" si="132">BV56+BV57</f>
-        <v>6663.9779719763228</v>
+        <f t="shared" ref="BV58" si="144">BV56+BV57</f>
+        <v>7675.3802391224026</v>
       </c>
       <c r="BW58" s="61">
-        <f t="shared" ref="BW58:DB58" si="133">BV58*(1+$CA$72)</f>
-        <v>6813.9174763457895</v>
+        <f t="shared" ref="BW58:DB58" si="145">BV58*(1+$CA$72)</f>
+        <v>7848.0762945026563</v>
       </c>
       <c r="BX58" s="61">
-        <f t="shared" si="133"/>
-        <v>6967.2306195635692</v>
+        <f t="shared" si="145"/>
+        <v>8024.6580111289659</v>
       </c>
       <c r="BY58" s="61">
-        <f t="shared" si="133"/>
-        <v>7123.9933085037492</v>
+        <f t="shared" si="145"/>
+        <v>8205.2128163793677</v>
       </c>
       <c r="BZ58" s="61">
-        <f t="shared" si="133"/>
-        <v>7284.2831579450831</v>
+        <f t="shared" si="145"/>
+        <v>8389.8301047479035</v>
       </c>
       <c r="CA58" s="61">
-        <f t="shared" si="133"/>
-        <v>7448.1795289988468</v>
+        <f t="shared" si="145"/>
+        <v>8578.6012821047316</v>
       </c>
       <c r="CB58" s="61">
-        <f t="shared" si="133"/>
-        <v>7615.7635684013203</v>
+        <f t="shared" si="145"/>
+        <v>8771.6198109520883</v>
       </c>
       <c r="CC58" s="61">
-        <f t="shared" si="133"/>
-        <v>7787.1182486903499</v>
+        <f t="shared" si="145"/>
+        <v>8968.9812566985092</v>
       </c>
       <c r="CD58" s="61">
-        <f t="shared" si="133"/>
-        <v>7962.3284092858821</v>
+        <f t="shared" si="145"/>
+        <v>9170.783334974225</v>
       </c>
       <c r="CE58" s="61">
-        <f t="shared" si="133"/>
-        <v>8141.4807984948138</v>
+        <f t="shared" si="145"/>
+        <v>9377.1259600111443</v>
       </c>
       <c r="CF58" s="61">
-        <f t="shared" si="133"/>
-        <v>8324.6641164609464</v>
+        <f t="shared" si="145"/>
+        <v>9588.1112941113952</v>
       </c>
       <c r="CG58" s="61">
-        <f t="shared" si="133"/>
-        <v>8511.969059081317</v>
+        <f t="shared" si="145"/>
+        <v>9803.8437982289015</v>
       </c>
       <c r="CH58" s="61">
-        <f t="shared" si="133"/>
-        <v>8703.4883629106462</v>
+        <f t="shared" si="145"/>
+        <v>10024.430283689051</v>
       </c>
       <c r="CI58" s="61">
-        <f t="shared" si="133"/>
-        <v>8899.3168510761352</v>
+        <f t="shared" si="145"/>
+        <v>10249.979965072054</v>
       </c>
       <c r="CJ58" s="61">
-        <f t="shared" si="133"/>
-        <v>9099.5514802253474</v>
+        <f t="shared" si="145"/>
+        <v>10480.604514286175</v>
       </c>
       <c r="CK58" s="61">
-        <f t="shared" si="133"/>
-        <v>9304.291388530417</v>
+        <f t="shared" si="145"/>
+        <v>10716.418115857614</v>
       </c>
       <c r="CL58" s="61">
-        <f t="shared" si="133"/>
-        <v>9513.6379447723502</v>
+        <f t="shared" si="145"/>
+        <v>10957.537523464411</v>
       </c>
       <c r="CM58" s="61">
-        <f t="shared" si="133"/>
-        <v>9727.6947985297284</v>
+        <f t="shared" si="145"/>
+        <v>11204.08211774236</v>
       </c>
       <c r="CN58" s="61">
-        <f t="shared" si="133"/>
-        <v>9946.5679314966474</v>
+        <f t="shared" si="145"/>
+        <v>11456.173965391563</v>
       </c>
       <c r="CO58" s="61">
-        <f t="shared" si="133"/>
-        <v>10170.365709955322</v>
+        <f t="shared" si="145"/>
+        <v>11713.937879612873</v>
       </c>
       <c r="CP58" s="61">
-        <f t="shared" si="133"/>
-        <v>10399.198938429316</v>
+        <f t="shared" si="145"/>
+        <v>11977.501481904163</v>
       </c>
       <c r="CQ58" s="61">
-        <f t="shared" si="133"/>
-        <v>10633.180914543975</v>
+        <f t="shared" si="145"/>
+        <v>12246.995265247006</v>
       </c>
       <c r="CR58" s="61">
-        <f t="shared" si="133"/>
-        <v>10872.427485121214</v>
+        <f t="shared" si="145"/>
+        <v>12522.552658715063</v>
       </c>
       <c r="CS58" s="61">
-        <f t="shared" si="133"/>
-        <v>11117.057103536441</v>
+        <f t="shared" si="145"/>
+        <v>12804.310093536153</v>
       </c>
       <c r="CT58" s="61">
-        <f t="shared" si="133"/>
-        <v>11367.190888366011</v>
+        <f t="shared" si="145"/>
+        <v>13092.407070640716</v>
       </c>
       <c r="CU58" s="61">
-        <f t="shared" si="133"/>
-        <v>11622.952683354246</v>
+        <f t="shared" si="145"/>
+        <v>13386.986229730132</v>
       </c>
       <c r="CV58" s="61">
-        <f t="shared" si="133"/>
-        <v>11884.469118729716</v>
+        <f t="shared" si="145"/>
+        <v>13688.193419899058</v>
       </c>
       <c r="CW58" s="61">
-        <f t="shared" si="133"/>
-        <v>12151.869673901134</v>
+        <f t="shared" si="145"/>
+        <v>13996.177771846787</v>
       </c>
       <c r="CX58" s="61">
-        <f t="shared" si="133"/>
-        <v>12425.286741563908</v>
+        <f t="shared" si="145"/>
+        <v>14311.09177171334</v>
       </c>
       <c r="CY58" s="61">
-        <f t="shared" si="133"/>
-        <v>12704.855693249096</v>
+        <f t="shared" si="145"/>
+        <v>14633.09133657689</v>
       </c>
       <c r="CZ58" s="61">
-        <f t="shared" si="133"/>
-        <v>12990.7149463472</v>
+        <f t="shared" si="145"/>
+        <v>14962.335891649869</v>
       </c>
       <c r="DA58" s="61">
-        <f t="shared" si="133"/>
-        <v>13283.006032640011</v>
+        <f t="shared" si="145"/>
+        <v>15298.988449211991</v>
       </c>
       <c r="DB58" s="61">
-        <f t="shared" si="133"/>
-        <v>13581.87366837441</v>
+        <f t="shared" si="145"/>
+        <v>15643.21568931926</v>
       </c>
       <c r="DC58" s="61">
-        <f t="shared" ref="DC58:DY58" si="134">DB58*(1+$CA$72)</f>
-        <v>13887.465825912834</v>
+        <f t="shared" ref="DC58:DY58" si="146">DB58*(1+$CA$72)</f>
+        <v>15995.188042328944</v>
       </c>
       <c r="DD58" s="61">
-        <f t="shared" si="134"/>
-        <v>14199.933806995872</v>
+        <f t="shared" si="146"/>
+        <v>16355.079773281344</v>
       </c>
       <c r="DE58" s="61">
-        <f t="shared" si="134"/>
-        <v>14519.432317653278</v>
+        <f t="shared" si="146"/>
+        <v>16723.069068180175</v>
       </c>
       <c r="DF58" s="61">
-        <f t="shared" si="134"/>
-        <v>14846.119544800476</v>
+        <f t="shared" si="146"/>
+        <v>17099.338122214227</v>
       </c>
       <c r="DG58" s="61">
-        <f t="shared" si="134"/>
-        <v>15180.157234558486</v>
+        <f t="shared" si="146"/>
+        <v>17484.073229964048</v>
       </c>
       <c r="DH58" s="61">
-        <f t="shared" si="134"/>
-        <v>15521.710772336051</v>
+        <f t="shared" si="146"/>
+        <v>17877.464877638238</v>
       </c>
       <c r="DI58" s="61">
-        <f t="shared" si="134"/>
-        <v>15870.949264713612</v>
+        <f t="shared" si="146"/>
+        <v>18279.707837385096</v>
       </c>
       <c r="DJ58" s="61">
-        <f t="shared" si="134"/>
-        <v>16228.045623169668</v>
+        <f t="shared" si="146"/>
+        <v>18691.001263726259</v>
       </c>
       <c r="DK58" s="61">
-        <f t="shared" si="134"/>
-        <v>16593.176649690984</v>
+        <f t="shared" si="146"/>
+        <v>19111.548792160098</v>
       </c>
       <c r="DL58" s="61">
-        <f t="shared" si="134"/>
-        <v>16966.523124309031</v>
+        <f t="shared" si="146"/>
+        <v>19541.558639983701</v>
       </c>
       <c r="DM58" s="61">
-        <f t="shared" si="134"/>
-        <v>17348.269894605983</v>
+        <f t="shared" si="146"/>
+        <v>19981.243709383332</v>
       </c>
       <c r="DN58" s="61">
-        <f t="shared" si="134"/>
-        <v>17738.605967234616</v>
+        <f t="shared" si="146"/>
+        <v>20430.821692844456</v>
       </c>
       <c r="DO58" s="61">
-        <f t="shared" si="134"/>
-        <v>18137.724601497393</v>
+        <f t="shared" si="146"/>
+        <v>20890.515180933457</v>
       </c>
       <c r="DP58" s="61">
-        <f t="shared" si="134"/>
-        <v>18545.823405031086</v>
+        <f t="shared" si="146"/>
+        <v>21360.551772504459</v>
       </c>
       <c r="DQ58" s="61">
-        <f t="shared" si="134"/>
-        <v>18963.104431644286</v>
+        <f t="shared" si="146"/>
+        <v>21841.16418738581</v>
       </c>
       <c r="DR58" s="61">
-        <f t="shared" si="134"/>
-        <v>19389.77428135628</v>
+        <f t="shared" si="146"/>
+        <v>22332.590381601989</v>
       </c>
       <c r="DS58" s="61">
-        <f t="shared" si="134"/>
-        <v>19826.044202686797</v>
+        <f t="shared" si="146"/>
+        <v>22835.073665188032</v>
       </c>
       <c r="DT58" s="61">
-        <f t="shared" si="134"/>
-        <v>20272.13019724725</v>
+        <f t="shared" si="146"/>
+        <v>23348.862822654763</v>
       </c>
       <c r="DU58" s="61">
-        <f t="shared" si="134"/>
-        <v>20728.253126685311</v>
+        <f t="shared" si="146"/>
+        <v>23874.212236164494</v>
       </c>
       <c r="DV58" s="61">
-        <f t="shared" si="134"/>
-        <v>21194.638822035729</v>
+        <f t="shared" si="146"/>
+        <v>24411.382011478196</v>
       </c>
       <c r="DW58" s="61">
-        <f t="shared" si="134"/>
-        <v>21671.518195531531</v>
+        <f t="shared" si="146"/>
+        <v>24960.638106736453</v>
       </c>
       <c r="DX58" s="61">
-        <f t="shared" si="134"/>
-        <v>22159.127354930988</v>
+        <f t="shared" si="146"/>
+        <v>25522.252464138022</v>
       </c>
       <c r="DY58" s="61">
-        <f t="shared" si="134"/>
-        <v>22657.707720416933</v>
+        <f t="shared" si="146"/>
+        <v>26096.503144581126</v>
       </c>
       <c r="DZ58" s="60"/>
       <c r="EA58" s="60"/>
@@ -26597,27 +26594,27 @@
         <v>1282</v>
       </c>
       <c r="BG59" s="1">
-        <f>SUM(C59:F59)</f>
+        <f t="shared" si="72"/>
         <v>4055</v>
       </c>
       <c r="BH59" s="1">
-        <f>SUM(G59:J59)</f>
+        <f t="shared" si="73"/>
         <v>5648</v>
       </c>
       <c r="BI59" s="1">
-        <f>SUM(K59:N59)</f>
+        <f t="shared" si="74"/>
         <v>5523</v>
       </c>
       <c r="BJ59" s="1">
-        <f>SUM(O59:R59)</f>
+        <f t="shared" si="75"/>
         <v>5428</v>
       </c>
       <c r="BK59" s="1">
-        <f>SUM(S59:V59)</f>
+        <f t="shared" si="76"/>
         <v>5391</v>
       </c>
       <c r="BL59" s="1">
-        <f>SUM(W59:Z59)</f>
+        <f t="shared" si="77"/>
         <v>5364</v>
       </c>
       <c r="BM59" s="43">
@@ -26661,171 +26658,171 @@
         <v>2223</v>
       </c>
       <c r="C60" s="40">
-        <f t="shared" ref="C60" si="135">C58/C59</f>
+        <f t="shared" ref="C60" si="147">C58/C59</f>
         <v>0.87713997985901304</v>
       </c>
       <c r="D60" s="40">
-        <f t="shared" ref="D60" si="136">D58/D59</f>
+        <f t="shared" ref="D60" si="148">D58/D59</f>
         <v>0.84317718940936859</v>
       </c>
       <c r="E60" s="40">
-        <f t="shared" ref="E60" si="137">E58/E59</f>
+        <f t="shared" ref="E60" si="149">E58/E59</f>
         <v>0.99288617886178865</v>
       </c>
       <c r="F60" s="40">
-        <f t="shared" ref="F60" si="138">F58/F59</f>
+        <f t="shared" ref="F60" si="150">F58/F59</f>
         <v>-9.1240875912408756E-4</v>
       </c>
       <c r="G60" s="40">
-        <f t="shared" ref="G60" si="139">G58/G59</f>
+        <f t="shared" ref="G60" si="151">G58/G59</f>
         <v>0.57827926657263751</v>
       </c>
       <c r="H60" s="40">
-        <f t="shared" ref="H60" si="140">H58/H59</f>
+        <f t="shared" ref="H60" si="152">H58/H59</f>
         <v>0.36801132342533616</v>
       </c>
       <c r="I60" s="40">
-        <f t="shared" ref="I60" si="141">I58/I59</f>
+        <f t="shared" ref="I60" si="153">I58/I59</f>
         <v>0.7782515991471215</v>
       </c>
       <c r="J60" s="40">
-        <f t="shared" ref="J60" si="142">J58/J59</f>
+        <f t="shared" ref="J60" si="154">J58/J59</f>
         <v>0.78226950354609925</v>
       </c>
       <c r="K60" s="40">
-        <f t="shared" ref="K60" si="143">K58/K59</f>
+        <f t="shared" ref="K60" si="155">K58/K59</f>
         <v>0.66738505747126442</v>
       </c>
       <c r="L60" s="40">
-        <f t="shared" ref="L60" si="144">L58/L59</f>
+        <f t="shared" ref="L60" si="156">L58/L59</f>
         <v>0.80797101449275366</v>
       </c>
       <c r="M60" s="40">
-        <f t="shared" ref="M60" si="145">M58/M59</f>
+        <f t="shared" ref="M60" si="157">M58/M59</f>
         <v>0.59839650145772594</v>
       </c>
       <c r="N60" s="40">
-        <f t="shared" ref="N60" si="146">N58/N59</f>
+        <f t="shared" ref="N60" si="158">N58/N59</f>
         <v>0.84336475707034086</v>
       </c>
       <c r="O60" s="40">
-        <f t="shared" ref="O60" si="147">O58/O59</f>
+        <f t="shared" ref="O60" si="159">O58/O59</f>
         <v>0.74596182085168872</v>
       </c>
       <c r="P60" s="40">
-        <f t="shared" ref="P60" si="148">P58/P59</f>
+        <f t="shared" ref="P60" si="160">P58/P59</f>
         <v>1.4885608856088561</v>
       </c>
       <c r="Q60" s="40">
-        <f t="shared" ref="Q60" si="149">Q58/Q59</f>
+        <f t="shared" ref="Q60" si="161">Q58/Q59</f>
         <v>-1.0258493353028064</v>
       </c>
       <c r="R60" s="40">
-        <f t="shared" ref="R60" si="150">R58/R59</f>
+        <f t="shared" ref="R60" si="162">R58/R59</f>
         <v>1.0759027266028003</v>
       </c>
       <c r="S60" s="40">
-        <f t="shared" ref="S60" si="151">S58/S59</f>
+        <f t="shared" ref="S60" si="163">S58/S59</f>
         <v>0.79453067257945309</v>
       </c>
       <c r="T60" s="40">
-        <f t="shared" ref="T60" si="152">T58/T59</f>
+        <f t="shared" ref="T60" si="164">T58/T59</f>
         <v>0.83395107487027431</v>
       </c>
       <c r="U60" s="40">
-        <f t="shared" ref="U60:AR60" si="153">U58/U59</f>
+        <f t="shared" ref="U60:AR60" si="165">U58/U59</f>
         <v>0.94787788533134776</v>
       </c>
       <c r="V60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>0.87072808320950967</v>
       </c>
       <c r="W60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>0.64429530201342278</v>
       </c>
       <c r="X60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>1.0171513795674869</v>
       </c>
       <c r="Y60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>1.4280387770320657</v>
       </c>
       <c r="Z60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>0.48173005219985088</v>
       </c>
       <c r="AA60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>0.36291825024219387</v>
       </c>
       <c r="AB60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>0.36373103243082411</v>
       </c>
       <c r="AC60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>0.94325609031491375</v>
       </c>
       <c r="AD60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>1.0112276005650978</v>
       </c>
       <c r="AE60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>0.56749721085905536</v>
       </c>
       <c r="AF60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>0.97464872500185862</v>
       </c>
       <c r="AG60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>1.1014363325146981</v>
       </c>
       <c r="AH60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>1.1062276519666268</v>
       </c>
       <c r="AI60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>0.69881149390702568</v>
       </c>
       <c r="AJ60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>0.32119753272152851</v>
       </c>
       <c r="AK60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>0.91865884829348965</v>
       </c>
       <c r="AL60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>0.88735148142577835</v>
       </c>
       <c r="AM60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>0.59451334084930474</v>
       </c>
       <c r="AN60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>0.68335588633288225</v>
       </c>
       <c r="AO60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>0.99420922012484014</v>
       </c>
       <c r="AP60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>0.49258115538148678</v>
       </c>
       <c r="AQ60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>0.80646408412587955</v>
       </c>
       <c r="AR60" s="40">
-        <f t="shared" si="153"/>
+        <f t="shared" si="165"/>
         <v>0.99033063006862121</v>
       </c>
       <c r="AS60" s="40">
@@ -26833,7 +26830,7 @@
         <v>1.0090455396132252</v>
       </c>
       <c r="AT60" s="40">
-        <f t="shared" ref="AT60" si="154">AT58/AT59</f>
+        <f t="shared" ref="AT60" si="166">AT58/AT59</f>
         <v>0.82062850031113888</v>
       </c>
       <c r="AU60" s="40">
@@ -26865,39 +26862,39 @@
       <c r="BC60" s="56"/>
       <c r="BD60" s="56"/>
       <c r="BG60" s="40">
-        <f>SUM(C60:F60)</f>
+        <f t="shared" si="72"/>
         <v>2.7122909393710462</v>
       </c>
       <c r="BH60" s="40">
-        <f>SUM(G60:J60)</f>
+        <f t="shared" si="73"/>
         <v>2.5068116926911945</v>
       </c>
       <c r="BI60" s="40">
-        <f>SUM(K60:N60)</f>
+        <f t="shared" si="74"/>
         <v>2.9171173304920845</v>
       </c>
       <c r="BJ60" s="40">
-        <f>SUM(O60:R60)</f>
+        <f t="shared" si="75"/>
         <v>2.2845760977605387</v>
       </c>
       <c r="BK60" s="40">
-        <f>SUM(S60:V60)</f>
+        <f t="shared" si="76"/>
         <v>3.4470877159905848</v>
       </c>
       <c r="BL60" s="40">
-        <f>SUM(W60:Z60)</f>
+        <f t="shared" si="77"/>
         <v>3.5712155108128263</v>
       </c>
       <c r="BM60" s="40">
-        <f t="shared" ref="BM60:BO60" si="155">BM58/BM59</f>
+        <f t="shared" ref="BM60:BO60" si="167">BM58/BM59</f>
         <v>2.6872345182204334</v>
       </c>
       <c r="BN60" s="40">
-        <f t="shared" si="155"/>
+        <f t="shared" si="167"/>
         <v>3.7537246722288438</v>
       </c>
       <c r="BO60" s="40">
-        <f t="shared" si="155"/>
+        <f t="shared" si="167"/>
         <v>2.8259888705068432</v>
       </c>
       <c r="BP60" s="40">
@@ -26909,24 +26906,24 @@
         <v>3.6264687541188647</v>
       </c>
       <c r="BR60" s="64">
-        <f t="shared" ref="BR60:BU60" si="156">BR58/BR59</f>
-        <v>3.2275790113893059</v>
+        <f t="shared" ref="BR60:BU60" si="168">BR58/BR59</f>
+        <v>3.5247347840060232</v>
       </c>
       <c r="BS60" s="64">
-        <f t="shared" si="156"/>
-        <v>3.667532818717421</v>
+        <f t="shared" si="168"/>
+        <v>4.0999864300520574</v>
       </c>
       <c r="BT60" s="64">
-        <f t="shared" si="156"/>
-        <v>4.138177960890931</v>
+        <f t="shared" si="168"/>
+        <v>4.6450960600374334</v>
       </c>
       <c r="BU60" s="64">
-        <f t="shared" si="156"/>
-        <v>4.5778264690163288</v>
+        <f t="shared" si="168"/>
+        <v>5.2057122398714588</v>
       </c>
       <c r="BV60" s="64">
-        <f t="shared" ref="BV60" si="157">BV58/BV59</f>
-        <v>5.0180557017893994</v>
+        <f t="shared" ref="BV60" si="169">BV58/BV59</f>
+        <v>5.7796537945198816</v>
       </c>
     </row>
     <row r="62" spans="2:131">
@@ -26938,243 +26935,243 @@
         <v>0.74139948513924647</v>
       </c>
       <c r="D62" s="44">
-        <f t="shared" ref="D62:AS62" si="158">D45/D43</f>
+        <f t="shared" ref="D62:AS62" si="170">D45/D43</f>
         <v>0.73843334860284016</v>
       </c>
       <c r="E62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.73876794812413149</v>
       </c>
       <c r="F62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.59830230010952901</v>
       </c>
       <c r="G62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.66235908715974701</v>
       </c>
       <c r="H62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.69084726551430997</v>
       </c>
       <c r="I62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.69123161234496688</v>
       </c>
       <c r="J62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.68772300779701334</v>
       </c>
       <c r="K62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.68448227742115542</v>
       </c>
       <c r="L62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.68332198774676656</v>
       </c>
       <c r="M62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.68858986681312651</v>
       </c>
       <c r="N62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.69188984335522996</v>
       </c>
       <c r="O62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.68173207036535854</v>
       </c>
       <c r="P62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.6988652482269504</v>
       </c>
       <c r="Q62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.70226625050888858</v>
       </c>
       <c r="R62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.70555009823182713</v>
       </c>
       <c r="S62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.70151679306608883</v>
       </c>
       <c r="T62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.70552065231920869</v>
       </c>
       <c r="U62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.6998409753511794</v>
       </c>
       <c r="V62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.69518782224404618</v>
       </c>
       <c r="W62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.68423862271453362</v>
       </c>
       <c r="X62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.68933298728263692</v>
       </c>
       <c r="Y62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.68899831540754175</v>
       </c>
       <c r="Z62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.62247790561947636</v>
       </c>
       <c r="AA62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.6150299677270632</v>
       </c>
       <c r="AB62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.64626650974238264</v>
       </c>
       <c r="AC62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.66289389067524118</v>
       </c>
       <c r="AD62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.67611138251099168</v>
       </c>
       <c r="AE62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.67472142231125576</v>
       </c>
       <c r="AF62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.6817892188097362</v>
       </c>
       <c r="AG62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.68324101507149293</v>
       </c>
       <c r="AH62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.6796884658177772</v>
       </c>
       <c r="AI62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.65866232532899205</v>
       </c>
       <c r="AJ62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.66578773895847065</v>
       </c>
       <c r="AK62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.65199948233467064</v>
       </c>
       <c r="AL62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.65133426966292129</v>
       </c>
       <c r="AM62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.6587899246948844</v>
       </c>
       <c r="AN62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.65418336673346689</v>
       </c>
       <c r="AO62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.6560761528000989</v>
       </c>
       <c r="AP62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.6454767726161369</v>
       </c>
       <c r="AQ62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.65116866708780796</v>
       </c>
       <c r="AR62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.6494109246697608</v>
       </c>
       <c r="AS62" s="44">
-        <f t="shared" si="158"/>
+        <f t="shared" si="170"/>
         <v>0.66485769416304874</v>
       </c>
       <c r="AT62" s="44">
-        <f t="shared" ref="AT62:AU62" si="159">AT45/AT43</f>
+        <f t="shared" ref="AT62:AU62" si="171">AT45/AT43</f>
         <v>0.6475070028011205</v>
       </c>
       <c r="AU62" s="44">
-        <f t="shared" si="159"/>
+        <f t="shared" si="171"/>
         <v>0.65015155047796691</v>
       </c>
       <c r="AV62" s="44">
-        <f t="shared" ref="AV62" si="160">AV45/AV43</f>
+        <f t="shared" ref="AV62" si="172">AV45/AV43</f>
         <v>0.65840865974779605</v>
       </c>
       <c r="BG62" s="44">
-        <f t="shared" ref="BG62:BL62" si="161">BG45/BG43</f>
+        <f t="shared" ref="BG62:BL62" si="173">BG45/BG43</f>
         <v>0.68861359261635657</v>
       </c>
       <c r="BH62" s="44">
-        <f t="shared" si="161"/>
+        <f t="shared" si="173"/>
         <v>0.68293275066763781</v>
       </c>
       <c r="BI62" s="44">
-        <f t="shared" si="161"/>
+        <f t="shared" si="173"/>
         <v>0.68717603500504876</v>
       </c>
       <c r="BJ62" s="44">
-        <f t="shared" si="161"/>
+        <f t="shared" si="173"/>
         <v>0.69729242479885156</v>
       </c>
       <c r="BK62" s="44">
-        <f t="shared" si="161"/>
+        <f t="shared" si="173"/>
         <v>0.70039598128088487</v>
       </c>
       <c r="BL62" s="44">
-        <f t="shared" si="161"/>
+        <f t="shared" si="173"/>
         <v>0.67405665271677095</v>
       </c>
       <c r="BM62" s="44">
-        <f t="shared" ref="BM62:BO62" si="162">BM45/BM43</f>
+        <f t="shared" ref="BM62:BO62" si="174">BM45/BM43</f>
         <v>0.6519241624331773</v>
       </c>
       <c r="BN62" s="44">
-        <f t="shared" si="162"/>
+        <f t="shared" si="174"/>
         <v>0.67982705295714196</v>
       </c>
       <c r="BO62" s="44">
-        <f t="shared" si="162"/>
+        <f t="shared" si="174"/>
         <v>0.65673936016908441</v>
       </c>
       <c r="BP62" s="44">
-        <f t="shared" ref="BP62:BQ62" si="163">BP45/BP43</f>
+        <f t="shared" ref="BP62:BQ62" si="175">BP45/BP43</f>
         <v>0.65344209615622295</v>
       </c>
       <c r="BQ62" s="44">
-        <f t="shared" si="163"/>
+        <f t="shared" si="175"/>
         <v>0.6531385120023856</v>
       </c>
       <c r="BR62" s="62">
-        <v>0.65</v>
+        <v>0.65200000000000002</v>
       </c>
       <c r="BS62" s="62">
-        <v>0.65200000000000002</v>
+        <v>0.65400000000000003</v>
       </c>
       <c r="BT62" s="62">
-        <v>0.65300000000000002</v>
+        <v>0.65600000000000003</v>
       </c>
       <c r="BU62" s="62">
-        <v>0.65400000000000003</v>
+        <v>0.65800000000000003</v>
       </c>
       <c r="BV62" s="62">
-        <v>0.65500000000000003</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="63" spans="2:131">
@@ -27182,211 +27179,211 @@
         <v>95</v>
       </c>
       <c r="C63" s="44">
-        <f t="shared" ref="C63:AS63" si="164">C46/C43</f>
+        <f t="shared" ref="C63:AS63" si="176">C46/C43</f>
         <v>8.5420079569389185E-2</v>
       </c>
       <c r="D63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>8.5661933119560232E-2</v>
       </c>
       <c r="E63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>8.6382584529874948E-2</v>
       </c>
       <c r="F63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.2289156626506021E-2</v>
       </c>
       <c r="G63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.6711575474291999E-2</v>
       </c>
       <c r="H63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.7217342023236046E-2</v>
       </c>
       <c r="I63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.8742428612633406E-2</v>
       </c>
       <c r="J63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.598784194528875E-2</v>
       </c>
       <c r="K63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.7588612894222725E-2</v>
       </c>
       <c r="L63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.5425459496255953E-2</v>
       </c>
       <c r="M63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.2772209254428122E-2</v>
       </c>
       <c r="N63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>6.985851440121274E-2</v>
       </c>
       <c r="O63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.4289580514208392E-2</v>
       </c>
       <c r="P63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.886524822695036E-2</v>
       </c>
       <c r="Q63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.5858325417288638E-2</v>
       </c>
       <c r="R63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.269155206286837E-2</v>
       </c>
       <c r="S63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.9225352112676062E-2</v>
       </c>
       <c r="T63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.8866461702980881E-2</v>
       </c>
       <c r="U63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.4344023323615158E-2</v>
       </c>
       <c r="V63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.2919224159096491E-2</v>
       </c>
       <c r="W63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.833978379821166E-2</v>
       </c>
       <c r="X63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.8250713729561383E-2</v>
       </c>
       <c r="Y63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.42516521964494E-2</v>
       </c>
       <c r="Z63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>9.4714023678505926E-2</v>
       </c>
       <c r="AA63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>9.5435684647302899E-2</v>
       </c>
       <c r="AB63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>8.3562181247548065E-2</v>
       </c>
       <c r="AC63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.7299035369774921E-2</v>
       </c>
       <c r="AD63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.7186126038104541E-2</v>
       </c>
       <c r="AE63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>9.3902591711531244E-2</v>
       </c>
       <c r="AF63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>8.6147572320632082E-2</v>
       </c>
       <c r="AG63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>8.6049207780497225E-2</v>
       </c>
       <c r="AH63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>8.0603288416367908E-2</v>
       </c>
       <c r="AI63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>9.3881427214760546E-2</v>
       </c>
       <c r="AJ63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>8.9123269611074488E-2</v>
       </c>
       <c r="AK63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>8.9038436650705322E-2</v>
       </c>
       <c r="AL63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.4906367041198504E-2</v>
       </c>
       <c r="AM63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>8.6730719293689945E-2</v>
       </c>
       <c r="AN63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>8.7424849699398802E-2</v>
       </c>
       <c r="AO63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>8.5919149462232655E-2</v>
       </c>
       <c r="AP63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>7.8472464780533241E-2</v>
       </c>
       <c r="AQ63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>8.54074542008844E-2</v>
       </c>
       <c r="AR63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>8.2946566702368205E-2</v>
       </c>
       <c r="AS63" s="44">
-        <f t="shared" si="164"/>
+        <f t="shared" si="176"/>
         <v>8.1403762662807522E-2</v>
       </c>
       <c r="AT63" s="44">
-        <f t="shared" ref="AT63:AU63" si="165">AT46/AT43</f>
+        <f t="shared" ref="AT63:AU63" si="177">AT46/AT43</f>
         <v>7.6638655462184874E-2</v>
       </c>
       <c r="AU63" s="44">
-        <f t="shared" si="165"/>
+        <f t="shared" si="177"/>
         <v>8.4635113079972027E-2</v>
       </c>
       <c r="AV63" s="44">
-        <f t="shared" ref="AV63" si="166">AV46/AV43</f>
+        <f t="shared" ref="AV63" si="178">AV46/AV43</f>
         <v>8.4142394822006472E-2</v>
       </c>
       <c r="BG63" s="44">
-        <f t="shared" ref="BG63:BL63" si="167">BG46/BG43</f>
+        <f t="shared" ref="BG63:BL63" si="179">BG46/BG43</f>
         <v>8.094368491189971E-2</v>
       </c>
       <c r="BH63" s="44">
-        <f t="shared" si="167"/>
+        <f t="shared" si="179"/>
         <v>7.7133839697568762E-2</v>
       </c>
       <c r="BI63" s="44">
-        <f t="shared" si="167"/>
+        <f t="shared" si="179"/>
         <v>7.3813530797711205E-2</v>
       </c>
       <c r="BJ63" s="44">
-        <f t="shared" si="167"/>
+        <f t="shared" si="179"/>
         <v>7.5317998197175579E-2</v>
       </c>
       <c r="BK63" s="44">
-        <f t="shared" si="167"/>
+        <f t="shared" si="179"/>
         <v>7.6250940864613675E-2</v>
       </c>
       <c r="BL63" s="44">
-        <f t="shared" si="167"/>
+        <f t="shared" si="179"/>
         <v>8.0621173866426865E-2</v>
       </c>
       <c r="BM63" s="44">
@@ -27430,211 +27427,211 @@
         <v>96</v>
       </c>
       <c r="C64" s="44">
-        <f t="shared" ref="C64:AS64" si="168">C47/C43</f>
+        <f t="shared" ref="C64:AS64" si="180">C47/C43</f>
         <v>0.35244558857945235</v>
       </c>
       <c r="D64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.34516720109940446</v>
       </c>
       <c r="E64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.3443723946271422</v>
       </c>
       <c r="F64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.32913472070098576</v>
       </c>
       <c r="G64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.33667858124828154</v>
       </c>
       <c r="H64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.33196372910172856</v>
       </c>
       <c r="I64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.33415056244591868</v>
       </c>
       <c r="J64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.31188053389718512</v>
       </c>
       <c r="K64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.33882221602009488</v>
       </c>
       <c r="L64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.32893124574540505</v>
       </c>
       <c r="M64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.32788685981051763</v>
       </c>
       <c r="N64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.35194542698332493</v>
       </c>
       <c r="O64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.34912043301759133</v>
       </c>
       <c r="P64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.36014184397163118</v>
       </c>
       <c r="Q64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.34238024155244945</v>
       </c>
       <c r="R64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.31876227897838899</v>
       </c>
       <c r="S64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.35170639219934996</v>
       </c>
       <c r="T64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.34821547921400881</v>
       </c>
       <c r="U64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.34402332361516036</v>
       </c>
       <c r="V64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.32163024797446599</v>
       </c>
       <c r="W64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.33938342452956094</v>
       </c>
       <c r="X64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.33999480923955361</v>
       </c>
       <c r="Y64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.33523389918362057</v>
       </c>
       <c r="Z64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.39336334834083708</v>
       </c>
       <c r="AA64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.3714461349316121</v>
       </c>
       <c r="AB64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.34000261540473387</v>
       </c>
       <c r="AC64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.3263022508038585</v>
       </c>
       <c r="AD64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.31619443087445043</v>
       </c>
       <c r="AE64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.31889320145236011</v>
       </c>
       <c r="AF64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.33324837517522621</v>
       </c>
       <c r="AG64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.32989823521834344</v>
       </c>
       <c r="AH64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.3175917913215478</v>
       </c>
       <c r="AI64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.34825668159001494</v>
       </c>
       <c r="AJ64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.34502307185234016</v>
       </c>
       <c r="AK64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.33842370907208491</v>
       </c>
       <c r="AL64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.3061797752808989</v>
       </c>
       <c r="AM64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.33926252921319139</v>
       </c>
       <c r="AN64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.33642284569138275</v>
       </c>
       <c r="AO64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.33044875757201136</v>
       </c>
       <c r="AP64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.32180696239375944</v>
       </c>
       <c r="AQ64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.33543903979785217</v>
       </c>
       <c r="AR64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.32809710817565158</v>
       </c>
       <c r="AS64" s="44">
-        <f t="shared" si="168"/>
+        <f t="shared" si="180"/>
         <v>0.32766521948866378</v>
       </c>
       <c r="AT64" s="44">
-        <f t="shared" ref="AT64:AU64" si="169">AT47/AT43</f>
+        <f t="shared" ref="AT64:AU64" si="181">AT47/AT43</f>
         <v>0.30476190476190479</v>
       </c>
       <c r="AU64" s="44">
-        <f t="shared" si="169"/>
+        <f t="shared" si="181"/>
         <v>0.3271158778269993</v>
       </c>
       <c r="AV64" s="44">
-        <f t="shared" ref="AV64" si="170">AV47/AV43</f>
+        <f t="shared" ref="AV64" si="182">AV47/AV43</f>
         <v>0.33087825019529071</v>
       </c>
       <c r="BG64" s="44">
-        <f t="shared" ref="BG64:BL64" si="171">BG47/BG43</f>
+        <f t="shared" ref="BG64:BL64" si="183">BG47/BG43</f>
         <v>0.34075317111692416</v>
       </c>
       <c r="BH64" s="44">
-        <f t="shared" si="171"/>
+        <f t="shared" si="183"/>
         <v>0.32840842090660005</v>
       </c>
       <c r="BI64" s="44">
-        <f t="shared" si="171"/>
+        <f t="shared" si="183"/>
         <v>0.33719286435543588</v>
       </c>
       <c r="BJ64" s="44">
-        <f t="shared" si="171"/>
+        <f t="shared" si="183"/>
         <v>0.34180215671218239</v>
       </c>
       <c r="BK64" s="44">
-        <f t="shared" si="171"/>
+        <f t="shared" si="183"/>
         <v>0.3409366102693327</v>
       </c>
       <c r="BL64" s="44">
-        <f t="shared" si="171"/>
+        <f t="shared" si="183"/>
         <v>0.3496351122332515</v>
       </c>
       <c r="BM64" s="44">
@@ -27658,19 +27655,19 @@
         <v>0.32351274787535411</v>
       </c>
       <c r="BR64" s="62">
-        <v>0.33</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="BS64" s="62">
-        <v>0.32800000000000001</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="BT64" s="62">
-        <v>0.32500000000000001</v>
+        <v>0.32100000000000001</v>
       </c>
       <c r="BU64" s="62">
-        <v>0.32400000000000001</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="BV64" s="62">
-        <v>0.32300000000000001</v>
+        <v>0.317</v>
       </c>
     </row>
     <row r="65" spans="2:131">
@@ -27678,211 +27675,211 @@
         <v>97</v>
       </c>
       <c r="C65" s="44">
-        <f t="shared" ref="C65:AS65" si="172">C51/C43</f>
+        <f t="shared" ref="C65:AS65" si="184">C51/C43</f>
         <v>0.25462204540135736</v>
       </c>
       <c r="D65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.23591387998167659</v>
       </c>
       <c r="E65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.29527559055118108</v>
       </c>
       <c r="F65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>5.106790799561884E-2</v>
       </c>
       <c r="G65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.155485290074237</v>
       </c>
       <c r="H65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.18418815528478322</v>
       </c>
       <c r="I65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.1954139025093741</v>
       </c>
       <c r="J65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.20814061054579094</v>
       </c>
       <c r="K65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.16285235835891712</v>
       </c>
       <c r="L65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.18856364874063988</v>
       </c>
       <c r="M65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.15749004531099822</v>
       </c>
       <c r="N65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.21273370389085397</v>
       </c>
       <c r="O65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.18700947225981054</v>
       </c>
       <c r="P65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.16978723404255319</v>
       </c>
       <c r="Q65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.19487040303976116</v>
       </c>
       <c r="R65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.32232318271119842</v>
       </c>
       <c r="S65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.16738894907908991</v>
       </c>
       <c r="T65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.20638952011763134</v>
       </c>
       <c r="U65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.20434667373442883</v>
       </c>
       <c r="V65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.23889025288485147</v>
       </c>
       <c r="W65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.19818497264113172</v>
       </c>
       <c r="X65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.17531793407734234</v>
       </c>
       <c r="Y65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.21238823376959959</v>
       </c>
       <c r="Z65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>5.2693013173253291E-2</v>
       </c>
       <c r="AA65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.10342707853081297</v>
       </c>
       <c r="AB65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.12161632012553943</v>
       </c>
       <c r="AC65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.16424437299035369</v>
       </c>
       <c r="AD65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.19650708353688323</v>
       </c>
       <c r="AE65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.10754976837360711</v>
       </c>
       <c r="AF65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.19918440168217152</v>
       </c>
       <c r="AG65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.21370604147880973</v>
       </c>
       <c r="AH65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.2067004574112993</v>
       </c>
       <c r="AI65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.15262515262515264</v>
       </c>
       <c r="AJ65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.18510217534607779</v>
       </c>
       <c r="AK65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.1801475346188689</v>
       </c>
       <c r="AL65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.18305243445692884</v>
       </c>
       <c r="AM65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.16463256297065698</v>
       </c>
       <c r="AN65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.16783567134268537</v>
       </c>
       <c r="AO65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.18333539374459143</v>
       </c>
       <c r="AP65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.12259867272092211</v>
       </c>
       <c r="AQ65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.16146557169930512</v>
       </c>
       <c r="AR65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.18981316196596454</v>
       </c>
       <c r="AS65" s="44">
-        <f t="shared" si="172"/>
+        <f t="shared" si="184"/>
         <v>0.19850458273034249</v>
       </c>
       <c r="AT65" s="44">
-        <f t="shared" ref="AT65:AU65" si="173">AT51/AT43</f>
+        <f t="shared" ref="AT65:AU65" si="185">AT51/AT43</f>
         <v>0.16089635854341736</v>
       </c>
       <c r="AU65" s="44">
-        <f t="shared" si="173"/>
+        <f t="shared" si="185"/>
         <v>0.16833760783399393</v>
       </c>
       <c r="AV65" s="44">
-        <f t="shared" ref="AV65" si="174">AV51/AV43</f>
+        <f t="shared" ref="AV65" si="186">AV51/AV43</f>
         <v>0.18814864412453966</v>
       </c>
       <c r="BG65" s="44">
-        <f t="shared" ref="BG65:BL65" si="175">BG51/BG43</f>
+        <f t="shared" ref="BG65:BL65" si="187">BG51/BG43</f>
         <v>0.18587433986476481</v>
       </c>
       <c r="BH65" s="44">
-        <f t="shared" si="175"/>
+        <f t="shared" si="187"/>
         <v>0.18593278535011964</v>
       </c>
       <c r="BI65" s="44">
-        <f t="shared" si="175"/>
+        <f t="shared" si="187"/>
         <v>0.1811847862672501</v>
       </c>
       <c r="BJ65" s="44">
-        <f t="shared" si="175"/>
+        <f t="shared" si="187"/>
         <v>0.22168063299168697</v>
       </c>
       <c r="BK65" s="44">
-        <f t="shared" si="175"/>
+        <f t="shared" si="187"/>
         <v>0.20512484864351868</v>
       </c>
       <c r="BL65" s="44">
-        <f t="shared" si="175"/>
+        <f t="shared" si="187"/>
         <v>0.16570400857745651</v>
       </c>
       <c r="BM65" s="44">
@@ -27906,24 +27903,24 @@
         <v>0.17757566721335918</v>
       </c>
       <c r="BR65" s="62">
-        <f t="shared" ref="BR65:BU65" si="176">BR51/BR43</f>
-        <v>0.16715579202774683</v>
+        <f t="shared" ref="BR65:BU65" si="188">BR51/BR43</f>
+        <v>0.1760181381201372</v>
       </c>
       <c r="BS65" s="62">
-        <f t="shared" si="176"/>
-        <v>0.17139563155297527</v>
+        <f t="shared" si="188"/>
+        <v>0.18138655502979989</v>
       </c>
       <c r="BT65" s="62">
-        <f t="shared" si="176"/>
-        <v>0.17543478759821304</v>
+        <f t="shared" si="188"/>
+        <v>0.18565842449279918</v>
       </c>
       <c r="BU65" s="62">
-        <f t="shared" si="176"/>
-        <v>0.1770951406452794</v>
+        <f t="shared" si="188"/>
+        <v>0.18947068473796755</v>
       </c>
       <c r="BV65" s="62">
-        <f t="shared" ref="BV65" si="177">BV51/BV43</f>
-        <v>0.17825498779638219</v>
+        <f t="shared" ref="BV65" si="189">BV51/BV43</f>
+        <v>0.19282033077244362</v>
       </c>
     </row>
     <row r="66" spans="2:131">
@@ -27931,211 +27928,211 @@
         <v>98</v>
       </c>
       <c r="C66" s="44">
-        <f t="shared" ref="C66:AS66" si="178">C55/C54</f>
+        <f t="shared" ref="C66:AS66" si="190">C55/C54</f>
         <v>0.19575253924284394</v>
       </c>
       <c r="D66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.18982387475538159</v>
       </c>
       <c r="E66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.18174204355108878</v>
       </c>
       <c r="F66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>1.0053475935828877</v>
       </c>
       <c r="G66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.1276595744680851</v>
       </c>
       <c r="H66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.51985226223453374</v>
       </c>
       <c r="I66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>7.124681933842239E-2</v>
       </c>
       <c r="J66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>2.7336860670194002E-2</v>
       </c>
       <c r="K66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>5.9716599190283402E-2</v>
       </c>
       <c r="L66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="M66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.15201654601861428</v>
       </c>
       <c r="N66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.18885017421602787</v>
       </c>
       <c r="O66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.15564853556485356</v>
       </c>
       <c r="P66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>-0.16493055555555555</v>
       </c>
       <c r="Q66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>2.3554040895813046</v>
       </c>
       <c r="R66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.15072463768115943</v>
       </c>
       <c r="S66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>8.7288135593220337E-2</v>
       </c>
       <c r="T66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.17343173431734318</v>
       </c>
       <c r="U66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>7.2262773722627738E-2</v>
       </c>
       <c r="V66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>8.5139318885448914E-2</v>
       </c>
       <c r="W66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.10235414534288639</v>
       </c>
       <c r="X66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>-5.9505409582689336E-2</v>
       </c>
       <c r="Y66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>-0.21532615579480685</v>
       </c>
       <c r="Z66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>-2.1170731707317074</v>
       </c>
       <c r="AA66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.15924657534246575</v>
       </c>
       <c r="AB66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>5.904761904761905E-2</v>
       </c>
       <c r="AC66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>-4.836065573770492E-2</v>
       </c>
       <c r="AD66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.1273074474856779</v>
       </c>
       <c r="AE66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>7.6830732292917162E-2</v>
       </c>
       <c r="AF66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.11788345612860013</v>
       </c>
       <c r="AG66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>6.6708621774701077E-2</v>
       </c>
       <c r="AH66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>6.8621334996880848E-2</v>
       </c>
       <c r="AI66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.1082375478927203</v>
       </c>
       <c r="AJ66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.68817204301075274</v>
       </c>
       <c r="AK66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.10618181818181818</v>
       </c>
       <c r="AL66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.23290322580645162</v>
       </c>
       <c r="AM66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.33444816053511706</v>
       </c>
       <c r="AN66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.30616907844630614</v>
       </c>
       <c r="AO66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>9.1711956521739135E-2</v>
       </c>
       <c r="AP66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.22780373831775702</v>
       </c>
       <c r="AQ66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.17271293375394323</v>
       </c>
       <c r="AR66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.17960230917254649</v>
       </c>
       <c r="AS66" s="44">
-        <f t="shared" si="178"/>
+        <f t="shared" si="190"/>
         <v>0.15389610389610389</v>
       </c>
       <c r="AT66" s="44">
-        <f t="shared" ref="AT66:AU66" si="179">AT55/AT54</f>
+        <f t="shared" ref="AT66:AU66" si="191">AT55/AT54</f>
         <v>0.15860428231562251</v>
       </c>
       <c r="AU66" s="44">
-        <f t="shared" si="179"/>
+        <f t="shared" si="191"/>
         <v>0.19600307455803229</v>
       </c>
       <c r="AV66" s="44">
-        <f t="shared" ref="AV66" si="180">AV55/AV54</f>
+        <f t="shared" ref="AV66" si="192">AV55/AV54</f>
         <v>0.13462742642454603</v>
       </c>
       <c r="BG66" s="44">
-        <f t="shared" ref="BG66:BL66" si="181">BG55/BG54</f>
+        <f t="shared" ref="BG66:BL66" si="193">BG55/BG54</f>
         <v>0.23264486517498564</v>
       </c>
       <c r="BH66" s="44">
-        <f t="shared" si="181"/>
+        <f t="shared" si="193"/>
         <v>0.18404059040590406</v>
       </c>
       <c r="BI66" s="44">
-        <f t="shared" si="181"/>
+        <f t="shared" si="193"/>
         <v>0.12559756627553237</v>
       </c>
       <c r="BJ66" s="44">
-        <f t="shared" si="181"/>
+        <f t="shared" si="193"/>
         <v>0.45462555066079297</v>
       </c>
       <c r="BK66" s="44">
-        <f t="shared" si="181"/>
+        <f t="shared" si="193"/>
         <v>0.10525303059457379</v>
       </c>
       <c r="BL66" s="44">
-        <f t="shared" si="181"/>
+        <f t="shared" si="193"/>
         <v>-0.18520345252774353</v>
       </c>
       <c r="BM66" s="44">
@@ -28179,211 +28176,211 @@
         <v>99</v>
       </c>
       <c r="C67" s="44">
-        <f t="shared" ref="C67:AS67" si="182">C56/C43</f>
+        <f t="shared" ref="C67:AS67" si="194">C56/C43</f>
         <v>0.20383805289024104</v>
       </c>
       <c r="D67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.18964727439303711</v>
       </c>
       <c r="E67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.22626215840666974</v>
       </c>
       <c r="F67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>-1.3691128148959474E-4</v>
       </c>
       <c r="G67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.11273027220236459</v>
       </c>
       <c r="H67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>7.3675262113913287E-2</v>
       </c>
       <c r="I67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.15791750793192963</v>
       </c>
       <c r="J67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.14576450376635391</v>
       </c>
       <c r="K67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.12963996650851242</v>
       </c>
       <c r="L67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.15125936010891763</v>
       </c>
       <c r="M67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.11259096526156803</v>
       </c>
       <c r="N67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.14704396159676605</v>
       </c>
       <c r="O67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.13653585926928283</v>
       </c>
       <c r="P67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.28553191489361701</v>
       </c>
       <c r="Q67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>-0.18889944361514452</v>
       </c>
       <c r="R67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.17988703339882123</v>
       </c>
       <c r="S67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.14585590465872156</v>
       </c>
       <c r="T67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.14971260526667557</v>
       </c>
       <c r="U67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.1684336072091174</v>
       </c>
       <c r="V67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.14510189049840413</v>
       </c>
       <c r="W67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.11704257306819699</v>
       </c>
       <c r="X67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.17791331430054502</v>
       </c>
       <c r="Y67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.24867176363871971</v>
       </c>
       <c r="Z67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.10655327663831916</v>
       </c>
       <c r="AA67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>7.5457199938527744E-2</v>
       </c>
       <c r="AB67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>6.4600496926899439E-2</v>
       </c>
       <c r="AC67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.16450160771704181</v>
       </c>
       <c r="AD67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.16744015632633122</v>
       </c>
       <c r="AE67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>9.6281457368223369E-2</v>
       </c>
       <c r="AF67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.16783484134063972</v>
       </c>
       <c r="AG67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.19103439391987634</v>
       </c>
       <c r="AH67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.18457164049944369</v>
       </c>
       <c r="AI67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.12630579297245964</v>
       </c>
       <c r="AJ67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>5.7350032959789056E-2</v>
       </c>
       <c r="AK67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.15905267244726284</v>
       </c>
       <c r="AL67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.13916198501872659</v>
       </c>
       <c r="AM67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.10334977927810958</v>
       </c>
       <c r="AN67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.11410320641282565</v>
       </c>
       <c r="AO67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.16528619112374829</v>
       </c>
       <c r="AP67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>7.6958900919781109E-2</v>
       </c>
       <c r="AQ67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.13253316487681618</v>
       </c>
       <c r="AR67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.15220754492443175</v>
       </c>
       <c r="AS67" s="44">
-        <f t="shared" si="182"/>
+        <f t="shared" si="194"/>
         <v>0.15713941148094548</v>
       </c>
       <c r="AT67" s="44">
-        <f t="shared" ref="AT67:AU67" si="183">AT56/AT43</f>
+        <f t="shared" ref="AT67:AU67" si="195">AT56/AT43</f>
         <v>0.11887955182072829</v>
       </c>
       <c r="AU67" s="44">
-        <f t="shared" si="183"/>
+        <f t="shared" si="195"/>
         <v>0.12193984611797622</v>
       </c>
       <c r="AV67" s="44">
-        <f t="shared" ref="AV67" si="184">AV56/AV43</f>
+        <f t="shared" ref="AV67" si="196">AV56/AV43</f>
         <v>0.15422385894431426</v>
       </c>
       <c r="BG67" s="44">
-        <f t="shared" ref="BG67:BL67" si="185">BG56/BG43</f>
+        <f t="shared" ref="BG67:BL67" si="197">BG56/BG43</f>
         <v>0.13202704703617787</v>
       </c>
       <c r="BH67" s="44">
-        <f t="shared" si="185"/>
+        <f t="shared" si="197"/>
         <v>0.12270662088579058</v>
       </c>
       <c r="BI67" s="44">
-        <f t="shared" si="185"/>
+        <f t="shared" si="197"/>
         <v>0.13544261191518006</v>
       </c>
       <c r="BJ67" s="44">
-        <f t="shared" si="185"/>
+        <f t="shared" si="197"/>
         <v>0.10332854805862518</v>
       </c>
       <c r="BK67" s="44">
-        <f t="shared" si="185"/>
+        <f t="shared" si="197"/>
         <v>0.15217462447229768</v>
       </c>
       <c r="BL67" s="44">
-        <f t="shared" si="185"/>
+        <f t="shared" si="197"/>
         <v>0.16622280635008474</v>
       </c>
       <c r="BM67" s="44">
@@ -28407,24 +28404,24 @@
         <v>0.13991352318473238</v>
       </c>
       <c r="BR67" s="62">
-        <f t="shared" ref="BR67:BU67" si="186">BR58/BR43</f>
-        <v>0.12177895416162207</v>
+        <f t="shared" ref="BR67:BU67" si="198">BR58/BR43</f>
+        <v>0.12944475556393412</v>
       </c>
       <c r="BS67" s="62">
-        <f t="shared" si="186"/>
-        <v>0.13248268443515709</v>
+        <f t="shared" si="198"/>
+        <v>0.14174016266435407</v>
       </c>
       <c r="BT67" s="62">
-        <f t="shared" si="186"/>
-        <v>0.14317020097643485</v>
+        <f t="shared" si="198"/>
+        <v>0.15326106404106712</v>
       </c>
       <c r="BU67" s="62">
-        <f t="shared" si="186"/>
-        <v>0.1521024836154822</v>
+        <f t="shared" si="198"/>
+        <v>0.164612505252866</v>
       </c>
       <c r="BV67" s="62">
-        <f t="shared" ref="BV67" si="187">BV58/BV43</f>
-        <v>0.16077860504212466</v>
+        <f t="shared" ref="BV67" si="199">BV58/BV43</f>
+        <v>0.1758476781920891</v>
       </c>
     </row>
     <row r="69" spans="2:131">
@@ -28489,44 +28486,44 @@
         <v>1282</v>
       </c>
       <c r="BM69" s="1">
-        <f>AD69</f>
+        <f t="shared" ref="BM69:BM79" si="200">AD69</f>
         <v>3593</v>
       </c>
       <c r="BN69" s="1">
-        <f>AH69</f>
+        <f t="shared" ref="BN69:BN79" si="201">AH69</f>
         <v>3714</v>
       </c>
       <c r="BO69" s="1">
-        <f>AL69</f>
+        <f t="shared" ref="BO69:BO79" si="202">AL69</f>
         <v>1543</v>
       </c>
       <c r="BP69" s="1">
-        <f>AP69</f>
+        <f t="shared" ref="BP69:BP79" si="203">AP69</f>
         <v>1284</v>
       </c>
       <c r="BQ69" s="1">
-        <f>AT69</f>
+        <f t="shared" ref="BQ69:BQ79" si="204">AT69</f>
         <v>2218</v>
       </c>
       <c r="BR69" s="63">
         <f>BQ69+BR58</f>
-        <v>6504.2249271249984</v>
+        <v>6898.8477931599991</v>
       </c>
       <c r="BS69" s="63">
         <f>BR69+BS58</f>
-        <v>11374.708510381734</v>
+        <v>12343.629772269131</v>
       </c>
       <c r="BT69" s="63">
         <f>BS69+BT58</f>
-        <v>16870.208842444888</v>
+        <v>18512.317339998841</v>
       </c>
       <c r="BU69" s="63">
         <f>BT69+BU58</f>
-        <v>22949.562393298573</v>
+        <v>25425.503194548139</v>
       </c>
       <c r="BV69" s="63">
         <f>BU69+BV58</f>
-        <v>29613.540365274894</v>
+        <v>33100.88343367054</v>
       </c>
     </row>
     <row r="70" spans="2:131">
@@ -28591,23 +28588,23 @@
         <v>7045</v>
       </c>
       <c r="BM70" s="1">
-        <f>AD70</f>
+        <f t="shared" si="200"/>
         <v>7224</v>
       </c>
       <c r="BN70" s="1">
-        <f>AH70</f>
+        <f t="shared" si="201"/>
         <v>6859</v>
       </c>
       <c r="BO70" s="1">
-        <f>AL70</f>
+        <f t="shared" si="202"/>
         <v>6416</v>
       </c>
       <c r="BP70" s="1">
-        <f>AP70</f>
+        <f t="shared" si="203"/>
         <v>6721</v>
       </c>
       <c r="BQ70" s="1">
-        <f>AT70</f>
+        <f t="shared" si="204"/>
         <v>6747</v>
       </c>
     </row>
@@ -28673,42 +28670,42 @@
         <v>6389</v>
       </c>
       <c r="BM71" s="1">
-        <f>AD71</f>
+        <f t="shared" si="200"/>
         <v>5462</v>
       </c>
       <c r="BN71" s="1">
-        <f>AH71</f>
+        <f t="shared" si="201"/>
         <v>5551</v>
       </c>
       <c r="BO71" s="1">
-        <f>AL71</f>
+        <f t="shared" si="202"/>
         <v>5998</v>
       </c>
       <c r="BP71" s="1">
-        <f>AP71</f>
+        <f t="shared" si="203"/>
         <v>6128</v>
       </c>
       <c r="BQ71" s="1">
-        <f>AT71</f>
+        <f t="shared" si="204"/>
         <v>6515</v>
       </c>
       <c r="BS71" s="71" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="BT71" s="72"/>
       <c r="BU71" s="72"/>
       <c r="BV71" s="71" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="BW71" s="72"/>
       <c r="BX71" s="73" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="BZ71" s="65" t="s">
         <v>2257</v>
       </c>
       <c r="CA71" s="79">
-        <v>6.3500000000000001E-2</v>
+        <v>6.6000000000000003E-2</v>
       </c>
       <c r="CC71" s="59" t="s">
         <v>2268</v>
@@ -28776,23 +28773,23 @@
         <v>6156</v>
       </c>
       <c r="BM72" s="1">
-        <f>AD72</f>
+        <f t="shared" si="200"/>
         <v>4313</v>
       </c>
       <c r="BN72" s="1">
-        <f>AH72</f>
+        <f t="shared" si="201"/>
         <v>4616</v>
       </c>
       <c r="BO72" s="1">
-        <f>AL72</f>
+        <f t="shared" si="202"/>
         <v>5293</v>
       </c>
       <c r="BP72" s="1">
-        <f>AP72</f>
+        <f t="shared" si="203"/>
         <v>5217</v>
       </c>
       <c r="BQ72" s="1">
-        <f>AT72</f>
+        <f t="shared" si="204"/>
         <v>5476</v>
       </c>
       <c r="BS72" s="72">
@@ -28807,7 +28804,7 @@
       </c>
       <c r="BW72" s="72"/>
       <c r="BX72" s="73" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="BZ72" s="65" t="s">
         <v>2258</v>
@@ -28878,28 +28875,28 @@
         <v>3124</v>
       </c>
       <c r="BM73" s="1">
-        <f>AD73</f>
+        <f t="shared" si="200"/>
         <v>1955</v>
       </c>
       <c r="BN73" s="1">
-        <f>AH73</f>
+        <f t="shared" si="201"/>
         <v>2318</v>
       </c>
       <c r="BO73" s="1">
-        <f>AL73</f>
+        <f t="shared" si="202"/>
         <v>2425</v>
       </c>
       <c r="BP73" s="1">
-        <f>AP73</f>
+        <f t="shared" si="203"/>
         <v>2584</v>
       </c>
       <c r="BQ73" s="1">
-        <f>AT73</f>
+        <f t="shared" si="204"/>
         <v>2858</v>
       </c>
       <c r="BS73" s="74">
         <f>AVERAGE(BR51)*(1-BR66)</f>
-        <v>4765.5075971249989</v>
+        <v>5155.6390131600001</v>
       </c>
       <c r="BT73" s="72"/>
       <c r="BU73" s="75">
@@ -28985,28 +28982,28 @@
         <v>7164</v>
       </c>
       <c r="BM74" s="1">
-        <f>AD74</f>
+        <f t="shared" si="200"/>
         <v>5221</v>
       </c>
       <c r="BN74" s="1">
-        <f>AH74</f>
+        <f t="shared" si="201"/>
         <v>5413</v>
       </c>
       <c r="BO74" s="1">
-        <f>AL74</f>
+        <f t="shared" si="202"/>
         <v>5569</v>
       </c>
       <c r="BP74" s="1">
-        <f>AP74</f>
+        <f t="shared" si="203"/>
         <v>6131</v>
       </c>
       <c r="BQ74" s="1">
-        <f>AT74</f>
+        <f t="shared" si="204"/>
         <v>6837</v>
       </c>
       <c r="BS74" s="76">
         <f>BS73/BX73</f>
-        <v>6.0736891304971216E-2</v>
+        <v>6.5709156887900438E-2</v>
       </c>
       <c r="BT74" s="72"/>
       <c r="BU74" s="72"/>
@@ -29083,23 +29080,23 @@
         <v>41811</v>
       </c>
       <c r="BM75" s="1">
-        <f>AD75</f>
+        <f t="shared" si="200"/>
         <v>41961</v>
       </c>
       <c r="BN75" s="1">
-        <f>AH75</f>
+        <f t="shared" si="201"/>
         <v>40502</v>
       </c>
       <c r="BO75" s="1">
-        <f>AL75</f>
+        <f t="shared" si="202"/>
         <v>41425</v>
       </c>
       <c r="BP75" s="1">
-        <f>AP75</f>
+        <f t="shared" si="203"/>
         <v>40986</v>
       </c>
       <c r="BQ75" s="1">
-        <f>AT75</f>
+        <f t="shared" si="204"/>
         <v>41737</v>
       </c>
       <c r="BS75" s="72"/>
@@ -29177,23 +29174,23 @@
         <v>10770</v>
       </c>
       <c r="BM76" s="1">
-        <f>AD76</f>
+        <f t="shared" si="200"/>
         <v>17740</v>
       </c>
       <c r="BN76" s="1">
-        <f>AH76</f>
+        <f t="shared" si="201"/>
         <v>15595</v>
       </c>
       <c r="BO76" s="1">
-        <f>AL76</f>
+        <f t="shared" si="202"/>
         <v>14844</v>
       </c>
       <c r="BP76" s="1">
-        <f>AP76</f>
+        <f t="shared" si="203"/>
         <v>13225</v>
       </c>
       <c r="BQ76" s="1">
-        <f>AT76</f>
+        <f t="shared" si="204"/>
         <v>11667</v>
       </c>
       <c r="BZ76" s="65" t="s">
@@ -29266,23 +29263,23 @@
         <v>3857</v>
       </c>
       <c r="BM77" s="1">
-        <f>AD77</f>
+        <f t="shared" si="200"/>
         <v>3169</v>
       </c>
       <c r="BN77" s="1">
-        <f>AH77</f>
+        <f t="shared" si="201"/>
         <v>3403</v>
       </c>
       <c r="BO77" s="1">
-        <f>AL77</f>
+        <f t="shared" si="202"/>
         <v>3477</v>
       </c>
       <c r="BP77" s="1">
-        <f>AP77</f>
+        <f t="shared" si="203"/>
         <v>3657</v>
       </c>
       <c r="BQ77" s="1">
-        <f>AT77</f>
+        <f t="shared" si="204"/>
         <v>4040</v>
       </c>
       <c r="BZ77" s="65"/>
@@ -29349,23 +29346,23 @@
         <v>3748</v>
       </c>
       <c r="BM78" s="1">
-        <f>AD78</f>
+        <f t="shared" si="200"/>
         <v>2446</v>
       </c>
       <c r="BN78" s="1">
-        <f>AH78</f>
+        <f t="shared" si="201"/>
         <v>3010</v>
       </c>
       <c r="BO78" s="1">
-        <f>AL78</f>
+        <f t="shared" si="202"/>
         <v>3958</v>
       </c>
       <c r="BP78" s="1">
-        <f>AP78</f>
+        <f t="shared" si="203"/>
         <v>4048</v>
       </c>
       <c r="BQ78" s="1">
-        <f>AT78</f>
+        <f t="shared" si="204"/>
         <v>3585</v>
       </c>
       <c r="BZ78" s="65" t="s">
@@ -29373,7 +29370,7 @@
       </c>
       <c r="CA78" s="63">
         <f>NPV(CA76,BR58:DY58)</f>
-        <v>122505.87197425291</v>
+        <v>140513.07944650803</v>
       </c>
       <c r="CB78" s="60"/>
       <c r="CC78" s="60"/>
@@ -29383,63 +29380,63 @@
         <v>2251</v>
       </c>
       <c r="AD79" s="2">
-        <f t="shared" ref="AD79:AR79" si="188">SUM(AD69:AD78)</f>
+        <f t="shared" ref="AD79:AR79" si="205">SUM(AD69:AD78)</f>
         <v>93084</v>
       </c>
       <c r="AE79" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="205"/>
         <v>91802</v>
       </c>
       <c r="AF79" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="205"/>
         <v>91756</v>
       </c>
       <c r="AG79" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="205"/>
         <v>91804</v>
       </c>
       <c r="AH79" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="205"/>
         <v>90981</v>
       </c>
       <c r="AI79" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="205"/>
         <v>89914</v>
       </c>
       <c r="AJ79" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="205"/>
         <v>93241</v>
       </c>
       <c r="AK79" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="205"/>
         <v>94134</v>
       </c>
       <c r="AL79" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="205"/>
         <v>90948</v>
       </c>
       <c r="AM79" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="205"/>
         <v>90776</v>
       </c>
       <c r="AN79" s="2">
-        <f t="shared" ref="AN79" si="189">SUM(AN69:AN78)</f>
+        <f t="shared" ref="AN79" si="206">SUM(AN69:AN78)</f>
         <v>90087</v>
       </c>
       <c r="AO79" s="2">
-        <f t="shared" ref="AO79" si="190">SUM(AO69:AO78)</f>
+        <f t="shared" ref="AO79" si="207">SUM(AO69:AO78)</f>
         <v>90836</v>
       </c>
       <c r="AP79" s="2">
-        <f t="shared" ref="AP79" si="191">SUM(AP69:AP78)</f>
+        <f t="shared" ref="AP79" si="208">SUM(AP69:AP78)</f>
         <v>89981</v>
       </c>
       <c r="AQ79" s="2">
-        <f t="shared" ref="AQ79" si="192">SUM(AQ69:AQ78)</f>
+        <f t="shared" ref="AQ79" si="209">SUM(AQ69:AQ78)</f>
         <v>89749</v>
       </c>
       <c r="AR79" s="2">
-        <f t="shared" si="188"/>
+        <f t="shared" si="205"/>
         <v>90042</v>
       </c>
       <c r="AS79" s="2">
@@ -29447,7 +29444,7 @@
         <v>89973</v>
       </c>
       <c r="AT79" s="2">
-        <f t="shared" ref="AT79" si="193">SUM(AT69:AT78)</f>
+        <f t="shared" ref="AT79" si="210">SUM(AT69:AT78)</f>
         <v>91680</v>
       </c>
       <c r="AU79" s="2">
@@ -29467,23 +29464,23 @@
       <c r="BC79" s="34"/>
       <c r="BD79" s="34"/>
       <c r="BM79" s="2">
-        <f>AD79</f>
+        <f t="shared" si="200"/>
         <v>93084</v>
       </c>
       <c r="BN79" s="2">
-        <f>AH79</f>
+        <f t="shared" si="201"/>
         <v>90981</v>
       </c>
       <c r="BO79" s="2">
-        <f>AL79</f>
+        <f t="shared" si="202"/>
         <v>90948</v>
       </c>
       <c r="BP79" s="2">
-        <f>AP79</f>
+        <f t="shared" si="203"/>
         <v>89981</v>
       </c>
       <c r="BQ79" s="2">
-        <f>AT79</f>
+        <f t="shared" si="204"/>
         <v>91680</v>
       </c>
       <c r="BR79" s="60"/>
@@ -29492,7 +29489,7 @@
       </c>
       <c r="CA79" s="63">
         <f>Main!C4</f>
-        <v>1282.68</v>
+        <v>1282.01</v>
       </c>
       <c r="CB79" s="59"/>
       <c r="CC79" s="59"/>
@@ -29551,7 +29548,7 @@
       </c>
       <c r="CA80" s="64">
         <f>CA78/CA79</f>
-        <v>95.507743142680098</v>
+        <v>109.60373120842117</v>
       </c>
     </row>
     <row r="81" spans="2:131" ht="15" customHeight="1">
@@ -29616,23 +29613,23 @@
         <v>1420</v>
       </c>
       <c r="BM81" s="1">
-        <f>AD81</f>
+        <f t="shared" ref="BM81:BM93" si="211">AD81</f>
         <v>11</v>
       </c>
       <c r="BN81" s="1">
-        <f>AH81</f>
+        <f t="shared" ref="BN81:BN93" si="212">AH81</f>
         <v>3742</v>
       </c>
       <c r="BO81" s="1">
-        <f>AL81</f>
+        <f t="shared" ref="BO81:BO93" si="213">AL81</f>
         <v>20</v>
       </c>
       <c r="BP81" s="1">
-        <f>AP81</f>
+        <f t="shared" ref="BP81:BP93" si="214">AP81</f>
         <v>1092</v>
       </c>
       <c r="BQ81" s="1">
-        <f>AT81</f>
+        <f t="shared" ref="BQ81:BQ93" si="215">AT81</f>
         <v>2874</v>
       </c>
       <c r="BZ81" s="65" t="s">
@@ -29640,7 +29637,7 @@
       </c>
       <c r="CA81" s="64">
         <f>Main!C3</f>
-        <v>91.17</v>
+        <v>97.89</v>
       </c>
     </row>
     <row r="82" spans="2:131" ht="15" customHeight="1">
@@ -29705,23 +29702,23 @@
         <v>2581</v>
       </c>
       <c r="BM82" s="1">
-        <f>AD82</f>
+        <f t="shared" si="211"/>
         <v>2106</v>
       </c>
       <c r="BN82" s="1">
-        <f>AH82</f>
+        <f t="shared" si="212"/>
         <v>2276</v>
       </c>
       <c r="BO82" s="1">
-        <f>AL82</f>
+        <f t="shared" si="213"/>
         <v>2662</v>
       </c>
       <c r="BP82" s="1">
-        <f>AP82</f>
+        <f t="shared" si="214"/>
         <v>2410</v>
       </c>
       <c r="BQ82" s="1">
-        <f>AT82</f>
+        <f t="shared" si="215"/>
         <v>2449</v>
       </c>
       <c r="BZ82" s="65" t="s">
@@ -29729,7 +29726,7 @@
       </c>
       <c r="CA82" s="66">
         <f>CA80/CA81-1</f>
-        <v>4.7578623918834051E-2</v>
+        <v>0.11966218417020302</v>
       </c>
       <c r="CB82" s="67" t="str">
         <f>IF(CA82&gt;0,"Upside","Downside")</f>
@@ -29798,28 +29795,28 @@
         <v>2130</v>
       </c>
       <c r="BM83" s="1">
-        <f>AD83</f>
+        <f t="shared" si="211"/>
         <v>2482</v>
       </c>
       <c r="BN83" s="1">
-        <f>AH83</f>
+        <f t="shared" si="212"/>
         <v>2121</v>
       </c>
       <c r="BO83" s="1">
-        <f>AL83</f>
+        <f t="shared" si="213"/>
         <v>1949</v>
       </c>
       <c r="BP83" s="1">
-        <f>AP83</f>
+        <f t="shared" si="214"/>
         <v>2375</v>
       </c>
       <c r="BQ83" s="1">
-        <f>AT83</f>
+        <f t="shared" si="215"/>
         <v>2514</v>
       </c>
       <c r="BZ83" s="80" t="str" cm="1">
         <f t="array" ref="BZ83">_xlfn.IFS(CA82&gt;=25%,"Strong Buy",CA82&gt;=10.00001%,"Buy",AND(CA82&lt;=10%,CA82&gt;=-4.9999%),"Hold",AND(CA82&lt;=-5%,CA82&gt;=-14.999999%),"Sell",CA82&lt;=-15%,"Strong Sell")</f>
-        <v>Hold</v>
+        <v>Buy</v>
       </c>
       <c r="CA83" s="80"/>
     </row>
@@ -29885,23 +29882,23 @@
         <v>650</v>
       </c>
       <c r="BM84" s="1">
-        <f>AD84</f>
+        <f t="shared" si="211"/>
         <v>435</v>
       </c>
       <c r="BN84" s="1">
-        <f>AH84</f>
+        <f t="shared" si="212"/>
         <v>704</v>
       </c>
       <c r="BO84" s="1">
-        <f>AL84</f>
+        <f t="shared" si="213"/>
         <v>840</v>
       </c>
       <c r="BP84" s="1">
-        <f>AP84</f>
+        <f t="shared" si="214"/>
         <v>1330</v>
       </c>
       <c r="BQ84" s="1">
-        <f>AT84</f>
+        <f t="shared" si="215"/>
         <v>1358</v>
       </c>
     </row>
@@ -29967,23 +29964,23 @@
         <v>3153</v>
       </c>
       <c r="BM85" s="1">
-        <f>AD85</f>
+        <f t="shared" si="211"/>
         <v>3475</v>
       </c>
       <c r="BN85" s="1">
-        <f>AH85</f>
+        <f t="shared" si="212"/>
         <v>3551</v>
       </c>
       <c r="BO85" s="1">
-        <f>AL85</f>
+        <f t="shared" si="213"/>
         <v>3581</v>
       </c>
       <c r="BP85" s="1">
-        <f>AP85</f>
+        <f t="shared" si="214"/>
         <v>3582</v>
       </c>
       <c r="BQ85" s="1">
-        <f>AT85</f>
+        <f t="shared" si="215"/>
         <v>3683</v>
       </c>
     </row>
@@ -30049,23 +30046,23 @@
         <v>27680</v>
       </c>
       <c r="BM86" s="1">
-        <f>AD86</f>
+        <f t="shared" si="211"/>
         <v>26378</v>
       </c>
       <c r="BN86" s="1">
-        <f>AH86</f>
+        <f t="shared" si="212"/>
         <v>20372</v>
       </c>
       <c r="BO86" s="1">
-        <f>AL86</f>
+        <f t="shared" si="213"/>
         <v>24344</v>
       </c>
       <c r="BP86" s="1">
-        <f>AP86</f>
+        <f t="shared" si="214"/>
         <v>23932</v>
       </c>
       <c r="BQ86" s="1">
-        <f>AT86</f>
+        <f t="shared" si="215"/>
         <v>25642</v>
       </c>
     </row>
@@ -30131,23 +30128,23 @@
         <v>1184</v>
       </c>
       <c r="BM87" s="1">
-        <f>AD87</f>
+        <f t="shared" si="211"/>
         <v>1557</v>
       </c>
       <c r="BN87" s="1">
-        <f>AH87</f>
+        <f t="shared" si="212"/>
         <v>1113</v>
       </c>
       <c r="BO87" s="1">
-        <f>AL87</f>
+        <f t="shared" si="213"/>
         <v>1093</v>
       </c>
       <c r="BP87" s="1">
-        <f>AP87</f>
+        <f t="shared" si="214"/>
         <v>1101</v>
       </c>
       <c r="BQ87" s="1">
-        <f>AT87</f>
+        <f t="shared" si="215"/>
         <v>1158</v>
       </c>
     </row>
@@ -30213,23 +30210,23 @@
         <v>1539</v>
       </c>
       <c r="BM88" s="1">
-        <f>AD88</f>
+        <f t="shared" si="211"/>
         <v>2251</v>
       </c>
       <c r="BN88" s="1">
-        <f>AH88</f>
+        <f t="shared" si="212"/>
         <v>2087</v>
       </c>
       <c r="BO88" s="1">
-        <f>AL88</f>
+        <f t="shared" si="213"/>
         <v>2360</v>
       </c>
       <c r="BP88" s="1">
-        <f>AP88</f>
+        <f t="shared" si="214"/>
         <v>1859</v>
       </c>
       <c r="BQ88" s="1">
-        <f>AT88</f>
+        <f t="shared" si="215"/>
         <v>1574</v>
       </c>
     </row>
@@ -30295,23 +30292,23 @@
         <v>386</v>
       </c>
       <c r="BM89" s="1">
-        <f>AD89</f>
+        <f t="shared" si="211"/>
         <v>1028</v>
       </c>
       <c r="BN89" s="1">
-        <f>AH89</f>
+        <f t="shared" si="212"/>
         <v>884</v>
       </c>
       <c r="BO89" s="1">
-        <f>AL89</f>
+        <f t="shared" si="213"/>
         <v>708</v>
       </c>
       <c r="BP89" s="1">
-        <f>AP89</f>
+        <f t="shared" si="214"/>
         <v>515</v>
       </c>
       <c r="BQ89" s="1">
-        <f>AT89</f>
+        <f t="shared" si="215"/>
         <v>403</v>
       </c>
     </row>
@@ -30377,23 +30374,23 @@
         <v>1764</v>
       </c>
       <c r="BM90" s="1">
-        <f>AD90</f>
+        <f t="shared" si="211"/>
         <v>1756</v>
       </c>
       <c r="BN90" s="1">
-        <f>AH90</f>
+        <f t="shared" si="212"/>
         <v>1410</v>
       </c>
       <c r="BO90" s="1">
-        <f>AL90</f>
+        <f t="shared" si="213"/>
         <v>1727</v>
       </c>
       <c r="BP90" s="1">
-        <f>AP90</f>
+        <f t="shared" si="214"/>
         <v>1365</v>
       </c>
       <c r="BQ90" s="1">
-        <f>AT90</f>
+        <f t="shared" si="215"/>
         <v>1769</v>
       </c>
     </row>
@@ -30402,63 +30399,63 @@
         <v>2252</v>
       </c>
       <c r="AD91" s="2">
-        <f t="shared" ref="AD91:AR91" si="194">SUM(AD81:AD90)</f>
+        <f t="shared" ref="AD91:AR91" si="216">SUM(AD81:AD90)</f>
         <v>41479</v>
       </c>
       <c r="AE91" s="2">
-        <f t="shared" si="194"/>
+        <f t="shared" si="216"/>
         <v>40138</v>
       </c>
       <c r="AF91" s="2">
-        <f t="shared" si="194"/>
+        <f t="shared" si="216"/>
         <v>39596</v>
       </c>
       <c r="AG91" s="2">
-        <f t="shared" si="194"/>
+        <f t="shared" si="216"/>
         <v>39092</v>
       </c>
       <c r="AH91" s="2">
-        <f t="shared" si="194"/>
+        <f t="shared" si="216"/>
         <v>38260</v>
       </c>
       <c r="AI91" s="2">
-        <f t="shared" si="194"/>
+        <f t="shared" si="216"/>
         <v>37071</v>
       </c>
       <c r="AJ91" s="2">
-        <f t="shared" si="194"/>
+        <f t="shared" si="216"/>
         <v>41186</v>
       </c>
       <c r="AK91" s="2">
-        <f t="shared" si="194"/>
+        <f t="shared" si="216"/>
         <v>42516</v>
       </c>
       <c r="AL91" s="2">
-        <f t="shared" si="194"/>
+        <f t="shared" si="216"/>
         <v>39284</v>
       </c>
       <c r="AM91" s="2">
-        <f t="shared" si="194"/>
+        <f t="shared" si="216"/>
         <v>39411</v>
       </c>
       <c r="AN91" s="2">
-        <f t="shared" si="194"/>
+        <f t="shared" si="216"/>
         <v>38440</v>
       </c>
       <c r="AO91" s="2">
-        <f t="shared" ref="AO91" si="195">SUM(AO81:AO90)</f>
+        <f t="shared" ref="AO91" si="217">SUM(AO81:AO90)</f>
         <v>38840</v>
       </c>
       <c r="AP91" s="2">
-        <f t="shared" ref="AP91" si="196">SUM(AP81:AP90)</f>
+        <f t="shared" ref="AP91" si="218">SUM(AP81:AP90)</f>
         <v>39561</v>
       </c>
       <c r="AQ91" s="2">
-        <f t="shared" si="194"/>
+        <f t="shared" si="216"/>
         <v>41589</v>
       </c>
       <c r="AR91" s="2">
-        <f t="shared" si="194"/>
+        <f t="shared" si="216"/>
         <v>41325</v>
       </c>
       <c r="AS91" s="2">
@@ -30466,7 +30463,7 @@
         <v>40058</v>
       </c>
       <c r="AT91" s="2">
-        <f t="shared" ref="AT91" si="197">SUM(AT81:AT90)</f>
+        <f t="shared" ref="AT91" si="219">SUM(AT81:AT90)</f>
         <v>43424</v>
       </c>
       <c r="AU91" s="2">
@@ -30486,23 +30483,23 @@
       <c r="BC91" s="34"/>
       <c r="BD91" s="34"/>
       <c r="BM91" s="2">
-        <f>AD91</f>
+        <f t="shared" si="211"/>
         <v>41479</v>
       </c>
       <c r="BN91" s="2">
-        <f>AH91</f>
+        <f t="shared" si="212"/>
         <v>38260</v>
       </c>
       <c r="BO91" s="2">
-        <f>AL91</f>
+        <f t="shared" si="213"/>
         <v>39284</v>
       </c>
       <c r="BP91" s="2">
-        <f>AP91</f>
+        <f t="shared" si="214"/>
         <v>39561</v>
       </c>
       <c r="BQ91" s="2">
-        <f>AT91</f>
+        <f t="shared" si="215"/>
         <v>43424</v>
       </c>
       <c r="BR91" s="60"/>
@@ -30630,23 +30627,23 @@
         <v>48857</v>
       </c>
       <c r="BM92" s="1">
-        <f>AD92</f>
+        <f t="shared" si="211"/>
         <v>51605</v>
       </c>
       <c r="BN92" s="1">
-        <f>AH92</f>
+        <f t="shared" si="212"/>
         <v>52721</v>
       </c>
       <c r="BO92" s="1">
-        <f>AL92</f>
+        <f t="shared" si="213"/>
         <v>51664</v>
       </c>
       <c r="BP92" s="1">
-        <f>AP92</f>
+        <f t="shared" si="214"/>
         <v>50420</v>
       </c>
       <c r="BQ92" s="1">
-        <f>AT92</f>
+        <f t="shared" si="215"/>
         <v>48256</v>
       </c>
     </row>
@@ -30655,63 +30652,63 @@
         <v>2253</v>
       </c>
       <c r="AD93" s="2">
-        <f t="shared" ref="AD93:AR93" si="198">AD91+AD92</f>
+        <f t="shared" ref="AD93:AR93" si="220">AD91+AD92</f>
         <v>93084</v>
       </c>
       <c r="AE93" s="2">
-        <f t="shared" si="198"/>
+        <f t="shared" si="220"/>
         <v>91802</v>
       </c>
       <c r="AF93" s="2">
-        <f t="shared" si="198"/>
+        <f t="shared" si="220"/>
         <v>91756</v>
       </c>
       <c r="AG93" s="2">
-        <f t="shared" si="198"/>
+        <f t="shared" si="220"/>
         <v>91804</v>
       </c>
       <c r="AH93" s="2">
-        <f t="shared" si="198"/>
+        <f t="shared" si="220"/>
         <v>90981</v>
       </c>
       <c r="AI93" s="2">
-        <f t="shared" si="198"/>
+        <f t="shared" si="220"/>
         <v>89914</v>
       </c>
       <c r="AJ93" s="2">
-        <f t="shared" si="198"/>
+        <f t="shared" si="220"/>
         <v>93241</v>
       </c>
       <c r="AK93" s="2">
-        <f t="shared" si="198"/>
+        <f t="shared" si="220"/>
         <v>94134</v>
       </c>
       <c r="AL93" s="2">
-        <f t="shared" si="198"/>
+        <f t="shared" si="220"/>
         <v>90948</v>
       </c>
       <c r="AM93" s="2">
-        <f t="shared" si="198"/>
+        <f t="shared" si="220"/>
         <v>90776</v>
       </c>
       <c r="AN93" s="2">
-        <f t="shared" ref="AN93" si="199">AN91+AN92</f>
+        <f t="shared" ref="AN93" si="221">AN91+AN92</f>
         <v>90087</v>
       </c>
       <c r="AO93" s="2">
-        <f t="shared" ref="AO93" si="200">AO91+AO92</f>
+        <f t="shared" ref="AO93" si="222">AO91+AO92</f>
         <v>90836</v>
       </c>
       <c r="AP93" s="2">
-        <f t="shared" ref="AP93" si="201">AP91+AP92</f>
+        <f t="shared" ref="AP93" si="223">AP91+AP92</f>
         <v>89981</v>
       </c>
       <c r="AQ93" s="2">
-        <f t="shared" ref="AQ93" si="202">AQ91+AQ92</f>
+        <f t="shared" ref="AQ93" si="224">AQ91+AQ92</f>
         <v>89749</v>
       </c>
       <c r="AR93" s="2">
-        <f t="shared" si="198"/>
+        <f t="shared" si="220"/>
         <v>90042</v>
       </c>
       <c r="AS93" s="2">
@@ -30719,7 +30716,7 @@
         <v>89673</v>
       </c>
       <c r="AT93" s="2">
-        <f t="shared" ref="AT93" si="203">AT91+AT92</f>
+        <f t="shared" ref="AT93" si="225">AT91+AT92</f>
         <v>91680</v>
       </c>
       <c r="AU93" s="2">
@@ -30739,23 +30736,23 @@
       <c r="BC93" s="34"/>
       <c r="BD93" s="34"/>
       <c r="BM93" s="2">
-        <f>AD93</f>
+        <f t="shared" si="211"/>
         <v>93084</v>
       </c>
       <c r="BN93" s="2">
-        <f>AH93</f>
+        <f t="shared" si="212"/>
         <v>90981</v>
       </c>
       <c r="BO93" s="2">
-        <f>AL93</f>
+        <f t="shared" si="213"/>
         <v>90948</v>
       </c>
       <c r="BP93" s="2">
-        <f>AP93</f>
+        <f t="shared" si="214"/>
         <v>89981</v>
       </c>
       <c r="BQ93" s="2">
-        <f>AT93</f>
+        <f t="shared" si="215"/>
         <v>91680</v>
       </c>
       <c r="BR93" s="60"/>
@@ -30826,63 +30823,63 @@
         <v>102</v>
       </c>
       <c r="AD95" s="40">
-        <f t="shared" ref="AD95:AR95" si="204">SUM(AD69:AD74)/SUM(AD81:AD85)</f>
+        <f t="shared" ref="AD95:AR95" si="226">SUM(AD69:AD74)/SUM(AD81:AD85)</f>
         <v>3.2633681983781879</v>
       </c>
       <c r="AE95" s="40">
-        <f t="shared" si="204"/>
+        <f t="shared" si="226"/>
         <v>3.5543534260690364</v>
       </c>
       <c r="AF95" s="40">
-        <f t="shared" si="204"/>
+        <f t="shared" si="226"/>
         <v>3.5779828271177752</v>
       </c>
       <c r="AG95" s="40">
-        <f t="shared" si="204"/>
+        <f t="shared" si="226"/>
         <v>3.198610955528173</v>
       </c>
       <c r="AH95" s="40">
-        <f t="shared" si="204"/>
+        <f t="shared" si="226"/>
         <v>2.2971599160884297</v>
       </c>
       <c r="AI95" s="40">
-        <f t="shared" si="204"/>
+        <f t="shared" si="226"/>
         <v>1.9517334662205452</v>
       </c>
       <c r="AJ95" s="40">
-        <f t="shared" si="204"/>
+        <f t="shared" si="226"/>
         <v>2.1220877981334256</v>
       </c>
       <c r="AK95" s="40">
-        <f t="shared" si="204"/>
+        <f t="shared" si="226"/>
         <v>2.1358435614728521</v>
       </c>
       <c r="AL95" s="40">
-        <f t="shared" si="204"/>
+        <f t="shared" si="226"/>
         <v>3.009721608484313</v>
       </c>
       <c r="AM95" s="40">
-        <f t="shared" si="204"/>
+        <f t="shared" si="226"/>
         <v>3.0433292804244503</v>
       </c>
       <c r="AN95" s="40">
-        <f t="shared" si="204"/>
+        <f t="shared" si="226"/>
         <v>2.8799958583557674</v>
       </c>
       <c r="AO95" s="40">
-        <f t="shared" si="204"/>
+        <f t="shared" si="226"/>
         <v>2.8954248366013071</v>
       </c>
       <c r="AP95" s="40">
-        <f t="shared" si="204"/>
+        <f t="shared" si="226"/>
         <v>2.6012605431457967</v>
       </c>
       <c r="AQ95" s="40">
-        <f t="shared" si="204"/>
+        <f t="shared" si="226"/>
         <v>2.7441430932244582</v>
       </c>
       <c r="AR95" s="40">
-        <f t="shared" si="204"/>
+        <f t="shared" si="226"/>
         <v>2.3678556785567855</v>
       </c>
       <c r="AS95" s="40">
@@ -30890,7 +30887,7 @@
         <v>2.5220970537261698</v>
       </c>
       <c r="AT95" s="40">
-        <f t="shared" ref="AT95" si="205">SUM(AT69:AT74)/SUM(AT81:AT85)</f>
+        <f t="shared" ref="AT95" si="227">SUM(AT69:AT74)/SUM(AT81:AT85)</f>
         <v>2.3801056064606305</v>
       </c>
       <c r="AU95" s="40">
@@ -30906,11 +30903,11 @@
       <c r="BK95" s="40"/>
       <c r="BL95" s="40"/>
       <c r="BM95" s="40">
-        <f t="shared" ref="BM95:BN95" si="206">SUM(BM69:BM74)/SUM(BM81:BM85)</f>
+        <f t="shared" ref="BM95:BN95" si="228">SUM(BM69:BM74)/SUM(BM81:BM85)</f>
         <v>3.2633681983781879</v>
       </c>
       <c r="BN95" s="40">
-        <f t="shared" si="206"/>
+        <f t="shared" si="228"/>
         <v>2.2971599160884297</v>
       </c>
       <c r="BO95" s="40">
@@ -30931,63 +30928,63 @@
         <v>103</v>
       </c>
       <c r="AD96" s="40">
-        <f t="shared" ref="AD96:AR96" si="207">(SUM(AD69:AD73)-AD72)/SUM(AD81:AD85)</f>
+        <f t="shared" ref="AD96:AR96" si="229">(SUM(AD69:AD73)-AD72)/SUM(AD81:AD85)</f>
         <v>2.1429075096956165</v>
       </c>
       <c r="AE96" s="40">
-        <f t="shared" si="207"/>
+        <f t="shared" si="229"/>
         <v>2.3371973209685728</v>
       </c>
       <c r="AF96" s="40">
-        <f t="shared" si="207"/>
+        <f t="shared" si="229"/>
         <v>2.3557606048955528</v>
       </c>
       <c r="AG96" s="40">
-        <f t="shared" si="207"/>
+        <f t="shared" si="229"/>
         <v>2.1047384339643775</v>
       </c>
       <c r="AH96" s="40">
-        <f t="shared" si="207"/>
+        <f t="shared" si="229"/>
         <v>1.4879780538970468</v>
       </c>
       <c r="AI96" s="40">
-        <f t="shared" si="207"/>
+        <f t="shared" si="229"/>
         <v>1.2334306257563892</v>
       </c>
       <c r="AJ96" s="40">
-        <f t="shared" si="207"/>
+        <f t="shared" si="229"/>
         <v>1.4063601797442102</v>
       </c>
       <c r="AK96" s="40">
-        <f t="shared" si="207"/>
+        <f t="shared" si="229"/>
         <v>1.3861035989182442</v>
       </c>
       <c r="AL96" s="40">
-        <f t="shared" si="207"/>
+        <f t="shared" si="229"/>
         <v>1.8097657976137871</v>
       </c>
       <c r="AM96" s="40">
-        <f t="shared" si="207"/>
+        <f t="shared" si="229"/>
         <v>1.7906488338675803</v>
       </c>
       <c r="AN96" s="40">
-        <f t="shared" si="207"/>
+        <f t="shared" si="229"/>
         <v>1.6904120936011597</v>
       </c>
       <c r="AO96" s="40">
-        <f t="shared" si="207"/>
+        <f t="shared" si="229"/>
         <v>1.7144607843137254</v>
       </c>
       <c r="AP96" s="40">
-        <f t="shared" si="207"/>
+        <f t="shared" si="229"/>
         <v>1.5494485123737141</v>
       </c>
       <c r="AQ96" s="40">
-        <f t="shared" si="207"/>
+        <f t="shared" si="229"/>
         <v>1.6071741032370954</v>
       </c>
       <c r="AR96" s="40">
-        <f t="shared" si="207"/>
+        <f t="shared" si="229"/>
         <v>1.3906519065190652</v>
       </c>
       <c r="AS96" s="40">
@@ -30995,7 +30992,7 @@
         <v>1.4646447140381282</v>
       </c>
       <c r="AT96" s="40">
-        <f t="shared" ref="AT96" si="208">(SUM(AT69:AT73)-AT72)/SUM(AT81:AT85)</f>
+        <f t="shared" ref="AT96" si="230">(SUM(AT69:AT73)-AT72)/SUM(AT81:AT85)</f>
         <v>1.423978878707874</v>
       </c>
       <c r="AU96" s="40">
@@ -31011,11 +31008,11 @@
       <c r="BK96" s="40"/>
       <c r="BL96" s="40"/>
       <c r="BM96" s="40">
-        <f t="shared" ref="BM96:BN96" si="209">(SUM(BM69:BM73)-BM72)/SUM(BM81:BM85)</f>
+        <f t="shared" ref="BM96:BN96" si="231">(SUM(BM69:BM73)-BM72)/SUM(BM81:BM85)</f>
         <v>2.1429075096956165</v>
       </c>
       <c r="BN96" s="40">
-        <f t="shared" si="209"/>
+        <f t="shared" si="231"/>
         <v>1.4879780538970468</v>
       </c>
       <c r="BO96" s="40">
@@ -31036,63 +31033,63 @@
         <v>104</v>
       </c>
       <c r="AD97" s="40">
-        <f t="shared" ref="AD97:AR97" si="210">AD69/SUM(AD81:AD85)</f>
+        <f t="shared" ref="AD97:AR97" si="232">AD69/SUM(AD81:AD85)</f>
         <v>0.42225878481607709</v>
       </c>
       <c r="AE97" s="40">
-        <f t="shared" si="210"/>
+        <f t="shared" si="232"/>
         <v>0.38691396187532201</v>
       </c>
       <c r="AF97" s="40">
-        <f t="shared" si="210"/>
+        <f t="shared" si="232"/>
         <v>0.37165192874535435</v>
       </c>
       <c r="AG97" s="40">
-        <f t="shared" si="210"/>
+        <f t="shared" si="232"/>
         <v>0.38971659011986109</v>
       </c>
       <c r="AH97" s="40">
-        <f t="shared" si="210"/>
+        <f t="shared" si="232"/>
         <v>0.29966112635146036</v>
       </c>
       <c r="AI97" s="40">
-        <f t="shared" si="210"/>
+        <f t="shared" si="232"/>
         <v>0.15234569659001923</v>
       </c>
       <c r="AJ97" s="40">
-        <f t="shared" si="210"/>
+        <f t="shared" si="232"/>
         <v>0.33377117179398547</v>
       </c>
       <c r="AK97" s="40">
-        <f t="shared" si="210"/>
+        <f t="shared" si="232"/>
         <v>0.31350114416475972</v>
       </c>
       <c r="AL97" s="40">
-        <f t="shared" si="210"/>
+        <f t="shared" si="232"/>
         <v>0.17045956694653117</v>
       </c>
       <c r="AM97" s="40">
-        <f t="shared" si="210"/>
+        <f t="shared" si="232"/>
         <v>0.14800486349065989</v>
       </c>
       <c r="AN97" s="40">
-        <f t="shared" si="210"/>
+        <f t="shared" si="232"/>
         <v>0.1357423897287223</v>
       </c>
       <c r="AO97" s="40">
-        <f t="shared" si="210"/>
+        <f t="shared" si="232"/>
         <v>0.16574754901960784</v>
       </c>
       <c r="AP97" s="40">
-        <f t="shared" si="210"/>
+        <f t="shared" si="232"/>
         <v>0.11901010288256558</v>
       </c>
       <c r="AQ97" s="40">
-        <f t="shared" si="210"/>
+        <f t="shared" si="232"/>
         <v>0.1274424030329542</v>
       </c>
       <c r="AR97" s="40">
-        <f t="shared" si="210"/>
+        <f t="shared" si="232"/>
         <v>0.11430914309143092</v>
       </c>
       <c r="AS97" s="40">
@@ -31100,7 +31097,7 @@
         <v>0.10745233968804159</v>
       </c>
       <c r="AT97" s="40">
-        <f t="shared" ref="AT97" si="211">AT69/SUM(AT81:AT85)</f>
+        <f t="shared" ref="AT97" si="233">AT69/SUM(AT81:AT85)</f>
         <v>0.17223171299891288</v>
       </c>
       <c r="AU97" s="40">
@@ -31116,11 +31113,11 @@
       <c r="BK97" s="40"/>
       <c r="BL97" s="40"/>
       <c r="BM97" s="40">
-        <f t="shared" ref="BM97:BN97" si="212">BM69/SUM(BM81:BM85)</f>
+        <f t="shared" ref="BM97:BN97" si="234">BM69/SUM(BM81:BM85)</f>
         <v>0.42225878481607709</v>
       </c>
       <c r="BN97" s="40">
-        <f t="shared" si="212"/>
+        <f t="shared" si="234"/>
         <v>0.29966112635146036</v>
       </c>
       <c r="BO97" s="40">
@@ -31141,79 +31138,79 @@
         <v>105</v>
       </c>
       <c r="AD98" s="40">
-        <f t="shared" ref="AD98:AT98" si="213">AD43/AD79</f>
+        <f t="shared" ref="AD98:AT98" si="235">AD43/AD79</f>
         <v>8.7963559795453575E-2</v>
       </c>
       <c r="AE98" s="40">
-        <f t="shared" si="213"/>
+        <f t="shared" si="235"/>
         <v>8.7002461820003915E-2</v>
       </c>
       <c r="AF98" s="40">
-        <f t="shared" si="213"/>
+        <f t="shared" si="235"/>
         <v>8.55202929508697E-2</v>
       </c>
       <c r="AG98" s="40">
-        <f t="shared" si="213"/>
+        <f t="shared" si="235"/>
         <v>8.4560585595398891E-2</v>
       </c>
       <c r="AH98" s="40">
-        <f t="shared" si="213"/>
+        <f t="shared" si="235"/>
         <v>8.8908673239467578E-2</v>
       </c>
       <c r="AI98" s="40">
-        <f t="shared" si="213"/>
+        <f t="shared" si="235"/>
         <v>8.1978334853304274E-2</v>
       </c>
       <c r="AJ98" s="40">
-        <f t="shared" si="213"/>
+        <f t="shared" si="235"/>
         <v>8.1348333887452939E-2</v>
       </c>
       <c r="AK98" s="40">
-        <f t="shared" si="213"/>
+        <f t="shared" si="235"/>
         <v>8.2085112711666353E-2</v>
       </c>
       <c r="AL98" s="40">
-        <f t="shared" si="213"/>
+        <f t="shared" si="235"/>
         <v>9.3943792056999598E-2</v>
       </c>
       <c r="AM98" s="40">
-        <f t="shared" si="213"/>
+        <f t="shared" si="235"/>
         <v>8.4846214858552926E-2</v>
       </c>
       <c r="AN98" s="40">
-        <f t="shared" si="213"/>
+        <f t="shared" si="235"/>
         <v>8.8625439852586946E-2</v>
       </c>
       <c r="AO98" s="40">
-        <f t="shared" si="213"/>
+        <f t="shared" si="235"/>
         <v>8.9050596679730504E-2</v>
       </c>
       <c r="AP98" s="40">
-        <f t="shared" si="213"/>
+        <f t="shared" si="235"/>
         <v>9.5453484624531848E-2</v>
       </c>
       <c r="AQ98" s="40">
-        <f t="shared" si="213"/>
+        <f t="shared" si="235"/>
         <v>8.8190397664597936E-2</v>
       </c>
       <c r="AR98" s="40">
-        <f t="shared" si="213"/>
+        <f t="shared" si="235"/>
         <v>9.3323115879256346E-2</v>
       </c>
       <c r="AS98" s="40">
-        <f t="shared" si="213"/>
+        <f t="shared" si="235"/>
         <v>9.2160981627821686E-2</v>
       </c>
       <c r="AT98" s="40">
-        <f t="shared" si="213"/>
+        <f t="shared" si="235"/>
         <v>9.7349476439790569E-2</v>
       </c>
       <c r="AU98" s="40">
-        <f t="shared" ref="AU98:AV98" si="214">AU43/AU79</f>
+        <f t="shared" ref="AU98:AV98" si="236">AU43/AU79</f>
         <v>9.5339713025018619E-2</v>
       </c>
       <c r="AV98" s="40">
-        <f t="shared" si="214"/>
+        <f t="shared" si="236"/>
         <v>9.8099533641319819E-2</v>
       </c>
       <c r="BG98" s="40"/>
@@ -31246,79 +31243,79 @@
         <v>106</v>
       </c>
       <c r="AD99" s="40">
-        <f t="shared" ref="AD99:AV99" si="215">AD44/AVERAGE(AA72:AD72)</f>
+        <f t="shared" ref="AD99:AV99" si="237">AD44/AVERAGE(AA72:AD72)</f>
         <v>0.61488523069789014</v>
       </c>
       <c r="AE99" s="40">
-        <f t="shared" si="215"/>
+        <f t="shared" si="237"/>
         <v>0.60411580048831526</v>
       </c>
       <c r="AF99" s="40">
-        <f t="shared" si="215"/>
+        <f t="shared" si="237"/>
         <v>0.57845559845559846</v>
       </c>
       <c r="AG99" s="40">
-        <f t="shared" si="215"/>
+        <f t="shared" si="237"/>
         <v>0.56321575813101232</v>
       </c>
       <c r="AH99" s="40">
-        <f t="shared" si="215"/>
+        <f t="shared" si="237"/>
         <v>0.58332864298981257</v>
       </c>
       <c r="AI99" s="40">
-        <f t="shared" si="215"/>
+        <f t="shared" si="237"/>
         <v>0.55030621172353456</v>
       </c>
       <c r="AJ99" s="40">
-        <f t="shared" si="215"/>
+        <f t="shared" si="237"/>
         <v>0.53385279561966936</v>
       </c>
       <c r="AK99" s="40">
-        <f t="shared" si="215"/>
+        <f t="shared" si="237"/>
         <v>0.54172752455300932</v>
       </c>
       <c r="AL99" s="40">
-        <f t="shared" si="215"/>
+        <f t="shared" si="237"/>
         <v>0.58036236119228524</v>
       </c>
       <c r="AM99" s="40">
-        <f t="shared" si="215"/>
+        <f t="shared" si="237"/>
         <v>0.49142162591744193</v>
       </c>
       <c r="AN99" s="40">
-        <f t="shared" si="215"/>
+        <f t="shared" si="237"/>
         <v>0.49995473064735174</v>
       </c>
       <c r="AO99" s="40">
-        <f t="shared" si="215"/>
+        <f t="shared" si="237"/>
         <v>0.49587808029945191</v>
       </c>
       <c r="AP99" s="40">
-        <f t="shared" si="215"/>
+        <f t="shared" si="237"/>
         <v>0.54460093896713613</v>
       </c>
       <c r="AQ99" s="40">
-        <f t="shared" si="215"/>
+        <f t="shared" si="237"/>
         <v>0.49947989688390393</v>
       </c>
       <c r="AR99" s="40">
-        <f t="shared" si="215"/>
+        <f t="shared" si="237"/>
         <v>0.53965927825609084</v>
       </c>
       <c r="AS99" s="40">
-        <f t="shared" si="215"/>
+        <f t="shared" si="237"/>
         <v>0.51178637200736643</v>
       </c>
       <c r="AT99" s="40">
-        <f t="shared" si="215"/>
+        <f t="shared" si="237"/>
         <v>0.57254652167978526</v>
       </c>
       <c r="AU99" s="40">
-        <f t="shared" si="215"/>
+        <f t="shared" si="237"/>
         <v>0.54133032694475758</v>
       </c>
       <c r="AV99" s="40">
-        <f t="shared" si="215"/>
+        <f t="shared" si="237"/>
         <v>0.53579555399964995</v>
       </c>
       <c r="BG99" s="40"/>
@@ -31351,79 +31348,79 @@
         <v>107</v>
       </c>
       <c r="AD100" s="57">
-        <f t="shared" ref="AD100:AT100" si="216">AD58/AD79</f>
+        <f t="shared" ref="AD100:AT100" si="238">AD58/AD79</f>
         <v>1.4610459370031369E-2</v>
       </c>
       <c r="AE100" s="57">
-        <f t="shared" si="216"/>
+        <f t="shared" si="238"/>
         <v>8.3113657654517326E-3</v>
       </c>
       <c r="AF100" s="57">
-        <f t="shared" si="216"/>
+        <f t="shared" si="238"/>
         <v>1.4287893979685252E-2</v>
       </c>
       <c r="AG100" s="57">
-        <f t="shared" si="216"/>
+        <f t="shared" si="238"/>
         <v>1.612130190405647E-2</v>
       </c>
       <c r="AH100" s="57">
-        <f t="shared" si="216"/>
+        <f t="shared" si="238"/>
         <v>1.6322089227421111E-2</v>
       </c>
       <c r="AI100" s="57">
-        <f t="shared" si="216"/>
+        <f t="shared" si="238"/>
         <v>1.0332095113108081E-2</v>
       </c>
       <c r="AJ100" s="57">
-        <f t="shared" si="216"/>
+        <f t="shared" si="238"/>
         <v>4.5795304640662369E-3</v>
       </c>
       <c r="AK100" s="57">
-        <f t="shared" si="216"/>
+        <f t="shared" si="238"/>
         <v>1.2981494465336647E-2</v>
       </c>
       <c r="AL100" s="57">
-        <f t="shared" si="216"/>
+        <f t="shared" si="238"/>
         <v>1.2974446936711088E-2</v>
       </c>
       <c r="AM100" s="57">
-        <f t="shared" si="216"/>
+        <f t="shared" si="238"/>
         <v>8.7137569401603953E-3</v>
       </c>
       <c r="AN100" s="57">
-        <f t="shared" si="216"/>
+        <f t="shared" si="238"/>
         <v>1.0090246095441074E-2</v>
       </c>
       <c r="AO100" s="57">
-        <f t="shared" si="216"/>
+        <f t="shared" si="238"/>
         <v>1.4553701175745299E-2</v>
       </c>
       <c r="AP100" s="57">
-        <f t="shared" si="216"/>
+        <f t="shared" si="238"/>
         <v>7.2682010646692077E-3</v>
       </c>
       <c r="AQ100" s="57">
-        <f t="shared" si="216"/>
+        <f t="shared" si="238"/>
         <v>1.1621299401664642E-2</v>
       </c>
       <c r="AR100" s="57">
-        <f t="shared" si="216"/>
+        <f t="shared" si="238"/>
         <v>1.4104528997578908E-2</v>
       </c>
       <c r="AS100" s="57">
-        <f t="shared" si="216"/>
+        <f t="shared" si="238"/>
         <v>1.4382092405499428E-2</v>
       </c>
       <c r="AT100" s="57">
-        <f t="shared" si="216"/>
+        <f t="shared" si="238"/>
         <v>1.1507417102966841E-2</v>
       </c>
       <c r="AU100" s="57">
-        <f t="shared" ref="AU100:AV100" si="217">AU58/AU79</f>
+        <f t="shared" ref="AU100:AV100" si="239">AU58/AU79</f>
         <v>1.1559023262534315E-2</v>
       </c>
       <c r="AV100" s="57">
-        <f t="shared" si="217"/>
+        <f t="shared" si="239"/>
         <v>1.5052656930790621E-2</v>
       </c>
       <c r="BG100" s="57"/>
@@ -31456,79 +31453,79 @@
         <v>108</v>
       </c>
       <c r="AD101" s="57">
-        <f t="shared" ref="AD101:AT101" si="218">AD58/AD92</f>
+        <f t="shared" ref="AD101:AT101" si="240">AD58/AD92</f>
         <v>2.6354035461680071E-2</v>
       </c>
       <c r="AE101" s="57">
-        <f t="shared" si="218"/>
+        <f t="shared" si="240"/>
         <v>1.4768504180860948E-2</v>
       </c>
       <c r="AF101" s="57">
-        <f t="shared" si="218"/>
+        <f t="shared" si="240"/>
         <v>2.5134202453987731E-2</v>
       </c>
       <c r="AG101" s="57">
-        <f t="shared" si="218"/>
+        <f t="shared" si="240"/>
         <v>2.8077098193959631E-2</v>
       </c>
       <c r="AH101" s="57">
-        <f t="shared" si="218"/>
+        <f t="shared" si="240"/>
         <v>2.8167144022306103E-2</v>
       </c>
       <c r="AI101" s="57">
-        <f t="shared" si="218"/>
+        <f t="shared" si="240"/>
         <v>1.7580379615086197E-2</v>
       </c>
       <c r="AJ101" s="57">
-        <f t="shared" si="218"/>
+        <f t="shared" si="240"/>
         <v>8.2028623571222745E-3</v>
       </c>
       <c r="AK101" s="57">
-        <f t="shared" si="218"/>
+        <f t="shared" si="240"/>
         <v>2.3673912201170134E-2</v>
       </c>
       <c r="AL101" s="57">
-        <f t="shared" si="218"/>
+        <f t="shared" si="240"/>
         <v>2.2839888510374728E-2</v>
       </c>
       <c r="AM101" s="57">
-        <f t="shared" si="218"/>
+        <f t="shared" si="240"/>
         <v>1.5399591161296603E-2</v>
       </c>
       <c r="AN101" s="57">
-        <f t="shared" si="218"/>
+        <f t="shared" si="240"/>
         <v>1.7600247836273161E-2</v>
       </c>
       <c r="AO101" s="57">
-        <f t="shared" si="218"/>
+        <f t="shared" si="240"/>
         <v>2.5425032694822679E-2</v>
       </c>
       <c r="AP101" s="57">
-        <f t="shared" si="218"/>
+        <f t="shared" si="240"/>
         <v>1.297104323681079E-2</v>
       </c>
       <c r="AQ101" s="57">
-        <f t="shared" si="218"/>
+        <f t="shared" si="240"/>
         <v>2.1656976744186048E-2</v>
       </c>
       <c r="AR101" s="57">
-        <f t="shared" si="218"/>
+        <f t="shared" si="240"/>
         <v>2.6068928710716997E-2</v>
       </c>
       <c r="AS101" s="57">
-        <f t="shared" si="218"/>
+        <f t="shared" si="240"/>
         <v>2.6080822331956063E-2</v>
       </c>
       <c r="AT101" s="57">
-        <f t="shared" si="218"/>
+        <f t="shared" si="240"/>
         <v>2.1862566312997347E-2</v>
       </c>
       <c r="AU101" s="57">
-        <f t="shared" ref="AU101:AV101" si="219">AU58/AU92</f>
+        <f t="shared" ref="AU101:AV101" si="241">AU58/AU92</f>
         <v>2.0961402801572104E-2</v>
       </c>
       <c r="AV101" s="57">
-        <f t="shared" si="219"/>
+        <f t="shared" si="241"/>
         <v>2.8143357144319134E-2</v>
       </c>
       <c r="BG101" s="57"/>
@@ -31561,211 +31558,211 @@
         <v>109</v>
       </c>
       <c r="C103" s="1">
-        <f t="shared" ref="C103:F103" si="220">C58</f>
+        <f t="shared" ref="C103:F103" si="242">C58</f>
         <v>871</v>
       </c>
       <c r="D103" s="1">
-        <f t="shared" si="220"/>
+        <f t="shared" si="242"/>
         <v>828</v>
       </c>
       <c r="E103" s="1">
-        <f t="shared" si="220"/>
+        <f t="shared" si="242"/>
         <v>977</v>
       </c>
       <c r="F103" s="1">
-        <f t="shared" si="220"/>
+        <f t="shared" si="242"/>
         <v>-1</v>
       </c>
       <c r="G103" s="1">
-        <f t="shared" ref="G103:Z103" si="221">G58</f>
+        <f t="shared" ref="G103:Z103" si="243">G58</f>
         <v>820</v>
       </c>
       <c r="H103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>520</v>
       </c>
       <c r="I103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>1095</v>
       </c>
       <c r="J103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>1103</v>
       </c>
       <c r="K103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>929</v>
       </c>
       <c r="L103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>1115</v>
       </c>
       <c r="M103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>821</v>
       </c>
       <c r="N103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>1163</v>
       </c>
       <c r="O103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>1016</v>
       </c>
       <c r="P103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>2017</v>
       </c>
       <c r="Q103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>-1389</v>
       </c>
       <c r="R103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>1460</v>
       </c>
       <c r="S103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>1075</v>
       </c>
       <c r="T103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>1125</v>
       </c>
       <c r="U103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>1273</v>
       </c>
       <c r="V103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>1172</v>
       </c>
       <c r="W103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>864</v>
       </c>
       <c r="X103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>1364</v>
       </c>
       <c r="Y103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>1915</v>
       </c>
       <c r="Z103" s="1">
-        <f t="shared" si="221"/>
+        <f t="shared" si="243"/>
         <v>646</v>
       </c>
       <c r="AA103" s="1">
-        <f t="shared" ref="AA103:AT103" si="222">AA58</f>
+        <f t="shared" ref="AA103:AT103" si="244">AA58</f>
         <v>487</v>
       </c>
       <c r="AB103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>489</v>
       </c>
       <c r="AC103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>1270</v>
       </c>
       <c r="AD103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>1360</v>
       </c>
       <c r="AE103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>763</v>
       </c>
       <c r="AF103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>1311</v>
       </c>
       <c r="AG103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>1480</v>
       </c>
       <c r="AH103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>1485</v>
       </c>
       <c r="AI103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>929</v>
       </c>
       <c r="AJ103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>427</v>
       </c>
       <c r="AK103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>1222</v>
       </c>
       <c r="AL103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>1180</v>
       </c>
       <c r="AM103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>791</v>
       </c>
       <c r="AN103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>909</v>
       </c>
       <c r="AO103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>1322</v>
       </c>
       <c r="AP103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>654</v>
       </c>
       <c r="AQ103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>1043</v>
       </c>
       <c r="AR103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>1270</v>
       </c>
       <c r="AS103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>1294</v>
       </c>
       <c r="AT103" s="1">
-        <f t="shared" si="222"/>
+        <f t="shared" si="244"/>
         <v>1055</v>
       </c>
       <c r="AU103" s="1">
-        <f t="shared" ref="AU103:AV103" si="223">AU58</f>
+        <f t="shared" ref="AU103:AV103" si="245">AU58</f>
         <v>1040</v>
       </c>
       <c r="AV103" s="1">
-        <f t="shared" si="223"/>
+        <f t="shared" si="245"/>
         <v>1375</v>
       </c>
       <c r="BG103" s="1">
-        <f>SUM(C103:F103)</f>
+        <f t="shared" ref="BG103:BG108" si="246">SUM(C103:F103)</f>
         <v>2675</v>
       </c>
       <c r="BH103" s="1">
-        <f>SUM(G103:J103)</f>
+        <f t="shared" ref="BH103:BH108" si="247">SUM(G103:J103)</f>
         <v>3538</v>
       </c>
       <c r="BI103" s="1">
-        <f>SUM(K103:N103)</f>
+        <f t="shared" ref="BI103:BI108" si="248">SUM(K103:N103)</f>
         <v>4028</v>
       </c>
       <c r="BJ103" s="1">
-        <f>SUM(O103:R103)</f>
+        <f t="shared" ref="BJ103:BJ108" si="249">SUM(O103:R103)</f>
         <v>3104</v>
       </c>
       <c r="BK103" s="1">
-        <f>SUM(S103:V103)</f>
+        <f t="shared" ref="BK103:BK108" si="250">SUM(S103:V103)</f>
         <v>4645</v>
       </c>
       <c r="BL103" s="1">
-        <f>SUM(W103:Z103)</f>
+        <f t="shared" ref="BL103:BL108" si="251">SUM(W103:Z103)</f>
         <v>4789</v>
       </c>
       <c r="BM103" s="1">
@@ -31950,27 +31947,27 @@
       <c r="BC104" s="34"/>
       <c r="BD104" s="34"/>
       <c r="BG104" s="2">
-        <f>SUM(C104:F104)</f>
+        <f t="shared" si="246"/>
         <v>4902</v>
       </c>
       <c r="BH104" s="2">
-        <f>SUM(G104:J104)</f>
+        <f t="shared" si="247"/>
         <v>5218</v>
       </c>
       <c r="BI104" s="2">
-        <f>SUM(K104:N104)</f>
+        <f t="shared" si="248"/>
         <v>6880</v>
       </c>
       <c r="BJ104" s="2">
-        <f>SUM(O104:R104)</f>
+        <f t="shared" si="249"/>
         <v>4684</v>
       </c>
       <c r="BK104" s="2">
-        <f>SUM(S104:V104)</f>
+        <f t="shared" si="250"/>
         <v>7007</v>
       </c>
       <c r="BL104" s="2">
-        <f>SUM(W104:Z104)</f>
+        <f t="shared" si="251"/>
         <v>7234</v>
       </c>
       <c r="BM104" s="2">
@@ -32204,27 +32201,27 @@
         <v>-468</v>
       </c>
       <c r="BG105" s="1">
-        <f>SUM(C105:F105)</f>
+        <f t="shared" si="246"/>
         <v>-571</v>
       </c>
       <c r="BH105" s="1">
-        <f>SUM(G105:J105)</f>
+        <f t="shared" si="247"/>
         <v>-1046</v>
       </c>
       <c r="BI105" s="1">
-        <f>SUM(K105:N105)</f>
+        <f t="shared" si="248"/>
         <v>-1254</v>
       </c>
       <c r="BJ105" s="1">
-        <f>SUM(O105:R105)</f>
+        <f t="shared" si="249"/>
         <v>-1068</v>
       </c>
       <c r="BK105" s="1">
-        <f>SUM(S105:V105)</f>
+        <f t="shared" si="250"/>
         <v>-1134</v>
       </c>
       <c r="BL105" s="1">
-        <f>SUM(W105:Z105)</f>
+        <f t="shared" si="251"/>
         <v>-1213</v>
       </c>
       <c r="BM105" s="1">
@@ -32253,95 +32250,95 @@
         <v>112</v>
       </c>
       <c r="C106" s="2">
-        <f t="shared" ref="C106" si="224">C104+C105</f>
+        <f t="shared" ref="C106" si="252">C104+C105</f>
         <v>201</v>
       </c>
       <c r="D106" s="2">
-        <f t="shared" ref="D106" si="225">D104+D105</f>
+        <f t="shared" ref="D106" si="253">D104+D105</f>
         <v>812</v>
       </c>
       <c r="E106" s="2">
-        <f t="shared" ref="E106" si="226">E104+E105</f>
+        <f t="shared" ref="E106" si="254">E104+E105</f>
         <v>1661</v>
       </c>
       <c r="F106" s="2">
-        <f t="shared" ref="F106" si="227">F104+F105</f>
+        <f t="shared" ref="F106" si="255">F104+F105</f>
         <v>1657</v>
       </c>
       <c r="G106" s="2">
-        <f t="shared" ref="G106:Y106" si="228">G104+G105</f>
+        <f t="shared" ref="G106:Y106" si="256">G104+G105</f>
         <v>592</v>
       </c>
       <c r="H106" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="256"/>
         <v>1057</v>
       </c>
       <c r="I106" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="256"/>
         <v>1550</v>
       </c>
       <c r="J106" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="256"/>
         <v>973</v>
       </c>
       <c r="K106" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="256"/>
         <v>1220</v>
       </c>
       <c r="L106" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="256"/>
         <v>1204</v>
       </c>
       <c r="M106" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="256"/>
         <v>1759</v>
       </c>
       <c r="N106" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="256"/>
         <v>1443</v>
       </c>
       <c r="O106" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="256"/>
         <v>459</v>
       </c>
       <c r="P106" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="256"/>
         <v>661</v>
       </c>
       <c r="Q106" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="256"/>
         <v>1750</v>
       </c>
       <c r="R106" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="256"/>
         <v>746</v>
       </c>
       <c r="S106" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="256"/>
         <v>1411</v>
       </c>
       <c r="T106" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="256"/>
         <v>957</v>
       </c>
       <c r="U106" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="256"/>
         <v>1753</v>
       </c>
       <c r="V106" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="256"/>
         <v>1752</v>
       </c>
       <c r="W106" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="256"/>
         <v>1209</v>
       </c>
       <c r="X106" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="256"/>
         <v>1584</v>
       </c>
       <c r="Y106" s="2">
-        <f t="shared" si="228"/>
+        <f t="shared" si="256"/>
         <v>2114</v>
       </c>
       <c r="Z106" s="2">
@@ -32361,79 +32358,79 @@
         <v>1993</v>
       </c>
       <c r="AD106" s="2">
-        <f t="shared" ref="AD106:AS106" si="229">AD104+AD105</f>
+        <f t="shared" ref="AD106:AS106" si="257">AD104+AD105</f>
         <v>1368</v>
       </c>
       <c r="AE106" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="257"/>
         <v>914</v>
       </c>
       <c r="AF106" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="257"/>
         <v>1498</v>
       </c>
       <c r="AG106" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="257"/>
         <v>1898</v>
       </c>
       <c r="AH106" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="257"/>
         <v>1668</v>
       </c>
       <c r="AI106" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="257"/>
         <v>657</v>
       </c>
       <c r="AJ106" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="257"/>
         <v>599</v>
       </c>
       <c r="AK106" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="257"/>
         <v>1242</v>
       </c>
       <c r="AL106" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="257"/>
         <v>2082</v>
       </c>
       <c r="AM106" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="257"/>
         <v>521</v>
       </c>
       <c r="AN106" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="257"/>
         <v>200</v>
       </c>
       <c r="AO106" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="257"/>
         <v>2128</v>
       </c>
       <c r="AP106" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="257"/>
         <v>2351</v>
       </c>
       <c r="AQ106" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="257"/>
         <v>466</v>
       </c>
       <c r="AR106" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="257"/>
         <v>554</v>
       </c>
       <c r="AS106" s="2">
-        <f t="shared" si="229"/>
+        <f t="shared" si="257"/>
         <v>2096</v>
       </c>
       <c r="AT106" s="2">
-        <f t="shared" ref="AT106:AU106" si="230">AT104+AT105</f>
+        <f t="shared" ref="AT106:AU106" si="258">AT104+AT105</f>
         <v>2069</v>
       </c>
       <c r="AU106" s="2">
-        <f t="shared" si="230"/>
+        <f t="shared" si="258"/>
         <v>584</v>
       </c>
       <c r="AV106" s="2">
-        <f t="shared" ref="AV106" si="231">AV104+AV105</f>
+        <f t="shared" ref="AV106" si="259">AV104+AV105</f>
         <v>457</v>
       </c>
       <c r="AW106" s="34"/>
@@ -32445,43 +32442,43 @@
       <c r="BC106" s="34"/>
       <c r="BD106" s="34"/>
       <c r="BG106" s="2">
-        <f>SUM(C106:F106)</f>
+        <f t="shared" si="246"/>
         <v>4331</v>
       </c>
       <c r="BH106" s="2">
-        <f>SUM(G106:J106)</f>
+        <f t="shared" si="247"/>
         <v>4172</v>
       </c>
       <c r="BI106" s="2">
-        <f>SUM(K106:N106)</f>
+        <f t="shared" si="248"/>
         <v>5626</v>
       </c>
       <c r="BJ106" s="2">
-        <f>SUM(O106:R106)</f>
+        <f t="shared" si="249"/>
         <v>3616</v>
       </c>
       <c r="BK106" s="2">
-        <f>SUM(S106:V106)</f>
+        <f t="shared" si="250"/>
         <v>5873</v>
       </c>
       <c r="BL106" s="2">
-        <f>SUM(W106:Z106)</f>
+        <f t="shared" si="251"/>
         <v>6021</v>
       </c>
       <c r="BM106" s="2">
-        <f t="shared" ref="BM106" si="232">BM104+BM105</f>
+        <f t="shared" ref="BM106" si="260">BM104+BM105</f>
         <v>4885</v>
       </c>
       <c r="BN106" s="2">
-        <f t="shared" ref="BN106" si="233">BN104+BN105</f>
+        <f t="shared" ref="BN106" si="261">BN104+BN105</f>
         <v>5978</v>
       </c>
       <c r="BO106" s="2">
-        <f t="shared" ref="BO106" si="234">BO104+BO105</f>
+        <f t="shared" ref="BO106" si="262">BO104+BO105</f>
         <v>4580</v>
       </c>
       <c r="BP106" s="2">
-        <f t="shared" ref="BP106" si="235">BP104+BP105</f>
+        <f t="shared" ref="BP106" si="263">BP104+BP105</f>
         <v>5200</v>
       </c>
       <c r="BQ106" s="2">
@@ -32556,227 +32553,227 @@
         <v>113</v>
       </c>
       <c r="C107" s="43">
-        <f t="shared" ref="C107:F107" si="236">C59</f>
+        <f t="shared" ref="C107:F107" si="264">C59</f>
         <v>993</v>
       </c>
       <c r="D107" s="43">
-        <f t="shared" si="236"/>
+        <f t="shared" si="264"/>
         <v>982</v>
       </c>
       <c r="E107" s="43">
-        <f t="shared" si="236"/>
+        <f t="shared" si="264"/>
         <v>984</v>
       </c>
       <c r="F107" s="43">
-        <f t="shared" si="236"/>
+        <f t="shared" si="264"/>
         <v>1096</v>
       </c>
       <c r="G107" s="43">
-        <f t="shared" ref="G107:Z107" si="237">G59</f>
+        <f t="shared" ref="G107:Z107" si="265">G59</f>
         <v>1418</v>
       </c>
       <c r="H107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1413</v>
       </c>
       <c r="I107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1407</v>
       </c>
       <c r="J107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1410</v>
       </c>
       <c r="K107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1392</v>
       </c>
       <c r="L107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1380</v>
       </c>
       <c r="M107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1372</v>
       </c>
       <c r="N107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1379</v>
       </c>
       <c r="O107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1362</v>
       </c>
       <c r="P107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1355</v>
       </c>
       <c r="Q107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1354</v>
       </c>
       <c r="R107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1357</v>
       </c>
       <c r="S107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1353</v>
       </c>
       <c r="T107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1349</v>
       </c>
       <c r="U107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1343</v>
       </c>
       <c r="V107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1346</v>
       </c>
       <c r="W107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1341</v>
       </c>
       <c r="X107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1341</v>
       </c>
       <c r="Y107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1341</v>
       </c>
       <c r="Z107" s="43">
-        <f t="shared" si="237"/>
+        <f t="shared" si="265"/>
         <v>1341</v>
       </c>
       <c r="AA107" s="43">
-        <f t="shared" ref="AA107:AT107" si="238">AA59</f>
+        <f t="shared" ref="AA107:AT107" si="266">AA59</f>
         <v>1341.9</v>
       </c>
       <c r="AB107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1344.4</v>
       </c>
       <c r="AC107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1346.4</v>
       </c>
       <c r="AD107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1344.9</v>
       </c>
       <c r="AE107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1344.5</v>
       </c>
       <c r="AF107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1345.1</v>
       </c>
       <c r="AG107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1343.7</v>
       </c>
       <c r="AH107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1342.4</v>
       </c>
       <c r="AI107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1329.4</v>
       </c>
       <c r="AJ107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1329.4</v>
       </c>
       <c r="AK107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1330.2</v>
       </c>
       <c r="AL107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1329.8</v>
       </c>
       <c r="AM107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1330.5</v>
       </c>
       <c r="AN107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1330.2</v>
       </c>
       <c r="AO107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1329.7</v>
       </c>
       <c r="AP107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1327.7</v>
       </c>
       <c r="AQ107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1293.3</v>
       </c>
       <c r="AR107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1282.4000000000001</v>
       </c>
       <c r="AS107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1282.4000000000001</v>
       </c>
       <c r="AT107" s="43">
-        <f t="shared" si="238"/>
+        <f t="shared" si="266"/>
         <v>1285.5999999999999</v>
       </c>
       <c r="AU107" s="43">
-        <f t="shared" ref="AU107:AV107" si="239">AU59</f>
+        <f t="shared" ref="AU107:AV107" si="267">AU59</f>
         <v>1281.5999999999999</v>
       </c>
       <c r="AV107" s="43">
-        <f t="shared" si="239"/>
+        <f t="shared" si="267"/>
         <v>1282</v>
       </c>
       <c r="BG107" s="1">
-        <f>SUM(C107:F107)</f>
+        <f t="shared" si="246"/>
         <v>4055</v>
       </c>
       <c r="BH107" s="1">
-        <f>SUM(G107:J107)</f>
+        <f t="shared" si="247"/>
         <v>5648</v>
       </c>
       <c r="BI107" s="1">
-        <f>SUM(K107:N107)</f>
+        <f t="shared" si="248"/>
         <v>5523</v>
       </c>
       <c r="BJ107" s="1">
-        <f>SUM(O107:R107)</f>
+        <f t="shared" si="249"/>
         <v>5428</v>
       </c>
       <c r="BK107" s="1">
-        <f>SUM(S107:V107)</f>
+        <f t="shared" si="250"/>
         <v>5391</v>
       </c>
       <c r="BL107" s="1">
-        <f>SUM(W107:Z107)</f>
+        <f t="shared" si="251"/>
         <v>5364</v>
       </c>
       <c r="BM107" s="43">
-        <f t="shared" ref="BM107:BP107" si="240">BM59</f>
+        <f t="shared" ref="BM107:BP107" si="268">BM59</f>
         <v>1341.9</v>
       </c>
       <c r="BN107" s="43">
-        <f t="shared" si="240"/>
+        <f t="shared" si="268"/>
         <v>1342.4</v>
       </c>
       <c r="BO107" s="43">
-        <f t="shared" si="240"/>
+        <f t="shared" si="268"/>
         <v>1329.8</v>
       </c>
       <c r="BP107" s="43">
-        <f t="shared" si="240"/>
+        <f t="shared" si="268"/>
         <v>1327.7</v>
       </c>
       <c r="BQ107" s="43">
@@ -32789,171 +32786,171 @@
         <v>114</v>
       </c>
       <c r="C108" s="40">
-        <f t="shared" ref="C108:F108" si="241">C106/C107</f>
+        <f t="shared" ref="C108:F108" si="269">C106/C107</f>
         <v>0.20241691842900303</v>
       </c>
       <c r="D108" s="40">
-        <f t="shared" si="241"/>
+        <f t="shared" si="269"/>
         <v>0.8268839103869654</v>
       </c>
       <c r="E108" s="40">
-        <f t="shared" si="241"/>
+        <f t="shared" si="269"/>
         <v>1.6880081300813008</v>
       </c>
       <c r="F108" s="40">
-        <f t="shared" si="241"/>
+        <f t="shared" si="269"/>
         <v>1.5118613138686132</v>
       </c>
       <c r="G108" s="40">
-        <f t="shared" ref="G108:AA108" si="242">G106/G107</f>
+        <f t="shared" ref="G108:AA108" si="270">G106/G107</f>
         <v>0.41748942172073344</v>
       </c>
       <c r="H108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>0.7480537862703468</v>
       </c>
       <c r="I108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>1.1016346837242359</v>
       </c>
       <c r="J108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>0.69007092198581566</v>
       </c>
       <c r="K108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>0.87643678160919536</v>
       </c>
       <c r="L108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>0.87246376811594206</v>
       </c>
       <c r="M108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>1.282069970845481</v>
       </c>
       <c r="N108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>1.0464104423495286</v>
       </c>
       <c r="O108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>0.33700440528634362</v>
       </c>
       <c r="P108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>0.48782287822878229</v>
       </c>
       <c r="Q108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>1.292466765140325</v>
       </c>
       <c r="R108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>0.54974207811348563</v>
       </c>
       <c r="S108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>1.0428677014042869</v>
       </c>
       <c r="T108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>0.70941438102297993</v>
       </c>
       <c r="U108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>1.3052866716306777</v>
       </c>
       <c r="V108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>1.3016344725111442</v>
       </c>
       <c r="W108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>0.90156599552572703</v>
       </c>
       <c r="X108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>1.1812080536912752</v>
       </c>
       <c r="Y108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>1.5764354958985831</v>
       </c>
       <c r="Z108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>0.83072334079045485</v>
       </c>
       <c r="AA108" s="40">
-        <f t="shared" si="242"/>
+        <f t="shared" si="270"/>
         <v>-4.1731872717788207E-2</v>
       </c>
       <c r="AB108" s="40">
-        <f t="shared" ref="AB108:AR108" si="243">AB106/AB107</f>
+        <f t="shared" ref="AB108:AR108" si="271">AB106/AB107</f>
         <v>1.1752454626599225</v>
       </c>
       <c r="AC108" s="40">
-        <f t="shared" si="243"/>
+        <f t="shared" si="271"/>
         <v>1.4802436125965537</v>
       </c>
       <c r="AD108" s="40">
-        <f t="shared" si="243"/>
+        <f t="shared" si="271"/>
         <v>1.0171759982154807</v>
       </c>
       <c r="AE108" s="40">
-        <f t="shared" si="243"/>
+        <f t="shared" si="271"/>
         <v>0.67980661956117516</v>
       </c>
       <c r="AF108" s="40">
-        <f t="shared" si="243"/>
+        <f t="shared" si="271"/>
         <v>1.1136718459594084</v>
       </c>
       <c r="AG108" s="40">
-        <f t="shared" si="243"/>
+        <f t="shared" si="271"/>
         <v>1.4125176750762818</v>
       </c>
       <c r="AH108" s="40">
-        <f t="shared" si="243"/>
+        <f t="shared" si="271"/>
         <v>1.2425506555423123</v>
       </c>
       <c r="AI108" s="40">
-        <f t="shared" si="243"/>
+        <f t="shared" si="271"/>
         <v>0.49420791334436587</v>
       </c>
       <c r="AJ108" s="40">
-        <f t="shared" si="243"/>
+        <f t="shared" si="271"/>
         <v>0.45057920866556339</v>
       </c>
       <c r="AK108" s="40">
-        <f t="shared" si="243"/>
+        <f t="shared" si="271"/>
         <v>0.93369418132611637</v>
       </c>
       <c r="AL108" s="40">
-        <f t="shared" si="243"/>
+        <f t="shared" si="271"/>
         <v>1.5656489697698903</v>
       </c>
       <c r="AM108" s="40">
-        <f t="shared" si="243"/>
+        <f t="shared" si="271"/>
         <v>0.39158211198797443</v>
       </c>
       <c r="AN108" s="40">
-        <f t="shared" si="243"/>
+        <f t="shared" si="271"/>
         <v>0.15035333032626672</v>
       </c>
       <c r="AO108" s="40">
-        <f t="shared" si="243"/>
+        <f t="shared" si="271"/>
         <v>1.6003609836805295</v>
       </c>
       <c r="AP108" s="40">
-        <f t="shared" si="243"/>
+        <f t="shared" si="271"/>
         <v>1.7707313399111244</v>
       </c>
       <c r="AQ108" s="40">
-        <f t="shared" si="243"/>
+        <f t="shared" si="271"/>
         <v>0.3603185649114668</v>
       </c>
       <c r="AR108" s="40">
-        <f t="shared" si="243"/>
+        <f t="shared" si="271"/>
         <v>0.43200249532127261</v>
       </c>
       <c r="AS108" s="40">
@@ -32961,7 +32958,7 @@
         <v>1.634435433562071</v>
       </c>
       <c r="AT108" s="40">
-        <f t="shared" ref="AT108" si="244">AT106/AT107</f>
+        <f t="shared" ref="AT108" si="272">AT106/AT107</f>
         <v>1.6093652769135036</v>
       </c>
       <c r="AU108" s="40">
@@ -32973,43 +32970,43 @@
         <v>0.35647425897035884</v>
       </c>
       <c r="BG108" s="40">
-        <f>SUM(C108:F108)</f>
+        <f t="shared" si="246"/>
         <v>4.2291702727658826</v>
       </c>
       <c r="BH108" s="40">
-        <f>SUM(G108:J108)</f>
+        <f t="shared" si="247"/>
         <v>2.9572488137011317</v>
       </c>
       <c r="BI108" s="40">
-        <f>SUM(K108:N108)</f>
+        <f t="shared" si="248"/>
         <v>4.077380962920147</v>
       </c>
       <c r="BJ108" s="40">
-        <f>SUM(O108:R108)</f>
+        <f t="shared" si="249"/>
         <v>2.6670361267689366</v>
       </c>
       <c r="BK108" s="40">
-        <f>SUM(S108:V108)</f>
+        <f t="shared" si="250"/>
         <v>4.3592032265690888</v>
       </c>
       <c r="BL108" s="40">
-        <f>SUM(W108:Z108)</f>
+        <f t="shared" si="251"/>
         <v>4.4899328859060397</v>
       </c>
       <c r="BM108" s="40">
-        <f t="shared" ref="BM108:BP108" si="245">BM106/BM107</f>
+        <f t="shared" ref="BM108:BP108" si="273">BM106/BM107</f>
         <v>3.6403606826142036</v>
       </c>
       <c r="BN108" s="40">
-        <f t="shared" si="245"/>
+        <f t="shared" si="273"/>
         <v>4.4532181168057212</v>
       </c>
       <c r="BO108" s="40">
-        <f t="shared" si="245"/>
+        <f t="shared" si="273"/>
         <v>3.4441269363814109</v>
       </c>
       <c r="BP108" s="40">
-        <f t="shared" si="245"/>
+        <f t="shared" si="273"/>
         <v>3.9165474128191606</v>
       </c>
       <c r="BQ108" s="40">
@@ -33138,7 +33135,7 @@
     </row>
     <row r="71" spans="8:30" ht="15">
       <c r="H71" s="2" t="s">
-        <v>2316</v>
+        <v>2314</v>
       </c>
       <c r="AD71" s="2" t="s">
         <v>118</v>
@@ -33164,7 +33161,7 @@
     </row>
     <row r="107" spans="8:30" ht="15">
       <c r="H107" s="2" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="AD107" s="2" t="s">
         <v>119</v>
@@ -33190,7 +33187,7 @@
     </row>
     <row r="140" spans="8:30" ht="15">
       <c r="H140" s="2" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="AD140" s="2" t="s">
         <v>2274</v>
@@ -33216,7 +33213,7 @@
     </row>
     <row r="173" spans="8:10" ht="15">
       <c r="H173" s="2" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="182" spans="1:7">
